--- a/AAII_Financials/Quarterly/BNED_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BNED_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="92">
   <si>
     <t>BNED</t>
   </si>
@@ -656,405 +656,431 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45318</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45227</v>
+      </c>
+      <c r="F7" s="2">
         <v>45136</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45045</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>44954</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44863</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44772</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44681</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44590</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44499</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44408</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44317</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44226</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44135</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44044</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>43953</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43855</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43764</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43673</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43582</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43491</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43400</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43309</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43218</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43127</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43036</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>42945</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>42854</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>42763</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>456700</v>
+      </c>
+      <c r="E8" s="3">
+        <v>610400</v>
+      </c>
+      <c r="F8" s="3">
         <v>264200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>215200</v>
       </c>
-      <c r="F8" s="3">
-        <v>447100</v>
-      </c>
-      <c r="G8" s="3">
-        <v>617100</v>
-      </c>
       <c r="H8" s="3">
+        <v>438100</v>
+      </c>
+      <c r="I8" s="3">
+        <v>608600</v>
+      </c>
+      <c r="J8" s="3">
         <v>254700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>225200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>402800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>867800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>240800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>222800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>411600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>595500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>204000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>256900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>502300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>772200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>319700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>332100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>548000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>814800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>337500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>357700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>603400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>1242600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>355700</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>342800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>521600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>770700</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>356600</v>
+      </c>
+      <c r="E9" s="3">
+        <v>474100</v>
+      </c>
+      <c r="F9" s="3">
         <v>213500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>178300</v>
       </c>
-      <c r="F9" s="3">
-        <v>342900</v>
-      </c>
-      <c r="G9" s="3">
-        <v>472300</v>
-      </c>
       <c r="H9" s="3">
+        <v>341000</v>
+      </c>
+      <c r="I9" s="3">
+        <v>470500</v>
+      </c>
+      <c r="J9" s="3">
         <v>198700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>331900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>315800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>662200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>180800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>186900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>341000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>480200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>173200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>191500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>383800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>585300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>248000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>214700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>799300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>1173000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>270900</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>228200</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>456900</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>961300</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>291000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>218600</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>405700</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>599200</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>100100</v>
+      </c>
+      <c r="E10" s="3">
+        <v>136300</v>
+      </c>
+      <c r="F10" s="3">
         <v>50700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>36900</v>
       </c>
-      <c r="F10" s="3">
-        <v>104200</v>
-      </c>
-      <c r="G10" s="3">
-        <v>144800</v>
-      </c>
       <c r="H10" s="3">
+        <v>97100</v>
+      </c>
+      <c r="I10" s="3">
+        <v>138100</v>
+      </c>
+      <c r="J10" s="3">
         <v>56000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>-106700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>87000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>205600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>60000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>35900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>70600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>115300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>30800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>65400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>118500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>186900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>71700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>117400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>-251300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>-358200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>66600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>129500</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>146500</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>281300</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>64700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>124200</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>115900</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>171500</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1086,8 +1112,10 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1175,8 +1203,14 @@
       <c r="AE12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1264,186 +1298,204 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>9200</v>
+      </c>
+      <c r="E14" s="3">
+        <v>4300</v>
+      </c>
+      <c r="F14" s="3">
         <v>4600</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>3500</v>
       </c>
-      <c r="F14" s="3">
-        <v>12000</v>
-      </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
+        <v>10100</v>
+      </c>
+      <c r="I14" s="3">
         <v>300</v>
       </c>
-      <c r="H14" s="3">
+      <c r="J14" s="3">
         <v>400</v>
       </c>
-      <c r="I14" s="3">
+      <c r="K14" s="3">
         <v>-2800</v>
       </c>
-      <c r="J14" s="3">
+      <c r="L14" s="3">
         <v>6500</v>
       </c>
-      <c r="K14" s="3">
+      <c r="M14" s="3">
         <v>3000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="N14" s="3">
         <v>1900</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>29300</v>
       </c>
-      <c r="O14" s="3">
+      <c r="Q14" s="3">
         <v>3400</v>
       </c>
-      <c r="P14" s="3">
+      <c r="R14" s="3">
         <v>5700</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="S14" s="3">
         <v>15300</v>
       </c>
-      <c r="R14" s="3">
+      <c r="T14" s="3">
         <v>200</v>
       </c>
-      <c r="S14" s="3">
+      <c r="U14" s="3">
         <v>1600</v>
       </c>
-      <c r="T14" s="3">
+      <c r="V14" s="3">
         <v>1900</v>
       </c>
-      <c r="U14" s="3">
+      <c r="W14" s="3">
         <v>62500</v>
       </c>
-      <c r="V14" s="3">
+      <c r="X14" s="3">
         <v>2600</v>
       </c>
-      <c r="W14" s="3">
+      <c r="Y14" s="3">
         <v>500</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3">
         <v>200</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AB14" s="3">
         <v>313200</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AC14" s="3">
         <v>7300</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AD14" s="3">
         <v>5800</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AE14" s="3">
         <v>7000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AF14" s="3">
         <v>500</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AG14" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>10100</v>
+      </c>
+      <c r="E15" s="3">
+        <v>10200</v>
+      </c>
+      <c r="F15" s="3">
         <v>10300</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>8300</v>
       </c>
-      <c r="F15" s="3">
-        <v>10600</v>
-      </c>
-      <c r="G15" s="3">
-        <v>10800</v>
-      </c>
       <c r="H15" s="3">
+        <v>10100</v>
+      </c>
+      <c r="I15" s="3">
+        <v>10300</v>
+      </c>
+      <c r="J15" s="3">
         <v>10900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>5400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>12200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>24600</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>12600</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>12400</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>13300</v>
       </c>
-      <c r="O15" s="3">
+      <c r="Q15" s="3">
         <v>13200</v>
       </c>
-      <c r="P15" s="3">
+      <c r="R15" s="3">
         <v>14100</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="S15" s="3">
         <v>15300</v>
       </c>
-      <c r="R15" s="3">
+      <c r="T15" s="3">
         <v>15100</v>
       </c>
-      <c r="S15" s="3">
+      <c r="U15" s="3">
         <v>15500</v>
       </c>
-      <c r="T15" s="3">
+      <c r="V15" s="3">
         <v>15900</v>
       </c>
-      <c r="U15" s="3">
+      <c r="W15" s="3">
         <v>16500</v>
       </c>
-      <c r="V15" s="3">
+      <c r="X15" s="3">
         <v>16400</v>
       </c>
-      <c r="W15" s="3">
+      <c r="Y15" s="3">
         <v>16400</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Z15" s="3">
         <v>16500</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="AA15" s="3">
         <v>16900</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AB15" s="3">
         <v>17000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AC15" s="3">
         <v>31700</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AD15" s="3">
         <v>15000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AE15" s="3">
         <v>14300</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AF15" s="3">
         <v>13100</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AG15" s="3">
         <v>13000</v>
       </c>
     </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1472,186 +1524,200 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>455800</v>
+      </c>
+      <c r="E17" s="3">
+        <v>574500</v>
+      </c>
+      <c r="F17" s="3">
         <v>305900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>242600</v>
       </c>
-      <c r="F17" s="3">
-        <v>464900</v>
-      </c>
-      <c r="G17" s="3">
-        <v>590400</v>
-      </c>
       <c r="H17" s="3">
+        <v>453100</v>
+      </c>
+      <c r="I17" s="3">
+        <v>580000</v>
+      </c>
+      <c r="J17" s="3">
         <v>300300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>235800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>435900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>883900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>281500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>282800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>476300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>588800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>262900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>309300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>505300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>715800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>363500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>392100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>545000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>736300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>386600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>352400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>899000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>1214900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>411300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>338500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>516400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>713900</v>
       </c>
     </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>900</v>
+      </c>
+      <c r="E18" s="3">
+        <v>35900</v>
+      </c>
+      <c r="F18" s="3">
         <v>-41700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-27400</v>
       </c>
-      <c r="F18" s="3">
-        <v>-17800</v>
-      </c>
-      <c r="G18" s="3">
-        <v>26700</v>
-      </c>
       <c r="H18" s="3">
+        <v>-15000</v>
+      </c>
+      <c r="I18" s="3">
+        <v>28600</v>
+      </c>
+      <c r="J18" s="3">
         <v>-45600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-10600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-33100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-16100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-40700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-60000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-64700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>6700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-58900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-52400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-3000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>56400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-43800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-60000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>3000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>78500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>-49100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>5300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>-295600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>27700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>-55600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>4300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>5200</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>56800</v>
       </c>
     </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1683,8 +1749,10 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1701,7 +1769,7 @@
         <v>0</v>
       </c>
       <c r="H20" s="3">
-        <v>0</v>
+        <v>6900</v>
       </c>
       <c r="I20" s="3">
         <v>0</v>
@@ -1772,364 +1840,394 @@
       <c r="AE20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>11100</v>
+      </c>
+      <c r="E21" s="3">
+        <v>46000</v>
+      </c>
+      <c r="F21" s="3">
         <v>-31500</v>
       </c>
-      <c r="E21" s="3">
-        <v>-24000</v>
-      </c>
-      <c r="F21" s="3">
-        <v>-5600</v>
-      </c>
       <c r="G21" s="3">
-        <v>39100</v>
+        <v>-16500</v>
       </c>
       <c r="H21" s="3">
+        <v>2000</v>
+      </c>
+      <c r="I21" s="3">
+        <v>35700</v>
+      </c>
+      <c r="J21" s="3">
         <v>-31500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-8800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-19600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>11000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-26800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-46300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-50100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>21100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>-43700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>-36000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>13200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>73000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>-27000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>-42500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>19200</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>95000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>-32500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>22100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>-278600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>59400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>-40500</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>18600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>18300</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>69700</v>
       </c>
     </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>10600</v>
+      </c>
+      <c r="E22" s="3">
+        <v>10700</v>
+      </c>
+      <c r="F22" s="3">
         <v>8300</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>7000</v>
       </c>
-      <c r="F22" s="3">
-        <v>6900</v>
-      </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
+        <v>13800</v>
+      </c>
+      <c r="I22" s="3">
         <v>4900</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>3900</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>2300</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>3100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>4800</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>2500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>2200</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>2300</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>900</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>2700</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>1600</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>1900</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>1400</v>
-      </c>
-      <c r="T22" s="3">
-        <v>2500</v>
-      </c>
-      <c r="U22" s="3">
-        <v>1900</v>
       </c>
       <c r="V22" s="3">
         <v>2500</v>
       </c>
       <c r="W22" s="3">
+        <v>1900</v>
+      </c>
+      <c r="X22" s="3">
+        <v>2500</v>
+      </c>
+      <c r="Y22" s="3">
         <v>1800</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Z22" s="3">
         <v>3500</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="AA22" s="3">
         <v>2500</v>
-      </c>
-      <c r="Z22" s="3">
-        <v>3000</v>
-      </c>
-      <c r="AA22" s="3">
-        <v>4900</v>
       </c>
       <c r="AB22" s="3">
         <v>3000</v>
       </c>
       <c r="AC22" s="3">
+        <v>4900</v>
+      </c>
+      <c r="AD22" s="3">
+        <v>3000</v>
+      </c>
+      <c r="AE22" s="3">
         <v>1500</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AF22" s="3">
         <v>700</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AG22" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-9700</v>
+      </c>
+      <c r="E23" s="3">
+        <v>25200</v>
+      </c>
+      <c r="F23" s="3">
         <v>-50000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-34400</v>
       </c>
-      <c r="F23" s="3">
-        <v>-24800</v>
-      </c>
-      <c r="G23" s="3">
-        <v>21800</v>
-      </c>
       <c r="H23" s="3">
+        <v>-22000</v>
+      </c>
+      <c r="I23" s="3">
+        <v>23800</v>
+      </c>
+      <c r="J23" s="3">
         <v>-49500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-12900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-36200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-20900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-43200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-62200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-67000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>5800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-61600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-54000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-4900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>55000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-46300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-62000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>76600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-52600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>2700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>-298600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>22800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>-58600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>2900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>4500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>56100</v>
       </c>
     </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E24" s="3">
+        <v>300</v>
+      </c>
+      <c r="F24" s="3">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3">
         <v>100</v>
       </c>
-      <c r="F24" s="3">
-        <v>300</v>
-      </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
+        <v>100</v>
+      </c>
+      <c r="I24" s="3">
+        <v>-400</v>
+      </c>
+      <c r="J24" s="3">
+        <v>800</v>
+      </c>
+      <c r="K24" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="L24" s="3">
+        <v>600</v>
+      </c>
+      <c r="M24" s="3">
+        <v>200</v>
+      </c>
+      <c r="N24" s="3">
+        <v>400</v>
+      </c>
+      <c r="O24" s="3">
+        <v>-9800</v>
+      </c>
+      <c r="P24" s="3">
+        <v>-18700</v>
+      </c>
+      <c r="Q24" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="R24" s="3">
+        <v>-14900</v>
+      </c>
+      <c r="S24" s="3">
+        <v>-13700</v>
+      </c>
+      <c r="T24" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="U24" s="3">
+        <v>19100</v>
+      </c>
+      <c r="V24" s="3">
+        <v>-14200</v>
+      </c>
+      <c r="W24" s="3">
+        <v>-15700</v>
+      </c>
+      <c r="X24" s="3">
         <v>-300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="Y24" s="3">
+        <v>16900</v>
+      </c>
+      <c r="Z24" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="AA24" s="3">
+        <v>-15000</v>
+      </c>
+      <c r="AB24" s="3">
+        <v>5800</v>
+      </c>
+      <c r="AC24" s="3">
+        <v>9200</v>
+      </c>
+      <c r="AD24" s="3">
+        <v>-23800</v>
+      </c>
+      <c r="AE24" s="3">
+        <v>2600</v>
+      </c>
+      <c r="AF24" s="3">
         <v>800</v>
       </c>
-      <c r="I24" s="3">
-        <v>-10000</v>
-      </c>
-      <c r="J24" s="3">
-        <v>600</v>
-      </c>
-      <c r="K24" s="3">
-        <v>200</v>
-      </c>
-      <c r="L24" s="3">
-        <v>400</v>
-      </c>
-      <c r="M24" s="3">
-        <v>-9800</v>
-      </c>
-      <c r="N24" s="3">
-        <v>-18700</v>
-      </c>
-      <c r="O24" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="P24" s="3">
-        <v>-14900</v>
-      </c>
-      <c r="Q24" s="3">
-        <v>-13700</v>
-      </c>
-      <c r="R24" s="3">
-        <v>-3200</v>
-      </c>
-      <c r="S24" s="3">
-        <v>19100</v>
-      </c>
-      <c r="T24" s="3">
-        <v>-14200</v>
-      </c>
-      <c r="U24" s="3">
-        <v>-15700</v>
-      </c>
-      <c r="V24" s="3">
-        <v>-300</v>
-      </c>
-      <c r="W24" s="3">
-        <v>16900</v>
-      </c>
-      <c r="X24" s="3">
-        <v>-14000</v>
-      </c>
-      <c r="Y24" s="3">
-        <v>-15000</v>
-      </c>
-      <c r="Z24" s="3">
-        <v>5800</v>
-      </c>
-      <c r="AA24" s="3">
-        <v>9200</v>
-      </c>
-      <c r="AB24" s="3">
-        <v>-23800</v>
-      </c>
-      <c r="AC24" s="3">
-        <v>2600</v>
-      </c>
-      <c r="AD24" s="3">
-        <v>800</v>
-      </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>26800</v>
       </c>
     </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2217,186 +2315,204 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-9900</v>
+      </c>
+      <c r="E26" s="3">
+        <v>24900</v>
+      </c>
+      <c r="F26" s="3">
         <v>-50000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-34500</v>
       </c>
-      <c r="F26" s="3">
-        <v>-25000</v>
-      </c>
-      <c r="G26" s="3">
-        <v>22100</v>
-      </c>
       <c r="H26" s="3">
+        <v>-22100</v>
+      </c>
+      <c r="I26" s="3">
+        <v>24200</v>
+      </c>
+      <c r="J26" s="3">
         <v>-50300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-2900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-36800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-21100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-43600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-52400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-48300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>7500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-46700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-40300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-1700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>35900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-32200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-46200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>59700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-38600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>17800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>-304400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>13600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>-34800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>3800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>29300</v>
       </c>
     </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-9900</v>
+      </c>
+      <c r="E27" s="3">
+        <v>24900</v>
+      </c>
+      <c r="F27" s="3">
         <v>-50000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-34500</v>
       </c>
-      <c r="F27" s="3">
-        <v>-25000</v>
-      </c>
-      <c r="G27" s="3">
-        <v>22100</v>
-      </c>
       <c r="H27" s="3">
+        <v>-22100</v>
+      </c>
+      <c r="I27" s="3">
+        <v>24200</v>
+      </c>
+      <c r="J27" s="3">
         <v>-50300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-2900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-36800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-21100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-43600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-52400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-48300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>7500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-46700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-40300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-1700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>35900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-32100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-46200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>59700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-38600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>17800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>-304400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>13600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>-34800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>3800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>29300</v>
       </c>
     </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2484,41 +2600,47 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>300</v>
+      </c>
+      <c r="E29" s="3">
+        <v>-700</v>
+      </c>
+      <c r="F29" s="3">
         <v>-400</v>
       </c>
-      <c r="E29" s="3">
+      <c r="G29" s="3">
         <v>-11700</v>
       </c>
-      <c r="F29" s="3" t="s">
+      <c r="H29" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="I29" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="J29" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="K29" s="3">
+        <v>-7300</v>
+      </c>
+      <c r="L29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G29" s="3" t="s">
+      <c r="M29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H29" s="3">
-        <v>-2400</v>
-      </c>
-      <c r="I29" s="3">
-        <v>-7300</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L29" s="3">
-        <v>0</v>
-      </c>
-      <c r="M29" s="3">
-        <v>0</v>
-      </c>
       <c r="N29" s="3">
         <v>0</v>
       </c>
@@ -2534,11 +2656,11 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-      <c r="S29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="T29" s="3" t="s">
-        <v>8</v>
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+      <c r="T29" s="3">
+        <v>0</v>
       </c>
       <c r="U29" s="3" t="s">
         <v>8</v>
@@ -2552,20 +2674,20 @@
       <c r="X29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Y29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA29" s="3">
         <v>-700</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AB29" s="3">
         <v>21100</v>
       </c>
-      <c r="AA29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC29" s="3" t="s">
-        <v>8</v>
+      <c r="AC29" s="3">
+        <v>0</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>8</v>
@@ -2573,8 +2695,14 @@
       <c r="AE29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2662,8 +2790,14 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2751,8 +2885,14 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2769,7 +2909,7 @@
         <v>0</v>
       </c>
       <c r="H32" s="3">
-        <v>0</v>
+        <v>-6900</v>
       </c>
       <c r="I32" s="3">
         <v>0</v>
@@ -2840,97 +2980,109 @@
       <c r="AE32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-9600</v>
+      </c>
+      <c r="E33" s="3">
+        <v>24200</v>
+      </c>
+      <c r="F33" s="3">
         <v>-50400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-46300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-25000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>22100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-52700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-10200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-36800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-21100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-43600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-52400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-48300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>7500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-46700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-40300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-1700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>35900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-32100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-46200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>59700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-38600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>17100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>-283200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>13600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>-34800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>3800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>29300</v>
       </c>
     </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3018,191 +3170,209 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-9600</v>
+      </c>
+      <c r="E35" s="3">
+        <v>24200</v>
+      </c>
+      <c r="F35" s="3">
         <v>-50400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-46300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-25000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>22100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-52700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-10200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-36800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-21100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-43600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-52400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-48300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>7500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-46700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-40300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-1700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>35900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-32100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-46200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>59700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-38600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>17100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>-283200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>13600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>-34800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>3800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>29300</v>
       </c>
     </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45318</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45227</v>
+      </c>
+      <c r="F38" s="2">
         <v>45136</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45045</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>44954</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44863</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44772</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44681</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44590</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44499</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44408</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44317</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44226</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44135</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44044</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>43953</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43855</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43764</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43673</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43582</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43491</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43400</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43309</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43218</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43127</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43036</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>42945</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>42854</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>42763</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3234,8 +3404,10 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3267,97 +3439,105 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>8100</v>
+      </c>
+      <c r="E41" s="3">
+        <v>15000</v>
+      </c>
+      <c r="F41" s="3">
         <v>7700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>14200</v>
       </c>
-      <c r="F41" s="3">
-        <v>11100</v>
-      </c>
-      <c r="G41" s="3">
-        <v>19100</v>
-      </c>
       <c r="H41" s="3">
+        <v>9400</v>
+      </c>
+      <c r="I41" s="3">
+        <v>17300</v>
+      </c>
+      <c r="J41" s="3">
         <v>7600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>8800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>10000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>11000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>7600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>8000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>9900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>7400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>7500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>8200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>9800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>24600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>8200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>14000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>22000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>20000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>13300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>16100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>22400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>17500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>14200</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>19000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>132100</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>176600</v>
       </c>
     </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3445,364 +3625,394 @@
       <c r="AE42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>315100</v>
+      </c>
+      <c r="E43" s="3">
+        <v>221800</v>
+      </c>
+      <c r="F43" s="3">
         <v>140900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>92500</v>
       </c>
-      <c r="F43" s="3">
-        <v>277500</v>
-      </c>
-      <c r="G43" s="3">
-        <v>210000</v>
-      </c>
       <c r="H43" s="3">
+        <v>276900</v>
+      </c>
+      <c r="I43" s="3">
+        <v>209300</v>
+      </c>
+      <c r="J43" s="3">
         <v>119000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>136000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>250200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>218100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>118300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>121100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>227200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>167500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>107500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>90900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>238000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>162500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>98500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>98200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>231100</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>138000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>99800</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>100100</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>243400</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>153600</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>112500</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>86000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>178800</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>93300</v>
       </c>
     </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>386100</v>
+      </c>
+      <c r="E44" s="3">
+        <v>416100</v>
+      </c>
+      <c r="F44" s="3">
         <v>391000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>353300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>444400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>420900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>472100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>323500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>444600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>421200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>479100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>309800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>493300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>508400</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>591700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>469600</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>578700</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>543600</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>723000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>467300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>630200</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>576500</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>736100</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>493900</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>675900</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>593600</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>787300</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>486900</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AF44" s="3">
         <v>561400</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AG44" s="3">
         <v>488000</v>
       </c>
     </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>54300</v>
+      </c>
+      <c r="E45" s="3">
+        <v>63400</v>
+      </c>
+      <c r="F45" s="3">
         <v>59000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>76900</v>
       </c>
-      <c r="F45" s="3">
-        <v>57000</v>
-      </c>
-      <c r="G45" s="3">
-        <v>54900</v>
-      </c>
       <c r="H45" s="3">
+        <v>140000</v>
+      </c>
+      <c r="I45" s="3">
+        <v>137000</v>
+      </c>
+      <c r="J45" s="3">
         <v>147800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>63400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>60600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>69000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>64700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>61900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>25300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>23800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>22400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>16200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>24600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>18500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>18100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>11800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>20700</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>16600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>18700</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>9200</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>12300</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>13400</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>13500</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>10700</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>8100</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>8100</v>
       </c>
     </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>763700</v>
+      </c>
+      <c r="E46" s="3">
+        <v>716400</v>
+      </c>
+      <c r="F46" s="3">
         <v>598600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>537000</v>
       </c>
-      <c r="F46" s="3">
-        <v>790100</v>
-      </c>
-      <c r="G46" s="3">
-        <v>705000</v>
-      </c>
       <c r="H46" s="3">
+        <v>813700</v>
+      </c>
+      <c r="I46" s="3">
+        <v>729600</v>
+      </c>
+      <c r="J46" s="3">
         <v>686200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>531700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>765400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>719200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>669700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>500800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>755700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>707000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>729100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>584900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>851200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>749200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>847800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>591400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>904000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>751200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>867900</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>619400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>954000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>778100</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>927500</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>602600</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>880400</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>766000</v>
       </c>
     </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3890,186 +4100,204 @@
       <c r="AE47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>277500</v>
+      </c>
+      <c r="E48" s="3">
+        <v>307900</v>
+      </c>
+      <c r="F48" s="3">
         <v>347500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>315100</v>
       </c>
-      <c r="F48" s="3">
-        <v>351700</v>
-      </c>
-      <c r="G48" s="3">
-        <v>387800</v>
-      </c>
       <c r="H48" s="3">
+        <v>331500</v>
+      </c>
+      <c r="I48" s="3">
+        <v>367200</v>
+      </c>
+      <c r="J48" s="3">
         <v>391800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>360200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>323000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>344500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>380200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>329600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>330300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>379200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>414400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>348600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>352800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>394900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>420300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>109800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>109400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>112000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>108100</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>111300</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>111000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>115300</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>112800</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>116600</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>107300</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>108500</v>
       </c>
     </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>97900</v>
+      </c>
+      <c r="E49" s="3">
+        <v>104000</v>
+      </c>
+      <c r="F49" s="3">
         <v>107400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>110600</v>
       </c>
-      <c r="F49" s="3">
-        <v>119600</v>
-      </c>
-      <c r="G49" s="3">
-        <v>126200</v>
-      </c>
       <c r="H49" s="3">
+        <v>119000</v>
+      </c>
+      <c r="I49" s="3">
+        <v>125200</v>
+      </c>
+      <c r="J49" s="3">
         <v>128000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>131700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>138700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>146500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>150700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>155600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>160200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>170800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>175200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>179800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>184300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>188900</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>193900</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>199700</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>262400</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>267900</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>263200</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>268400</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>273600</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>591900</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>535800</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>539400</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AF49" s="3">
         <v>473000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AG49" s="3">
         <v>475900</v>
       </c>
     </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4157,8 +4385,14 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4246,97 +4480,109 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>12500</v>
+      </c>
+      <c r="E52" s="3">
+        <v>16700</v>
+      </c>
+      <c r="F52" s="3">
         <v>17300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>18000</v>
       </c>
-      <c r="F52" s="3">
-        <v>19700</v>
-      </c>
-      <c r="G52" s="3">
-        <v>21000</v>
-      </c>
       <c r="H52" s="3">
+        <v>39600</v>
+      </c>
+      <c r="I52" s="3">
+        <v>42100</v>
+      </c>
+      <c r="J52" s="3">
         <v>44600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>52700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>39700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>42000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>43300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>45000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>42200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>40000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>42100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>43100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>39800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>47300</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>40500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>45400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>40200</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>41600</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>41700</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>40100</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>42000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>41900</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>42500</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>41200</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>39200</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>38200</v>
       </c>
     </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4424,97 +4670,109 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1151600</v>
+      </c>
+      <c r="E54" s="3">
+        <v>1145000</v>
+      </c>
+      <c r="F54" s="3">
         <v>1070800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>980800</v>
       </c>
-      <c r="F54" s="3">
-        <v>1281100</v>
-      </c>
-      <c r="G54" s="3">
-        <v>1240000</v>
-      </c>
       <c r="H54" s="3">
+        <v>1279400</v>
+      </c>
+      <c r="I54" s="3">
+        <v>1238400</v>
+      </c>
+      <c r="J54" s="3">
         <v>1223600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>1071600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>1266700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>1252200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>1244000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>1031100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>1288500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>1297000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>1360800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>1156400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>1428100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>1380300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>1502400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>946200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>1316100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>1172700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>1280900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>1039200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>1380600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>1527200</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>1618700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>1299800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>1499900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>1388600</v>
       </c>
     </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4546,8 +4804,10 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4579,105 +4839,113 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>343100</v>
+      </c>
+      <c r="E57" s="3">
+        <v>385900</v>
+      </c>
+      <c r="F57" s="3">
         <v>275400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>267900</v>
       </c>
-      <c r="F57" s="3">
-        <v>355300</v>
-      </c>
-      <c r="G57" s="3">
-        <v>326200</v>
-      </c>
       <c r="H57" s="3">
+        <v>355200</v>
+      </c>
+      <c r="I57" s="3">
+        <v>326000</v>
+      </c>
+      <c r="J57" s="3">
         <v>324400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>182600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>359700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>333100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>331100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>137600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>318800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>314000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>291500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>143700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>389100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>387700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>443100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>186800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>464900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>443300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>463700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>187900</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>489000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>458800</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>511500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>192700</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>480400</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>439700</v>
       </c>
     </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
-      </c>
-      <c r="E58" s="3">
-        <v>0</v>
+        <v>224100</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F58" s="3">
         <v>0</v>
@@ -4686,435 +4954,465 @@
         <v>0</v>
       </c>
       <c r="H58" s="3">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
         <v>40000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>40000</v>
       </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3">
         <v>50000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>50000</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
-      </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
       <c r="P58" s="3">
         <v>0</v>
       </c>
       <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3">
+        <v>0</v>
+      </c>
+      <c r="S58" s="3">
         <v>75000</v>
       </c>
-      <c r="R58" s="3">
-        <v>0</v>
-      </c>
-      <c r="S58" s="3">
-        <v>0</v>
-      </c>
       <c r="T58" s="3">
+        <v>0</v>
+      </c>
+      <c r="U58" s="3">
+        <v>0</v>
+      </c>
+      <c r="V58" s="3">
         <v>100000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>100000</v>
       </c>
-      <c r="V58" s="3">
-        <v>0</v>
-      </c>
-      <c r="W58" s="3">
-        <v>0</v>
-      </c>
       <c r="X58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z58" s="3">
         <v>100000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>100000</v>
       </c>
-      <c r="Z58" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA58" s="3">
-        <v>0</v>
-      </c>
       <c r="AB58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD58" s="3">
         <v>100000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>100000</v>
       </c>
-      <c r="AD58" s="3" t="s">
+      <c r="AF58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE58" s="3" t="s">
+      <c r="AG58" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>282400</v>
+      </c>
+      <c r="E59" s="3">
+        <v>238500</v>
+      </c>
+      <c r="F59" s="3">
         <v>240700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>194200</v>
       </c>
-      <c r="F59" s="3">
-        <v>254200</v>
-      </c>
-      <c r="G59" s="3">
-        <v>249500</v>
-      </c>
       <c r="H59" s="3">
+        <v>392600</v>
+      </c>
+      <c r="I59" s="3">
+        <v>368400</v>
+      </c>
+      <c r="J59" s="3">
         <v>244100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>192800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>402300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>363900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>228000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>186100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>231400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>255700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>206600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>188000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>296000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>304900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>187000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>121700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>219700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>170000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>93200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>125600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>252200</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>184300</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>89900</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>120500</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>207700</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>140800</v>
       </c>
     </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>849600</v>
+      </c>
+      <c r="E60" s="3">
+        <v>624400</v>
+      </c>
+      <c r="F60" s="3">
         <v>516100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>462100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>609600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>575700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>608400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>415400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>611300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>574300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>609100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>373700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>550200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>569700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>498100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>406700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>685000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>692600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>730200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>408500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>684600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>613400</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>657000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>413500</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>741200</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>643100</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>701400</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>413200</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>688100</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>580500</v>
       </c>
     </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>30200</v>
+      </c>
+      <c r="E61" s="3">
+        <v>233900</v>
+      </c>
+      <c r="F61" s="3">
         <v>277700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>182200</v>
       </c>
-      <c r="F61" s="3">
-        <v>285600</v>
-      </c>
-      <c r="G61" s="3">
-        <v>252000</v>
-      </c>
       <c r="H61" s="3">
+        <v>283900</v>
+      </c>
+      <c r="I61" s="3">
+        <v>250400</v>
+      </c>
+      <c r="J61" s="3">
         <v>218600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>185700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>200400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>183300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>153700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>127600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>150800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>99500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>234600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>99700</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>65900</v>
       </c>
-      <c r="S61" s="3">
-        <v>0</v>
-      </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+      <c r="V61" s="3">
         <v>74100</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>33500</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>70100</v>
       </c>
-      <c r="W61" s="3">
-        <v>0</v>
-      </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z61" s="3">
         <v>130200</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>96400</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>113000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>41800</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>120100</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>59600</v>
       </c>
-      <c r="AD61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE61" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>174700</v>
+      </c>
+      <c r="E62" s="3">
+        <v>180700</v>
+      </c>
+      <c r="F62" s="3">
         <v>196000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>205800</v>
       </c>
-      <c r="F62" s="3">
-        <v>209400</v>
-      </c>
-      <c r="G62" s="3">
-        <v>211800</v>
-      </c>
       <c r="H62" s="3">
+        <v>228800</v>
+      </c>
+      <c r="I62" s="3">
+        <v>231500</v>
+      </c>
+      <c r="J62" s="3">
         <v>219800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>242100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>266300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>273600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>257300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>262100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>243300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>247300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>255900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>232300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>219800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>230300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>277400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>53500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>66600</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>67300</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>62000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>61400</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>77700</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>112500</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>116200</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>113300</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>98900</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>101700</v>
       </c>
     </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5202,8 +5500,14 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5291,8 +5595,14 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5380,97 +5690,109 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1054500</v>
+      </c>
+      <c r="E66" s="3">
+        <v>1039000</v>
+      </c>
+      <c r="F66" s="3">
         <v>989800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>850000</v>
       </c>
-      <c r="F66" s="3">
-        <v>1104600</v>
-      </c>
-      <c r="G66" s="3">
-        <v>1039500</v>
-      </c>
       <c r="H66" s="3">
+        <v>1102900</v>
+      </c>
+      <c r="I66" s="3">
+        <v>1037900</v>
+      </c>
+      <c r="J66" s="3">
         <v>1046800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>843200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>1029300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>980000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>994700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>738100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>944300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>916600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>988500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>738700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>970700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>922900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>1081700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>495600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>821400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>680700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>849200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>571200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>931900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>797400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>937800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>586100</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>787000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>682200</v>
       </c>
     </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5502,8 +5824,10 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5591,8 +5915,14 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5680,8 +6010,14 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5769,8 +6105,14 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5858,97 +6200,109 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-629200</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-619600</v>
+      </c>
+      <c r="F72" s="3">
         <v>-643700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-593400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-547100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-522100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-544200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-491500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-480500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-443700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-466300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-422600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-370300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-322000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-329500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-282800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-242500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-240800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-276700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-244600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-198400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-199100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>-258800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>-220200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>-237300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>46000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>-2400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>32400</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>32100</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>28400</v>
       </c>
     </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6036,8 +6390,14 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6125,8 +6485,14 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6214,97 +6580,109 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>97100</v>
+      </c>
+      <c r="E76" s="3">
+        <v>106000</v>
+      </c>
+      <c r="F76" s="3">
         <v>81100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>130800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>176500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>200500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>176800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>228400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>237500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>272200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>249300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>293000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>344200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>380400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>372300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>417800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>457400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>457300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>420800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>450600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>494700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>492000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>431700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>468000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>448700</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>729800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>680900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>713700</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>712900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>706400</v>
       </c>
     </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6392,191 +6770,209 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45318</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45227</v>
+      </c>
+      <c r="F80" s="2">
         <v>45136</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45045</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>44954</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44863</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44772</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44681</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44590</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44499</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44408</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44317</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44226</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44135</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44044</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>43953</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43855</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43764</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43673</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43582</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43491</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43400</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43309</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43218</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43127</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43036</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>42945</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>42854</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>42763</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-9600</v>
+      </c>
+      <c r="E81" s="3">
+        <v>24200</v>
+      </c>
+      <c r="F81" s="3">
         <v>-50400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-46300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-25000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>22100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-52700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-10200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-36800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-21100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-43600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-52400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-48300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>7500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-46700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-40300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-1700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>35900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-32100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-46200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>59700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-38600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>17100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>-283200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>13600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>-34800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>3800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>29300</v>
       </c>
     </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6608,97 +7004,105 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>10100</v>
+      </c>
+      <c r="E83" s="3">
+        <v>10200</v>
+      </c>
+      <c r="F83" s="3">
         <v>10300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>3400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>12300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>12400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>14100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>14100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>13600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>27200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>13900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>13700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>14600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>14400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>15200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>16400</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>16200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>16500</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>16800</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>17600</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>16200</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>16600</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>16500</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>16900</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>17000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>31700</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AD83" s="3">
         <v>15000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AE83" s="3">
         <v>14300</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AF83" s="3">
         <v>13100</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AG83" s="3">
         <v>13000</v>
       </c>
     </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6786,8 +7190,14 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6875,8 +7285,14 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6964,8 +7380,14 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7053,8 +7475,14 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7142,97 +7570,109 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-35800</v>
+      </c>
+      <c r="E89" s="3">
+        <v>72000</v>
+      </c>
+      <c r="F89" s="3">
         <v>-123100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>114300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-32000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>38400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-29000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-5800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-16400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>24300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-17300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-8700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-49800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>144500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-53100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-100700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-69400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>201700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>-40200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>-55000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>-60700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>263900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>-27400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>-81400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>-58200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>199600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>-56000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>-77000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>-34300</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>204500</v>
       </c>
     </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7264,97 +7704,105 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="F91" s="3">
         <v>-4200</v>
       </c>
-      <c r="E91" s="3">
-        <v>-1800</v>
-      </c>
-      <c r="F91" s="3">
-        <v>-6300</v>
-      </c>
       <c r="G91" s="3">
-        <v>-10800</v>
+        <v>-3400</v>
       </c>
       <c r="H91" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="I91" s="3">
+        <v>-7100</v>
+      </c>
+      <c r="J91" s="3">
         <v>-9700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-12100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-9900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-11400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-11300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-9700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-9100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-7100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-9400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-7600</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-10900</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-8300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-14700</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-8600</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-14900</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-8200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-12700</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-7700</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-22400</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-7900</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-8200</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AF91" s="3">
         <v>-9000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AG91" s="3">
         <v>-11300</v>
       </c>
     </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7442,8 +7890,14 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7531,97 +7985,109 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="F94" s="3">
         <v>17300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-4700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-6000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-10600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-9700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-10000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-11900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-20800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-11000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-11300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-12600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-7500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-5500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-7900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-5600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-10000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-6100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-13000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-7400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-25000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-9300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-11300</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-7500</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-81300</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-9100</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-190800</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>-10200</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>-10600</v>
       </c>
     </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7653,8 +8119,10 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7742,8 +8210,14 @@
       <c r="AE96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7831,8 +8305,14 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7920,8 +8400,14 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8009,97 +8495,109 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>18700</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-52000</v>
+      </c>
+      <c r="F100" s="3">
         <v>93200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-106100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>32700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-9700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>33400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>25000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>17300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>3400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>24900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>25700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>62200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-135600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>59500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>108800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>65900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-175300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>40600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>60000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>70100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-232200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>33800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>83400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>71200</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-119400</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>60500</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>155100</v>
       </c>
-      <c r="AD100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG100" s="3">
         <v>-26300</v>
       </c>
     </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8187,93 +8685,105 @@
       <c r="AE101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-20300</v>
+      </c>
+      <c r="E102" s="3">
+        <v>16000</v>
+      </c>
+      <c r="F102" s="3">
         <v>-12700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>3400</v>
-      </c>
-      <c r="F102" s="3">
-        <v>-5300</v>
-      </c>
-      <c r="G102" s="3">
-        <v>18100</v>
       </c>
       <c r="H102" s="3">
         <v>-5300</v>
       </c>
       <c r="I102" s="3">
+        <v>18100</v>
+      </c>
+      <c r="J102" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="K102" s="3">
         <v>9200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-10800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>6700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-3600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>6100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>2600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-1600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-14800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>16400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-5800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>-8000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>2000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>6800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>-2900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>-8200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>4900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>-1500</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>-4800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>-112700</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>-44500</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>167700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BNED_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BNED_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="92">
   <si>
     <t>BNED</t>
   </si>
@@ -656,431 +656,456 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45500</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45409</v>
+      </c>
+      <c r="F7" s="2">
         <v>45318</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45227</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45136</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45045</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44954</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44863</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44772</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44681</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44590</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44499</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44408</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44317</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44226</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44135</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44044</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43953</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43855</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43764</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43673</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43582</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43491</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43400</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43309</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43218</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43127</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43036</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>42945</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>42854</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>42763</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>263400</v>
+      </c>
+      <c r="E8" s="3">
+        <v>235900</v>
+      </c>
+      <c r="F8" s="3">
         <v>456700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>610400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>264200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>215200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>438100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>608600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>254700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>225200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>402800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>867800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>240800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>222800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>411600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>595500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>204000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>256900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>502300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>772200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>319700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>332100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>548000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>814800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>337500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>357700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>603400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>1242600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>355700</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>342800</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>521600</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AI8" s="3">
         <v>770700</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>216200</v>
+      </c>
+      <c r="E9" s="3">
+        <v>166100</v>
+      </c>
+      <c r="F9" s="3">
         <v>356600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>474100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>213500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>178300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>341000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>470500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>198700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>331900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>315800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>662200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>180800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>186900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>341000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>480200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>173200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>191500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>383800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>585300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>248000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>214700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>799300</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>1173000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>270900</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>228200</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>456900</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>961300</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>291000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>218600</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>405700</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AI9" s="3">
         <v>599200</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>47200</v>
+      </c>
+      <c r="E10" s="3">
+        <v>69800</v>
+      </c>
+      <c r="F10" s="3">
         <v>100100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>136300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>50700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>36900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>97100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>138100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>56000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>-106700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>87000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>205600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>60000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>35900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>70600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>115300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>30800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>65400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>118500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>186900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>71700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>117400</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>-251300</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>-358200</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>66600</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>129500</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>146500</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>281300</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>64700</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>124200</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>115900</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AI10" s="3">
         <v>171500</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1114,8 +1139,10 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1209,8 +1236,14 @@
       <c r="AG12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1304,198 +1337,216 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>58900</v>
+      </c>
+      <c r="E14" s="3">
+        <v>8500</v>
+      </c>
+      <c r="F14" s="3">
         <v>9200</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>4300</v>
       </c>
-      <c r="F14" s="3">
+      <c r="H14" s="3">
         <v>4600</v>
       </c>
-      <c r="G14" s="3">
+      <c r="I14" s="3">
         <v>3500</v>
       </c>
-      <c r="H14" s="3">
+      <c r="J14" s="3">
         <v>10100</v>
       </c>
-      <c r="I14" s="3">
+      <c r="K14" s="3">
         <v>300</v>
       </c>
-      <c r="J14" s="3">
+      <c r="L14" s="3">
         <v>400</v>
       </c>
-      <c r="K14" s="3">
+      <c r="M14" s="3">
         <v>-2800</v>
       </c>
-      <c r="L14" s="3">
+      <c r="N14" s="3">
         <v>6500</v>
       </c>
-      <c r="M14" s="3">
+      <c r="O14" s="3">
         <v>3000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="P14" s="3">
         <v>1900</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>29300</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="S14" s="3">
         <v>3400</v>
       </c>
-      <c r="R14" s="3">
+      <c r="T14" s="3">
         <v>5700</v>
       </c>
-      <c r="S14" s="3">
+      <c r="U14" s="3">
         <v>15300</v>
       </c>
-      <c r="T14" s="3">
+      <c r="V14" s="3">
         <v>200</v>
       </c>
-      <c r="U14" s="3">
+      <c r="W14" s="3">
         <v>1600</v>
       </c>
-      <c r="V14" s="3">
+      <c r="X14" s="3">
         <v>1900</v>
       </c>
-      <c r="W14" s="3">
+      <c r="Y14" s="3">
         <v>62500</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Z14" s="3">
         <v>2600</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="AA14" s="3">
         <v>500</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="3">
         <v>200</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AD14" s="3">
         <v>313200</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AE14" s="3">
         <v>7300</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AF14" s="3">
         <v>5800</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AG14" s="3">
         <v>7000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AH14" s="3">
         <v>500</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AI14" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>13100</v>
+      </c>
+      <c r="E15" s="3">
+        <v>10000</v>
+      </c>
+      <c r="F15" s="3">
         <v>10100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>10200</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
         <v>10300</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>8300</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>10100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>10300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>10900</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>5400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>12200</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>24600</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>12600</v>
       </c>
-      <c r="O15" s="3">
+      <c r="Q15" s="3">
         <v>12400</v>
       </c>
-      <c r="P15" s="3">
+      <c r="R15" s="3">
         <v>13300</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="S15" s="3">
         <v>13200</v>
       </c>
-      <c r="R15" s="3">
+      <c r="T15" s="3">
         <v>14100</v>
       </c>
-      <c r="S15" s="3">
+      <c r="U15" s="3">
         <v>15300</v>
       </c>
-      <c r="T15" s="3">
+      <c r="V15" s="3">
         <v>15100</v>
       </c>
-      <c r="U15" s="3">
+      <c r="W15" s="3">
         <v>15500</v>
       </c>
-      <c r="V15" s="3">
+      <c r="X15" s="3">
         <v>15900</v>
       </c>
-      <c r="W15" s="3">
+      <c r="Y15" s="3">
         <v>16500</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Z15" s="3">
         <v>16400</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="AA15" s="3">
         <v>16400</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AB15" s="3">
         <v>16500</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AC15" s="3">
         <v>16900</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AD15" s="3">
         <v>17000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AE15" s="3">
         <v>31700</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AF15" s="3">
         <v>15000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AG15" s="3">
         <v>14300</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AH15" s="3">
         <v>13100</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AI15" s="3">
         <v>13000</v>
       </c>
     </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1526,198 +1577,212 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>355200</v>
+      </c>
+      <c r="E17" s="3">
+        <v>252900</v>
+      </c>
+      <c r="F17" s="3">
         <v>455800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>574500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>305900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>242600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>453100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>580000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>300300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>235800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>435900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>883900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>281500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>282800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>476300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>588800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>262900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>309300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>505300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>715800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>363500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>392100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>545000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>736300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>386600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>352400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>899000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>1214900</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>411300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>338500</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>516400</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AI17" s="3">
         <v>713900</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-91800</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-17000</v>
+      </c>
+      <c r="F18" s="3">
         <v>900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>35900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-41700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-27400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-15000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>28600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-45600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-10600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-33100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-16100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-40700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-60000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-64700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>6700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-58900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-52400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-3000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>56400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>-43800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>-60000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>3000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>78500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>-49100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>5300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>-295600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>27700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>-55600</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>4300</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>5200</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AI18" s="3">
         <v>56800</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1751,16 +1816,18 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E20" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="F20" s="3">
         <v>0</v>
@@ -1769,14 +1836,14 @@
         <v>0</v>
       </c>
       <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
         <v>6900</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
       <c r="K20" s="3">
         <v>0</v>
       </c>
@@ -1846,388 +1913,418 @@
       <c r="AG20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-78600</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="F21" s="3">
         <v>11100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>46000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-31500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-16500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>2000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>35700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-31500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-8800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-19600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>11000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-26800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>-46300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>-50100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>21100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>-43700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>-36000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>13200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>73000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>-27000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>-42500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>19200</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>95000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>-32500</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>22100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>-278600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>59400</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>-40500</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>18600</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>18300</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AI21" s="3">
         <v>69700</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>7700</v>
+      </c>
+      <c r="E22" s="3">
+        <v>11800</v>
+      </c>
+      <c r="F22" s="3">
         <v>10600</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>10700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>8300</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>7000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>13800</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>4900</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>3900</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>2300</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>3100</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>4800</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>2500</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>2200</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>2300</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>900</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>2700</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>1600</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>1900</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>1400</v>
-      </c>
-      <c r="V22" s="3">
-        <v>2500</v>
-      </c>
-      <c r="W22" s="3">
-        <v>1900</v>
       </c>
       <c r="X22" s="3">
         <v>2500</v>
       </c>
       <c r="Y22" s="3">
+        <v>1900</v>
+      </c>
+      <c r="Z22" s="3">
+        <v>2500</v>
+      </c>
+      <c r="AA22" s="3">
         <v>1800</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AB22" s="3">
         <v>3500</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AC22" s="3">
         <v>2500</v>
-      </c>
-      <c r="AB22" s="3">
-        <v>3000</v>
-      </c>
-      <c r="AC22" s="3">
-        <v>4900</v>
       </c>
       <c r="AD22" s="3">
         <v>3000</v>
       </c>
       <c r="AE22" s="3">
+        <v>4900</v>
+      </c>
+      <c r="AF22" s="3">
+        <v>3000</v>
+      </c>
+      <c r="AG22" s="3">
         <v>1500</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AH22" s="3">
         <v>700</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AI22" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-99300</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-27800</v>
+      </c>
+      <c r="F23" s="3">
         <v>-9700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>25200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-50000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-34400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-22000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>23800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-49500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-12900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-36200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-20900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-43200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-62200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-67000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>5800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-61600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-54000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-4900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>55000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-46300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>-62000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>76600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>-52600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>2700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>-298600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>22800</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>-58600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>2900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>4500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AI23" s="3">
         <v>56100</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>100</v>
+      </c>
+      <c r="E24" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F24" s="3">
         <v>200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>300</v>
       </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3">
         <v>100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>-400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>-10000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>-9800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>-18700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>-1700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>-14900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>-13700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>-3200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>19100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>-14200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>-15700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>-300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>16900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>-14000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>-15000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>5800</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>9200</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>-23800</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>2600</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AH24" s="3">
         <v>800</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AI24" s="3">
         <v>26800</v>
       </c>
     </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2321,198 +2418,216 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-99500</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-27400</v>
+      </c>
+      <c r="F26" s="3">
         <v>-9900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>24900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-50000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-34500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-22100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>24200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-50300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-2900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-36800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-21100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-43600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-52400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-48300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>7500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-46700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-40300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-1700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>35900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-32200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>-46200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>59700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>-38600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>17800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>-304400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>13600</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>-34800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>3800</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AI26" s="3">
         <v>29300</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-99500</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-27400</v>
+      </c>
+      <c r="F27" s="3">
         <v>-9900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>24900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-50000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-34500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-22100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>24200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-50300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-2900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-36800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-21100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-43600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-52400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-48300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>7500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-46700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-40300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-1700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>35900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-32100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>-46200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>59700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>-38600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>17800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>-304400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>13600</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>-34800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>200</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>3800</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AI27" s="3">
         <v>29300</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2606,47 +2721,53 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>100</v>
+      </c>
+      <c r="F29" s="3">
         <v>300</v>
       </c>
-      <c r="E29" s="3">
+      <c r="G29" s="3">
         <v>-700</v>
       </c>
-      <c r="F29" s="3">
+      <c r="H29" s="3">
         <v>-400</v>
       </c>
-      <c r="G29" s="3">
+      <c r="I29" s="3">
         <v>-11700</v>
       </c>
-      <c r="H29" s="3">
+      <c r="J29" s="3">
         <v>-2900</v>
       </c>
-      <c r="I29" s="3">
+      <c r="K29" s="3">
         <v>-2000</v>
       </c>
-      <c r="J29" s="3">
+      <c r="L29" s="3">
         <v>-2400</v>
       </c>
-      <c r="K29" s="3">
+      <c r="M29" s="3">
         <v>-7300</v>
       </c>
-      <c r="L29" s="3" t="s">
+      <c r="N29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M29" s="3" t="s">
+      <c r="O29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N29" s="3">
-        <v>0</v>
-      </c>
-      <c r="O29" s="3">
-        <v>0</v>
-      </c>
       <c r="P29" s="3">
         <v>0</v>
       </c>
@@ -2662,11 +2783,11 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V29" s="3" t="s">
-        <v>8</v>
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+      <c r="V29" s="3">
+        <v>0</v>
       </c>
       <c r="W29" s="3" t="s">
         <v>8</v>
@@ -2680,20 +2801,20 @@
       <c r="Z29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AA29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC29" s="3">
         <v>-700</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AD29" s="3">
         <v>21100</v>
       </c>
-      <c r="AC29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE29" s="3" t="s">
-        <v>8</v>
+      <c r="AE29" s="3">
+        <v>0</v>
       </c>
       <c r="AF29" s="3" t="s">
         <v>8</v>
@@ -2701,8 +2822,14 @@
       <c r="AG29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2796,8 +2923,14 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2891,16 +3024,22 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E32" s="3">
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="F32" s="3">
         <v>0</v>
@@ -2909,14 +3048,14 @@
         <v>0</v>
       </c>
       <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
         <v>-6900</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
       <c r="K32" s="3">
         <v>0</v>
       </c>
@@ -2986,103 +3125,115 @@
       <c r="AG32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-99500</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-27400</v>
+      </c>
+      <c r="F33" s="3">
         <v>-9600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>24200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-50400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-46300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-25000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>22100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-52700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-10200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-36800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-21100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-43600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-52400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-48300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>7500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-46700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-40300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-1700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>35900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-32100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-46200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>59700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>-38600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>17100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>-283200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>13600</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>-34800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>200</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>3800</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AI33" s="3">
         <v>29300</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3176,203 +3327,221 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-99500</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-27400</v>
+      </c>
+      <c r="F35" s="3">
         <v>-9600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>24200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-50400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-46300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-25000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>22100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-52700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-10200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-36800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-21100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-43600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-52400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-48300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>7500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-46700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-40300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-1700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>35900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-32100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-46200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>59700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>-38600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>17100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>-283200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>13600</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>-34800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>200</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>3800</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AI35" s="3">
         <v>29300</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45500</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45409</v>
+      </c>
+      <c r="F38" s="2">
         <v>45318</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45227</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45136</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45045</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44954</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44863</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44772</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44681</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44590</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44499</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44408</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44317</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44226</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44135</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44044</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43953</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43855</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43764</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43673</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43582</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43491</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43400</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43309</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43218</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43127</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43036</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>42945</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>42854</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>42763</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3406,8 +3575,10 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3441,103 +3612,111 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E41" s="3">
+        <v>10500</v>
+      </c>
+      <c r="F41" s="3">
         <v>8100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>15000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>7700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>14200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>9400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>17300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>7600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>8800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>10000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>11000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>7600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>8000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>9900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>7400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>7500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>8200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>9800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>24600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>8200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>14000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>22000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>20000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>13300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>16100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>22400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>17500</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>14200</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>19000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>132100</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AI41" s="3">
         <v>176600</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3631,388 +3810,418 @@
       <c r="AG42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>154400</v>
+      </c>
+      <c r="E43" s="3">
+        <v>104100</v>
+      </c>
+      <c r="F43" s="3">
         <v>315100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>221800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>140900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>92500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>276900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>209300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>119000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>136000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>250200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>218100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>118300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>121100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>227200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>167500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>107500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>90900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>238000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>162500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>98500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>98200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>231100</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>138000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>99800</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>100100</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>243400</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>153600</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>112500</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>86000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AH43" s="3">
         <v>178800</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AI43" s="3">
         <v>93300</v>
       </c>
     </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>405600</v>
+      </c>
+      <c r="E44" s="3">
+        <v>377000</v>
+      </c>
+      <c r="F44" s="3">
         <v>386100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>416100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>391000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>353300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>444400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>420900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>472100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>323500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>444600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>421200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>479100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>309800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>493300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>508400</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>591700</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>469600</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>578700</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>543600</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>723000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>467300</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>630200</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>576500</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>736100</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>493900</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>675900</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>593600</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AF44" s="3">
         <v>787300</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AG44" s="3">
         <v>486900</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AH44" s="3">
         <v>561400</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AI44" s="3">
         <v>488000</v>
       </c>
     </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>33200</v>
+      </c>
+      <c r="E45" s="3">
+        <v>39200</v>
+      </c>
+      <c r="F45" s="3">
         <v>54300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>63400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>59000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>76900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>140000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>137000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>147800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>63400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>60600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>69000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>64700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>61900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>25300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>23800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>22400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>16200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>24600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>18500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>18100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>11800</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>20700</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>16600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>18700</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>9200</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>12300</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>13400</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>13500</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>10700</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AH45" s="3">
         <v>8100</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AI45" s="3">
         <v>8100</v>
       </c>
     </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>601400</v>
+      </c>
+      <c r="E46" s="3">
+        <v>530800</v>
+      </c>
+      <c r="F46" s="3">
         <v>763700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>716400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>598600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>537000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>813700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>729600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>686200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>531700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>765400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>719200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>669700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>500800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>755700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>707000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>729100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>584900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>851200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>749200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>847800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>591400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>904000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>751200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>867900</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>619400</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>954000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>778100</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>927500</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>602600</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>880400</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AI46" s="3">
         <v>766000</v>
       </c>
     </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4106,198 +4315,216 @@
       <c r="AG47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>290100</v>
+      </c>
+      <c r="E48" s="3">
+        <v>255400</v>
+      </c>
+      <c r="F48" s="3">
         <v>277500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>307900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>347500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>315100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>331500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>367200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>391800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>360200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>323000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>344500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>380200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>329600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>330300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>379200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>414400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>348600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>352800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>394900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>420300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>109800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>109400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>112000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>108100</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>111300</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>111000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>115300</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>112800</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>116600</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AH48" s="3">
         <v>107300</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AI48" s="3">
         <v>108500</v>
       </c>
     </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>87800</v>
+      </c>
+      <c r="E49" s="3">
+        <v>94200</v>
+      </c>
+      <c r="F49" s="3">
         <v>97900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>104000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>107400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>110600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>119000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>125200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>128000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>131700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>138700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>146500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>150700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>155600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>160200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>170800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>175200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>179800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>184300</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>188900</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>193900</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>199700</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>262400</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>267900</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>263200</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>268400</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>273600</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>591900</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AF49" s="3">
         <v>535800</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AG49" s="3">
         <v>539400</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AH49" s="3">
         <v>473000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AI49" s="3">
         <v>475900</v>
       </c>
     </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4391,8 +4618,14 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4486,103 +4719,115 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>25900</v>
+      </c>
+      <c r="E52" s="3">
+        <v>24700</v>
+      </c>
+      <c r="F52" s="3">
         <v>12500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>16700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>17300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>18000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>39600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>42100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>44600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>52700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>39700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>42000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>43300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>45000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>42200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>40000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>42100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>43100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>39800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>47300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>40500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>45400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>40200</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>41600</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>41700</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>40100</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>42000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>41900</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>42500</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>41200</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AH52" s="3">
         <v>39200</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AI52" s="3">
         <v>38200</v>
       </c>
     </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4676,103 +4921,115 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1005200</v>
+      </c>
+      <c r="E54" s="3">
+        <v>905100</v>
+      </c>
+      <c r="F54" s="3">
         <v>1151600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>1145000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>1070800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>980800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>1279400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>1238400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>1223600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>1071600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>1266700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>1252200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>1244000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>1031100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>1288500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>1297000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>1360800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>1156400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>1428100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>1380300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>1502400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>946200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>1316100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>1172700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>1280900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>1039200</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>1380600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>1527200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>1618700</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>1299800</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>1499900</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AI54" s="3">
         <v>1388600</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4806,8 +5063,10 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4841,117 +5100,125 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>266300</v>
+      </c>
+      <c r="E57" s="3">
+        <v>299200</v>
+      </c>
+      <c r="F57" s="3">
         <v>343100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>385900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>275400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>267900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>355200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>326000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>324400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>182600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>359700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>333100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>331100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>137600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>318800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>314000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>291500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>143700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>389100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>387700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>443100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>186800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>464900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>443300</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>463700</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>187900</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>489000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>458800</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>511500</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>192700</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>480400</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AI57" s="3">
         <v>439700</v>
       </c>
     </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3">
-        <v>224100</v>
+      <c r="D58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>8</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
-      </c>
-      <c r="G58" s="3">
-        <v>0</v>
+        <v>224100</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H58" s="3">
         <v>0</v>
@@ -4960,459 +5227,489 @@
         <v>0</v>
       </c>
       <c r="J58" s="3">
+        <v>0</v>
+      </c>
+      <c r="K58" s="3">
+        <v>0</v>
+      </c>
+      <c r="L58" s="3">
         <v>40000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>40000</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
       <c r="N58" s="3">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3">
         <v>50000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>50000</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
       <c r="R58" s="3">
         <v>0</v>
       </c>
       <c r="S58" s="3">
+        <v>0</v>
+      </c>
+      <c r="T58" s="3">
+        <v>0</v>
+      </c>
+      <c r="U58" s="3">
         <v>75000</v>
       </c>
-      <c r="T58" s="3">
-        <v>0</v>
-      </c>
-      <c r="U58" s="3">
-        <v>0</v>
-      </c>
       <c r="V58" s="3">
+        <v>0</v>
+      </c>
+      <c r="W58" s="3">
+        <v>0</v>
+      </c>
+      <c r="X58" s="3">
         <v>100000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>100000</v>
       </c>
-      <c r="X58" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y58" s="3">
-        <v>0</v>
-      </c>
       <c r="Z58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB58" s="3">
         <v>100000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>100000</v>
       </c>
-      <c r="AB58" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC58" s="3">
-        <v>0</v>
-      </c>
       <c r="AD58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF58" s="3">
         <v>100000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AG58" s="3">
         <v>100000</v>
       </c>
-      <c r="AF58" s="3" t="s">
+      <c r="AH58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG58" s="3" t="s">
+      <c r="AI58" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>223600</v>
+      </c>
+      <c r="E59" s="3">
+        <v>179600</v>
+      </c>
+      <c r="F59" s="3">
         <v>282400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>238500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>240700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>194200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>392600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>368400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>244100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>192800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>402300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>363900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>228000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>186100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>231400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>255700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>206600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>188000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>296000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>304900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>187000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>121700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>219700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>170000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>93200</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>125600</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>252200</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>184300</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>89900</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>120500</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>207700</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AI59" s="3">
         <v>140800</v>
       </c>
     </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>489900</v>
+      </c>
+      <c r="E60" s="3">
+        <v>478800</v>
+      </c>
+      <c r="F60" s="3">
         <v>849600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>624400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>516100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>462100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>609600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>575700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>608400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>415400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>611300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>574300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>609100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>373700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>550200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>569700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>498100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>406700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>685000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>692600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>730200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>408500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>684600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>613400</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>657000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>413500</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>741200</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>643100</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>701400</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>413200</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>688100</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AI60" s="3">
         <v>580500</v>
       </c>
     </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>221900</v>
+      </c>
+      <c r="E61" s="3">
+        <v>196300</v>
+      </c>
+      <c r="F61" s="3">
         <v>30200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>233900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>277700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>182200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>283900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>250400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>218600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>185700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>200400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>183300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>153700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>127600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>150800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>99500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>234600</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>99700</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>65900</v>
       </c>
-      <c r="U61" s="3">
-        <v>0</v>
-      </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+      <c r="X61" s="3">
         <v>74100</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>33500</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>70100</v>
       </c>
-      <c r="Y61" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB61" s="3">
         <v>130200</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>96400</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>113000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>41800</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AF61" s="3">
         <v>120100</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AG61" s="3">
         <v>59600</v>
       </c>
-      <c r="AF61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG61" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>149100</v>
+      </c>
+      <c r="E62" s="3">
+        <v>159400</v>
+      </c>
+      <c r="F62" s="3">
         <v>174700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>180700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>196000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>205800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>228800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>231500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>219800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>242100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>266300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>273600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>257300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>262100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>243300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>247300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>255900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>232300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>219800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>230300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>277400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>53500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>66600</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>67300</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>62000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>61400</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>77700</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>112500</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>116200</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>113300</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AH62" s="3">
         <v>98900</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AI62" s="3">
         <v>101700</v>
       </c>
     </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5506,8 +5803,14 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5601,8 +5904,14 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5696,103 +6005,115 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>860800</v>
+      </c>
+      <c r="E66" s="3">
+        <v>834500</v>
+      </c>
+      <c r="F66" s="3">
         <v>1054500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>1039000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>989800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>850000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>1102900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>1037900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>1046800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>843200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>1029300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>980000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>994700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>738100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>944300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>916600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>988500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>738700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>970700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>922900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>1081700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>495600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>821400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>680700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>849200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>571200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>931900</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>797400</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>937800</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>586100</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>787000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AI66" s="3">
         <v>682200</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5826,8 +6147,10 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5921,8 +6244,14 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6016,8 +6345,14 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6111,8 +6446,14 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6206,103 +6547,115 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-756000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-656600</v>
+      </c>
+      <c r="F72" s="3">
         <v>-629200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-619600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-643700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-593400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-547100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-522100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-544200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-491500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-480500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-443700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-466300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-422600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-370300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-322000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-329500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-282800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-242500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-240800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-276700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-244600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>-198400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>-199100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>-258800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>-220200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>-237300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>46000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>-2400</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>32400</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>32100</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AI72" s="3">
         <v>28400</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6396,8 +6749,14 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6491,8 +6850,14 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6586,103 +6951,115 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>144400</v>
+      </c>
+      <c r="E76" s="3">
+        <v>70600</v>
+      </c>
+      <c r="F76" s="3">
         <v>97100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>106000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>81100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>130800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>176500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>200500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>176800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>228400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>237500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>272200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>249300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>293000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>344200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>380400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>372300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>417800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>457400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>457300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>420800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>450600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>494700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>492000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>431700</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>468000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>448700</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>729800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>680900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>713700</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>712900</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AI76" s="3">
         <v>706400</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6776,203 +7153,221 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45500</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45409</v>
+      </c>
+      <c r="F80" s="2">
         <v>45318</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45227</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45136</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45045</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44954</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44863</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44772</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44681</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44590</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44499</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44408</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44317</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44226</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44135</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44044</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43953</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43855</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43764</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43673</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43582</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43491</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43400</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43309</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43218</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43127</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43036</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>42945</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>42854</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>42763</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-99500</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-27400</v>
+      </c>
+      <c r="F81" s="3">
         <v>-9600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>24200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-50400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-46300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-25000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>22100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-52700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-10200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-36800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-21100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-43600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-52400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-48300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>7500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-46700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-40300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-1700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>35900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-32100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-46200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>59700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>-38600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>17100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>-283200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>13600</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>-34800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>200</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>3800</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AI81" s="3">
         <v>29300</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7006,103 +7401,111 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>13100</v>
+      </c>
+      <c r="E83" s="3">
+        <v>10000</v>
+      </c>
+      <c r="F83" s="3">
         <v>10100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>10200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>10300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>3400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>12300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>12400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>14100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>14100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>13600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>27200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>13900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>13700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>14600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>14400</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>15200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>16400</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>16200</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>16500</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>16800</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>17600</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>16200</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>16600</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>16500</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>16900</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AD83" s="3">
         <v>17000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AE83" s="3">
         <v>31700</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AF83" s="3">
         <v>15000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AG83" s="3">
         <v>14300</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AH83" s="3">
         <v>13100</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AI83" s="3">
         <v>13000</v>
       </c>
     </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7196,8 +7599,14 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7291,8 +7700,14 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7386,8 +7801,14 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7481,8 +7902,14 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7576,103 +8003,115 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-144000</v>
+      </c>
+      <c r="E89" s="3">
+        <v>81700</v>
+      </c>
+      <c r="F89" s="3">
         <v>-35800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>72000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-123100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>114300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-32000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>38400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-29000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-5800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-16400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>24300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-17300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-8700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-49800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>144500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-53100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-100700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>-69400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>201700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>-40200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>-55000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>-60700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>263900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>-27400</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>-81400</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>-58200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>199600</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>-56000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>-77000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>-34300</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AI89" s="3">
         <v>204500</v>
       </c>
     </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7706,103 +8145,111 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="F91" s="3">
         <v>-3300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-4000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-4200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-3400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-4900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-7100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-9700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-12100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-9900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-11400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-11300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-9700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-9100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-7100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-9400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-7600</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-10900</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-8300</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-14700</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-8600</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-14900</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-8200</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-12700</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-7700</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-22400</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AF91" s="3">
         <v>-7900</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AG91" s="3">
         <v>-8200</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AH91" s="3">
         <v>-9000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AI91" s="3">
         <v>-11300</v>
       </c>
     </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7896,8 +8343,14 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7991,103 +8444,115 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="F94" s="3">
         <v>-3300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-4000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>17300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-4700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-6000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-10600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-9700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-10000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-11900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-20800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-11000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-11300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-12600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-7500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-5500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-7900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-5600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-10000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-6100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-13000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-7400</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-25000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-9300</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-11300</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-7500</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-81300</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>-9100</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>-190800</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AH94" s="3">
         <v>-10200</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AI94" s="3">
         <v>-10600</v>
       </c>
     </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8121,8 +8586,10 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8216,8 +8683,14 @@
       <c r="AG96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8311,8 +8784,14 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8406,8 +8885,14 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8501,103 +8986,115 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>139900</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-65600</v>
+      </c>
+      <c r="F100" s="3">
         <v>18700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-52000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>93200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-106100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>32700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-9700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>33400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>25000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>17300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>3400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>24900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>25700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>62200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-135600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>59500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>108800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>65900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-175300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>40600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>60000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>70100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>-232200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>33800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>83400</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>71200</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>-119400</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>60500</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>155100</v>
       </c>
-      <c r="AF100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI100" s="3">
         <v>-26300</v>
       </c>
     </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8691,99 +9188,111 @@
       <c r="AG101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-7300</v>
+      </c>
+      <c r="E102" s="3">
+        <v>13500</v>
+      </c>
+      <c r="F102" s="3">
         <v>-20300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>16000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-12700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>3400</v>
-      </c>
-      <c r="H102" s="3">
-        <v>-5300</v>
-      </c>
-      <c r="I102" s="3">
-        <v>18100</v>
       </c>
       <c r="J102" s="3">
         <v>-5300</v>
       </c>
       <c r="K102" s="3">
+        <v>18100</v>
+      </c>
+      <c r="L102" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="M102" s="3">
         <v>9200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-10800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>6700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-3600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>6100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>2600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-1600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-14800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>16400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-5800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-8000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>2000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>6800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-2900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>-8200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>4900</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>-1500</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>-4800</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>-112700</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>-44500</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AI102" s="3">
         <v>167700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BNED_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BNED_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="92">
   <si>
     <t>BNED</t>
   </si>
@@ -822,7 +822,7 @@
         <v>264200</v>
       </c>
       <c r="I8" s="3">
-        <v>215200</v>
+        <v>241800</v>
       </c>
       <c r="J8" s="3">
         <v>438100</v>
@@ -923,7 +923,7 @@
         <v>213500</v>
       </c>
       <c r="I9" s="3">
-        <v>178300</v>
+        <v>183600</v>
       </c>
       <c r="J9" s="3">
         <v>341000</v>
@@ -1012,22 +1012,22 @@
         <v>47200</v>
       </c>
       <c r="E10" s="3">
-        <v>69800</v>
+        <v>69900</v>
       </c>
       <c r="F10" s="3">
-        <v>100100</v>
+        <v>100000</v>
       </c>
       <c r="G10" s="3">
-        <v>136300</v>
+        <v>136200</v>
       </c>
       <c r="H10" s="3">
-        <v>50700</v>
+        <v>50600</v>
       </c>
       <c r="I10" s="3">
-        <v>36900</v>
+        <v>58300</v>
       </c>
       <c r="J10" s="3">
-        <v>97100</v>
+        <v>97000</v>
       </c>
       <c r="K10" s="3">
         <v>138100</v>
@@ -1352,7 +1352,7 @@
         <v>58900</v>
       </c>
       <c r="E14" s="3">
-        <v>8500</v>
+        <v>9800</v>
       </c>
       <c r="F14" s="3">
         <v>9200</v>
@@ -1364,7 +1364,7 @@
         <v>4600</v>
       </c>
       <c r="I14" s="3">
-        <v>3500</v>
+        <v>5300</v>
       </c>
       <c r="J14" s="3">
         <v>10100</v>
@@ -1465,7 +1465,7 @@
         <v>10300</v>
       </c>
       <c r="I15" s="3">
-        <v>8300</v>
+        <v>10900</v>
       </c>
       <c r="J15" s="3">
         <v>10100</v>
@@ -1585,25 +1585,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>355200</v>
+        <v>296300</v>
       </c>
       <c r="E17" s="3">
-        <v>252900</v>
+        <v>243100</v>
       </c>
       <c r="F17" s="3">
-        <v>455800</v>
+        <v>446500</v>
       </c>
       <c r="G17" s="3">
-        <v>574500</v>
+        <v>570300</v>
       </c>
       <c r="H17" s="3">
-        <v>305900</v>
+        <v>301300</v>
       </c>
       <c r="I17" s="3">
-        <v>242600</v>
+        <v>270900</v>
       </c>
       <c r="J17" s="3">
-        <v>453100</v>
+        <v>443000</v>
       </c>
       <c r="K17" s="3">
         <v>580000</v>
@@ -1686,25 +1686,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-91800</v>
+        <v>-32900</v>
       </c>
       <c r="E18" s="3">
-        <v>-17000</v>
+        <v>-7200</v>
       </c>
       <c r="F18" s="3">
-        <v>900</v>
+        <v>10100</v>
       </c>
       <c r="G18" s="3">
-        <v>35900</v>
+        <v>40100</v>
       </c>
       <c r="H18" s="3">
-        <v>-41700</v>
+        <v>-37100</v>
       </c>
       <c r="I18" s="3">
-        <v>-27400</v>
+        <v>-29100</v>
       </c>
       <c r="J18" s="3">
-        <v>-15000</v>
+        <v>-4900</v>
       </c>
       <c r="K18" s="3">
         <v>28600</v>
@@ -1823,26 +1823,26 @@
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>100</v>
-      </c>
-      <c r="E20" s="3">
-        <v>1000</v>
-      </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3">
-        <v>6900</v>
+      <c r="D20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
@@ -1925,25 +1925,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-78600</v>
+        <v>-19800</v>
       </c>
       <c r="E21" s="3">
-        <v>-6000</v>
+        <v>2800</v>
       </c>
       <c r="F21" s="3">
-        <v>11100</v>
+        <v>20300</v>
       </c>
       <c r="G21" s="3">
-        <v>46000</v>
+        <v>50300</v>
       </c>
       <c r="H21" s="3">
-        <v>-31500</v>
+        <v>-26800</v>
       </c>
       <c r="I21" s="3">
-        <v>-16500</v>
+        <v>-18200</v>
       </c>
       <c r="J21" s="3">
-        <v>2000</v>
+        <v>5200</v>
       </c>
       <c r="K21" s="3">
         <v>35700</v>
@@ -2029,7 +2029,7 @@
         <v>7700</v>
       </c>
       <c r="E22" s="3">
-        <v>11800</v>
+        <v>12000</v>
       </c>
       <c r="F22" s="3">
         <v>10600</v>
@@ -2041,10 +2041,10 @@
         <v>8300</v>
       </c>
       <c r="I22" s="3">
-        <v>7000</v>
+        <v>7500</v>
       </c>
       <c r="J22" s="3">
-        <v>13800</v>
+        <v>6900</v>
       </c>
       <c r="K22" s="3">
         <v>4900</v>
@@ -2142,7 +2142,7 @@
         <v>-50000</v>
       </c>
       <c r="I23" s="3">
-        <v>-34400</v>
+        <v>-41400</v>
       </c>
       <c r="J23" s="3">
         <v>-22000</v>
@@ -2243,7 +2243,7 @@
         <v>0</v>
       </c>
       <c r="I24" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="J24" s="3">
         <v>100</v>
@@ -2445,7 +2445,7 @@
         <v>-50000</v>
       </c>
       <c r="I26" s="3">
-        <v>-34500</v>
+        <v>-41900</v>
       </c>
       <c r="J26" s="3">
         <v>-22100</v>
@@ -2537,19 +2537,19 @@
         <v>-27400</v>
       </c>
       <c r="F27" s="3">
-        <v>-9900</v>
+        <v>-9600</v>
       </c>
       <c r="G27" s="3">
-        <v>24900</v>
+        <v>24200</v>
       </c>
       <c r="H27" s="3">
-        <v>-50000</v>
+        <v>-50400</v>
       </c>
       <c r="I27" s="3">
-        <v>-34500</v>
+        <v>-46300</v>
       </c>
       <c r="J27" s="3">
-        <v>-22100</v>
+        <v>-25000</v>
       </c>
       <c r="K27" s="3">
         <v>24200</v>
@@ -2748,7 +2748,7 @@
         <v>-400</v>
       </c>
       <c r="I29" s="3">
-        <v>-11700</v>
+        <v>-4400</v>
       </c>
       <c r="J29" s="3">
         <v>-2900</v>
@@ -3035,26 +3035,26 @@
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="E32" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3">
-        <v>-6900</v>
+      <c r="D32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K32" s="3">
         <v>0</v>
@@ -3638,7 +3638,7 @@
         <v>14200</v>
       </c>
       <c r="J41" s="3">
-        <v>9400</v>
+        <v>11100</v>
       </c>
       <c r="K41" s="3">
         <v>17300</v>
@@ -3822,10 +3822,10 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>154400</v>
+        <v>162900</v>
       </c>
       <c r="E43" s="3">
-        <v>104100</v>
+        <v>118600</v>
       </c>
       <c r="F43" s="3">
         <v>315100</v>
@@ -3834,13 +3834,13 @@
         <v>221800</v>
       </c>
       <c r="H43" s="3">
-        <v>140900</v>
+        <v>150900</v>
       </c>
       <c r="I43" s="3">
-        <v>92500</v>
+        <v>98700</v>
       </c>
       <c r="J43" s="3">
-        <v>276900</v>
+        <v>277500</v>
       </c>
       <c r="K43" s="3">
         <v>209300</v>
@@ -4023,26 +4023,26 @@
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>33200</v>
+      <c r="D45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E45" s="3">
-        <v>39200</v>
+        <v>1300</v>
       </c>
       <c r="F45" s="3">
-        <v>54300</v>
-      </c>
-      <c r="G45" s="3">
-        <v>63400</v>
-      </c>
-      <c r="H45" s="3">
-        <v>59000</v>
+        <v>14600</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I45" s="3">
-        <v>76900</v>
-      </c>
-      <c r="J45" s="3">
-        <v>140000</v>
+        <v>33600</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K45" s="3">
         <v>137000</v>
@@ -4143,7 +4143,7 @@
         <v>537000</v>
       </c>
       <c r="J46" s="3">
-        <v>813700</v>
+        <v>790100</v>
       </c>
       <c r="K46" s="3">
         <v>729600</v>
@@ -4225,26 +4225,26 @@
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -4345,7 +4345,7 @@
         <v>315100</v>
       </c>
       <c r="J48" s="3">
-        <v>331500</v>
+        <v>351700</v>
       </c>
       <c r="K48" s="3">
         <v>367200</v>
@@ -4446,7 +4446,7 @@
         <v>110600</v>
       </c>
       <c r="J49" s="3">
-        <v>119000</v>
+        <v>119600</v>
       </c>
       <c r="K49" s="3">
         <v>125200</v>
@@ -4731,10 +4731,10 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>25900</v>
+        <v>11600</v>
       </c>
       <c r="E52" s="3">
-        <v>24700</v>
+        <v>11800</v>
       </c>
       <c r="F52" s="3">
         <v>12500</v>
@@ -4746,10 +4746,10 @@
         <v>17300</v>
       </c>
       <c r="I52" s="3">
-        <v>18000</v>
+        <v>16600</v>
       </c>
       <c r="J52" s="3">
-        <v>39600</v>
+        <v>19700</v>
       </c>
       <c r="K52" s="3">
         <v>42100</v>
@@ -4951,7 +4951,7 @@
         <v>980800</v>
       </c>
       <c r="J54" s="3">
-        <v>1279400</v>
+        <v>1281100</v>
       </c>
       <c r="K54" s="3">
         <v>1238400</v>
@@ -5126,7 +5126,7 @@
         <v>267900</v>
       </c>
       <c r="J57" s="3">
-        <v>355200</v>
+        <v>355300</v>
       </c>
       <c r="K57" s="3">
         <v>326000</v>
@@ -5208,26 +5208,26 @@
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>8</v>
+      <c r="D58" s="3">
+        <v>147800</v>
+      </c>
+      <c r="E58" s="3">
+        <v>102200</v>
       </c>
       <c r="F58" s="3">
-        <v>224100</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>8</v>
+        <v>349600</v>
+      </c>
+      <c r="G58" s="3">
+        <v>126400</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>150900</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>116100</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -5310,25 +5310,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>223600</v>
+        <v>12000</v>
       </c>
       <c r="E59" s="3">
-        <v>179600</v>
+        <v>11300</v>
       </c>
       <c r="F59" s="3">
-        <v>282400</v>
+        <v>50000</v>
       </c>
       <c r="G59" s="3">
-        <v>238500</v>
+        <v>40400</v>
       </c>
       <c r="H59" s="3">
-        <v>240700</v>
+        <v>12800</v>
       </c>
       <c r="I59" s="3">
-        <v>194200</v>
+        <v>21400</v>
       </c>
       <c r="J59" s="3">
-        <v>392600</v>
+        <v>53700</v>
       </c>
       <c r="K59" s="3">
         <v>368400</v>
@@ -5512,25 +5512,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>221900</v>
+        <v>354100</v>
       </c>
       <c r="E61" s="3">
-        <v>196300</v>
+        <v>338500</v>
       </c>
       <c r="F61" s="3">
-        <v>30200</v>
+        <v>185400</v>
       </c>
       <c r="G61" s="3">
-        <v>233900</v>
+        <v>394100</v>
       </c>
       <c r="H61" s="3">
-        <v>277700</v>
+        <v>448800</v>
       </c>
       <c r="I61" s="3">
-        <v>182200</v>
+        <v>366900</v>
       </c>
       <c r="J61" s="3">
-        <v>283900</v>
+        <v>474100</v>
       </c>
       <c r="K61" s="3">
         <v>250400</v>
@@ -5613,25 +5613,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>149100</v>
+        <v>12200</v>
       </c>
       <c r="E62" s="3">
-        <v>159400</v>
+        <v>12300</v>
       </c>
       <c r="F62" s="3">
-        <v>174700</v>
+        <v>13700</v>
       </c>
       <c r="G62" s="3">
-        <v>180700</v>
+        <v>14800</v>
       </c>
       <c r="H62" s="3">
-        <v>196000</v>
+        <v>19000</v>
       </c>
       <c r="I62" s="3">
-        <v>205800</v>
+        <v>14900</v>
       </c>
       <c r="J62" s="3">
-        <v>228800</v>
+        <v>15100</v>
       </c>
       <c r="K62" s="3">
         <v>231500</v>
@@ -6035,7 +6035,7 @@
         <v>850000</v>
       </c>
       <c r="J66" s="3">
-        <v>1102900</v>
+        <v>1104600</v>
       </c>
       <c r="K66" s="3">
         <v>1037900</v>
@@ -7409,25 +7409,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>13100</v>
+        <v>10300</v>
       </c>
       <c r="E83" s="3">
-        <v>10000</v>
+        <v>10900</v>
       </c>
       <c r="F83" s="3">
         <v>10100</v>
       </c>
       <c r="G83" s="3">
-        <v>10200</v>
+        <v>10300</v>
       </c>
       <c r="H83" s="3">
-        <v>10300</v>
-      </c>
-      <c r="I83" s="3">
-        <v>3400</v>
+        <v>10900</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J83" s="3">
-        <v>12300</v>
+        <v>13600</v>
       </c>
       <c r="K83" s="3">
         <v>12400</v>
@@ -8593,26 +8593,26 @@
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -9098,26 +9098,26 @@
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -9215,7 +9215,7 @@
         <v>-12700</v>
       </c>
       <c r="I102" s="3">
-        <v>3400</v>
+        <v>3500</v>
       </c>
       <c r="J102" s="3">
         <v>-5300</v>

--- a/AAII_Financials/Quarterly/BNED_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BNED_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="92">
   <si>
     <t>BNED</t>
   </si>
@@ -656,456 +656,482 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45682</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45591</v>
+      </c>
+      <c r="F7" s="2">
         <v>45500</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45409</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45318</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45227</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45136</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45045</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44954</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44863</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44772</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44681</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44590</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44499</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44408</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44317</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44226</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44135</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44044</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43953</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43855</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43764</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43673</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43582</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43491</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43400</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43309</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43218</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43127</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43036</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>42945</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>42854</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AJ7" s="2">
         <v>42763</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AK7" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>466300</v>
+      </c>
+      <c r="E8" s="3">
+        <v>602100</v>
+      </c>
+      <c r="F8" s="3">
         <v>263400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>235900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>456700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>610400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>264200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>241800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>438100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>608600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>254700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>225200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>402800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>867800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>240800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>222800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>411600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>595500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>204000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>256900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>502300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>772200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>319700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>332100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>548000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>814800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>337500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>357700</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>603400</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>1242600</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>355700</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AI8" s="3">
         <v>342800</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AJ8" s="3">
         <v>521600</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AK8" s="3">
         <v>770700</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>369900</v>
+      </c>
+      <c r="E9" s="3">
+        <v>464500</v>
+      </c>
+      <c r="F9" s="3">
         <v>216200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>166100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>356600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>474100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>213500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>183600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>341000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>470500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>198700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>331900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>315800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>662200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>180800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>186900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>341000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>480200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>173200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>191500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>383800</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>585300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>248000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>214700</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>799300</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>1173000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>270900</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>228200</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>456900</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>961300</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>291000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AI9" s="3">
         <v>218600</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AJ9" s="3">
         <v>405700</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AK9" s="3">
         <v>599200</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>96400</v>
+      </c>
+      <c r="E10" s="3">
+        <v>137600</v>
+      </c>
+      <c r="F10" s="3">
         <v>47200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>69900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>100000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>136200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>50600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>58300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>97000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>138100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>56000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>-106700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>87000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>205600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>60000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>35900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>70600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>115300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>30800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>65400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>118500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>186900</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>71700</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>117400</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>-251300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>-358200</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>66600</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>129500</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>146500</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>281300</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>64700</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AI10" s="3">
         <v>124200</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AJ10" s="3">
         <v>115900</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AK10" s="3">
         <v>171500</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1141,8 +1167,10 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1242,8 +1270,14 @@
       <c r="AI12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1343,210 +1377,228 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="E14" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F14" s="3">
         <v>58900</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>9800</v>
       </c>
-      <c r="F14" s="3">
+      <c r="H14" s="3">
         <v>9200</v>
       </c>
-      <c r="G14" s="3">
+      <c r="I14" s="3">
         <v>4300</v>
       </c>
-      <c r="H14" s="3">
+      <c r="J14" s="3">
         <v>4600</v>
       </c>
-      <c r="I14" s="3">
+      <c r="K14" s="3">
         <v>5300</v>
       </c>
-      <c r="J14" s="3">
+      <c r="L14" s="3">
         <v>10100</v>
       </c>
-      <c r="K14" s="3">
+      <c r="M14" s="3">
         <v>300</v>
       </c>
-      <c r="L14" s="3">
+      <c r="N14" s="3">
         <v>400</v>
       </c>
-      <c r="M14" s="3">
+      <c r="O14" s="3">
         <v>-2800</v>
       </c>
-      <c r="N14" s="3">
+      <c r="P14" s="3">
         <v>6500</v>
       </c>
-      <c r="O14" s="3">
+      <c r="Q14" s="3">
         <v>3000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="R14" s="3">
         <v>1900</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>29300</v>
       </c>
-      <c r="S14" s="3">
+      <c r="U14" s="3">
         <v>3400</v>
       </c>
-      <c r="T14" s="3">
+      <c r="V14" s="3">
         <v>5700</v>
       </c>
-      <c r="U14" s="3">
+      <c r="W14" s="3">
         <v>15300</v>
       </c>
-      <c r="V14" s="3">
+      <c r="X14" s="3">
         <v>200</v>
       </c>
-      <c r="W14" s="3">
+      <c r="Y14" s="3">
         <v>1600</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Z14" s="3">
         <v>1900</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="AA14" s="3">
         <v>62500</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AB14" s="3">
         <v>2600</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AC14" s="3">
         <v>500</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="3">
         <v>200</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AF14" s="3">
         <v>313200</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AG14" s="3">
         <v>7300</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AH14" s="3">
         <v>5800</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AI14" s="3">
         <v>7000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AJ14" s="3">
         <v>500</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AK14" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>7800</v>
+      </c>
+      <c r="E15" s="3">
+        <v>8500</v>
+      </c>
+      <c r="F15" s="3">
         <v>13100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>10000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
         <v>10100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>10200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>10300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>10900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>10100</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>10300</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>10900</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>5400</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>12200</v>
       </c>
-      <c r="O15" s="3">
+      <c r="Q15" s="3">
         <v>24600</v>
       </c>
-      <c r="P15" s="3">
+      <c r="R15" s="3">
         <v>12600</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="S15" s="3">
         <v>12400</v>
       </c>
-      <c r="R15" s="3">
+      <c r="T15" s="3">
         <v>13300</v>
       </c>
-      <c r="S15" s="3">
+      <c r="U15" s="3">
         <v>13200</v>
       </c>
-      <c r="T15" s="3">
+      <c r="V15" s="3">
         <v>14100</v>
       </c>
-      <c r="U15" s="3">
+      <c r="W15" s="3">
         <v>15300</v>
       </c>
-      <c r="V15" s="3">
+      <c r="X15" s="3">
         <v>15100</v>
       </c>
-      <c r="W15" s="3">
+      <c r="Y15" s="3">
         <v>15500</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Z15" s="3">
         <v>15900</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="AA15" s="3">
         <v>16500</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AB15" s="3">
         <v>16400</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AC15" s="3">
         <v>16400</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AD15" s="3">
         <v>16500</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AE15" s="3">
         <v>16900</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AF15" s="3">
         <v>17000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AG15" s="3">
         <v>31700</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AH15" s="3">
         <v>15000</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AI15" s="3">
         <v>14300</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AJ15" s="3">
         <v>13100</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AK15" s="3">
         <v>13000</v>
       </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1579,210 +1631,224 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>449300</v>
+      </c>
+      <c r="E17" s="3">
+        <v>545900</v>
+      </c>
+      <c r="F17" s="3">
         <v>296300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>243100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>446500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>570300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>301300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>270900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>443000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>580000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>300300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>235800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>435900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>883900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>281500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>282800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>476300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>588800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>262900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>309300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>505300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>715800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>363500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>392100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>545000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>736300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>386600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>352400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>899000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>1214900</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>411300</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AI17" s="3">
         <v>338500</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AJ17" s="3">
         <v>516400</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AK17" s="3">
         <v>713900</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>17000</v>
+      </c>
+      <c r="E18" s="3">
+        <v>56200</v>
+      </c>
+      <c r="F18" s="3">
         <v>-32900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-7200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>10100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>40100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>-37100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-29100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-4900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>28600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-45600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-10600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-33100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>-16100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>-40700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-60000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-64700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>6700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>-58900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-52400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>-3000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>56400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>-43800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>-60000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>3000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>78500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>-49100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>5300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>-295600</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>27700</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>-55600</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AI18" s="3">
         <v>4300</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AJ18" s="3">
         <v>5200</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AK18" s="3">
         <v>56800</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1818,8 +1884,10 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1844,11 +1912,11 @@
       <c r="J20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
-      <c r="L20" s="3">
-        <v>0</v>
+      <c r="K20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M20" s="3">
         <v>0</v>
@@ -1919,412 +1987,442 @@
       <c r="AI20" s="3">
         <v>0</v>
       </c>
+      <c r="AJ20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>24800</v>
+      </c>
+      <c r="E21" s="3">
+        <v>64700</v>
+      </c>
+      <c r="F21" s="3">
         <v>-19800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>2800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>20300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>50300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>-26800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-18200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>5200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>35700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>-31500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-8800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-19600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>11000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>-26800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>-46300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>-50100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>21100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>-43700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>-36000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>13200</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>73000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>-27000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>-42500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>19200</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>95000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>-32500</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>22100</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>-278600</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>59400</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>-40500</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AI21" s="3">
         <v>18600</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AJ21" s="3">
         <v>18300</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AK21" s="3">
         <v>69700</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E22" s="3">
+        <v>5800</v>
+      </c>
+      <c r="F22" s="3">
         <v>7700</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>12000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>10600</v>
       </c>
-      <c r="G22" s="3">
-        <v>10700</v>
-      </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
+        <v>10800</v>
+      </c>
+      <c r="J22" s="3">
         <v>8300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>7500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>6900</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>4900</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>3900</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>2300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>3100</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>4800</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>2500</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>2200</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>2300</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>900</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>2700</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>1600</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>1900</v>
       </c>
-      <c r="W22" s="3">
+      <c r="Y22" s="3">
         <v>1400</v>
-      </c>
-      <c r="X22" s="3">
-        <v>2500</v>
-      </c>
-      <c r="Y22" s="3">
-        <v>1900</v>
       </c>
       <c r="Z22" s="3">
         <v>2500</v>
       </c>
       <c r="AA22" s="3">
+        <v>1900</v>
+      </c>
+      <c r="AB22" s="3">
+        <v>2500</v>
+      </c>
+      <c r="AC22" s="3">
         <v>1800</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AD22" s="3">
         <v>3500</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AE22" s="3">
         <v>2500</v>
-      </c>
-      <c r="AD22" s="3">
-        <v>3000</v>
-      </c>
-      <c r="AE22" s="3">
-        <v>4900</v>
       </c>
       <c r="AF22" s="3">
         <v>3000</v>
       </c>
       <c r="AG22" s="3">
+        <v>4900</v>
+      </c>
+      <c r="AH22" s="3">
+        <v>3000</v>
+      </c>
+      <c r="AI22" s="3">
         <v>1500</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AJ22" s="3">
         <v>700</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AK22" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>17800</v>
+      </c>
+      <c r="E23" s="3">
+        <v>50900</v>
+      </c>
+      <c r="F23" s="3">
         <v>-99300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-27800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-9700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>25200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>-50000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-41400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-22000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>23800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>-49500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-12900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-36200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>-20900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>-43200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-62200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-67000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>5800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>-61600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-54000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-4900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>55000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-46300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>-62000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>76600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>-52600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>2700</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>-298600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>22800</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>-58600</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AI23" s="3">
         <v>2900</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AJ23" s="3">
         <v>4500</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AK23" s="3">
         <v>56100</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>10700</v>
+      </c>
+      <c r="E24" s="3">
+        <v>1100</v>
+      </c>
+      <c r="F24" s="3">
         <v>100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>-300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>300</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
+        <v>0</v>
+      </c>
+      <c r="K24" s="3">
         <v>400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>-400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>-10000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>-9800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>-18700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>-1700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>-14900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>-13700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>-3200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>19100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>-14200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>-15700</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>-300</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>16900</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>-14000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>-15000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>5800</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>9200</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AH24" s="3">
         <v>-23800</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AI24" s="3">
         <v>2600</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AJ24" s="3">
         <v>800</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AK24" s="3">
         <v>26800</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2424,210 +2522,228 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E26" s="3">
+        <v>49700</v>
+      </c>
+      <c r="F26" s="3">
         <v>-99500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-27400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-9900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>24900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>-50000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-41900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-22100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>24200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>-50300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-2900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-36800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>-21100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>-43600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-52400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-48300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>7500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>-46700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-40300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-1700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>35900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-32200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>-46200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>59700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>-38600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>17800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>-304400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>13600</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>-34800</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AI26" s="3">
         <v>200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AJ26" s="3">
         <v>3800</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AK26" s="3">
         <v>29300</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E27" s="3">
+        <v>49700</v>
+      </c>
+      <c r="F27" s="3">
         <v>-99500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-27400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-9600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>24200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-50400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-46300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-25000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>24200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-50300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-2900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-36800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>-21100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>-43600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-52400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-48300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>7500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>-46700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-40300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-1700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>35900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-32100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>-46200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>59700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>-38600</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>17800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>-304400</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>13600</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>-34800</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AI27" s="3">
         <v>200</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AJ27" s="3">
         <v>3800</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AK27" s="3">
         <v>29300</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2727,8 +2843,14 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2736,43 +2858,43 @@
         <v>0</v>
       </c>
       <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
         <v>100</v>
       </c>
-      <c r="F29" s="3">
+      <c r="H29" s="3">
         <v>300</v>
       </c>
-      <c r="G29" s="3">
+      <c r="I29" s="3">
         <v>-700</v>
       </c>
-      <c r="H29" s="3">
+      <c r="J29" s="3">
         <v>-400</v>
       </c>
-      <c r="I29" s="3">
+      <c r="K29" s="3">
         <v>-4400</v>
       </c>
-      <c r="J29" s="3">
+      <c r="L29" s="3">
         <v>-2900</v>
       </c>
-      <c r="K29" s="3">
+      <c r="M29" s="3">
         <v>-2000</v>
       </c>
-      <c r="L29" s="3">
+      <c r="N29" s="3">
         <v>-2400</v>
       </c>
-      <c r="M29" s="3">
+      <c r="O29" s="3">
         <v>-7300</v>
       </c>
-      <c r="N29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P29" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q29" s="3">
-        <v>0</v>
+      <c r="P29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R29" s="3">
         <v>0</v>
@@ -2789,11 +2911,11 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-      <c r="W29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="X29" s="3" t="s">
-        <v>8</v>
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+      <c r="X29" s="3">
+        <v>0</v>
       </c>
       <c r="Y29" s="3" t="s">
         <v>8</v>
@@ -2807,20 +2929,20 @@
       <c r="AB29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AC29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE29" s="3">
         <v>-700</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AF29" s="3">
         <v>21100</v>
       </c>
-      <c r="AE29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG29" s="3" t="s">
-        <v>8</v>
+      <c r="AG29" s="3">
+        <v>0</v>
       </c>
       <c r="AH29" s="3" t="s">
         <v>8</v>
@@ -2828,8 +2950,14 @@
       <c r="AI29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2929,8 +3057,14 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3030,8 +3164,14 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3056,11 +3196,11 @@
       <c r="J32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
-      <c r="L32" s="3">
-        <v>0</v>
+      <c r="K32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M32" s="3">
         <v>0</v>
@@ -3131,109 +3271,121 @@
       <c r="AI32" s="3">
         <v>0</v>
       </c>
+      <c r="AJ32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E33" s="3">
+        <v>49700</v>
+      </c>
+      <c r="F33" s="3">
         <v>-99500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-27400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-9600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>24200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-50400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-46300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-25000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>22100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-52700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-10200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-36800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>-21100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>-43600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-52400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-48300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>7500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>-46700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-40300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-1700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>35900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-32100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>-46200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>59700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>-38600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>17100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>-283200</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>13600</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>-34800</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AI33" s="3">
         <v>200</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AJ33" s="3">
         <v>3800</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AK33" s="3">
         <v>29300</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3333,215 +3485,233 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E35" s="3">
+        <v>49700</v>
+      </c>
+      <c r="F35" s="3">
         <v>-99500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-27400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-9600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>24200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-50400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-46300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-25000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>22100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-52700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-10200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-36800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>-21100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>-43600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-52400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-48300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>7500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>-46700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-40300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-1700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>35900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-32100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>-46200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>59700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>-38600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>17100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>-283200</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>13600</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>-34800</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AI35" s="3">
         <v>200</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AJ35" s="3">
         <v>3800</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AK35" s="3">
         <v>29300</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45682</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45591</v>
+      </c>
+      <c r="F38" s="2">
         <v>45500</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45409</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45318</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45227</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45136</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45045</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44954</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44863</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44772</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44681</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44590</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44499</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44408</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44317</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44226</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44135</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44044</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43953</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43855</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43764</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43673</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43582</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43491</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43400</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43309</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43218</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43127</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43036</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>42945</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>42854</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AJ38" s="2">
         <v>42763</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AK38" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3577,8 +3747,10 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3614,109 +3786,117 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>9200</v>
+      </c>
+      <c r="E41" s="3">
+        <v>11600</v>
+      </c>
+      <c r="F41" s="3">
         <v>8200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>10500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>8100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>15000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>7700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>14200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>11100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>17300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>7600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>8800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>10000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>11000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>7600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>8000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>9900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>7400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>7500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>8200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>9800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>24600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>8200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>14000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>22000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>20000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>13300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>16100</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>22400</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>17500</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>14200</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AI41" s="3">
         <v>19000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AJ41" s="3">
         <v>132100</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AK41" s="3">
         <v>176600</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3816,412 +3996,442 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>354200</v>
+      </c>
+      <c r="E43" s="3">
+        <v>278500</v>
+      </c>
+      <c r="F43" s="3">
         <v>162900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>118600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>315100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>221800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>150900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>98700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>277500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>209300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>119000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>136000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>250200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>218100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>118300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>121100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>227200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>167500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>107500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>90900</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>238000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>162500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>98500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>98200</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>231100</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>138000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>99800</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>100100</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>243400</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>153600</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AH43" s="3">
         <v>112500</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AI43" s="3">
         <v>86000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AJ43" s="3">
         <v>178800</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AK43" s="3">
         <v>93300</v>
       </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>367900</v>
+      </c>
+      <c r="E44" s="3">
+        <v>365100</v>
+      </c>
+      <c r="F44" s="3">
         <v>405600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>377000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>386100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>416100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>391000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>353300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>444400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>420900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>472100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>323500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>444600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>421200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>479100</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>309800</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>493300</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>508400</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>591700</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>469600</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>578700</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>543600</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>723000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>467300</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>630200</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>576500</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>736100</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>493900</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AF44" s="3">
         <v>675900</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AG44" s="3">
         <v>593600</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AH44" s="3">
         <v>787300</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AI44" s="3">
         <v>486900</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AJ44" s="3">
         <v>561400</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AK44" s="3">
         <v>488000</v>
       </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E45" s="3">
+      <c r="E45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G45" s="3">
         <v>1300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>14600</v>
       </c>
-      <c r="G45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I45" s="3">
+      <c r="I45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K45" s="3">
         <v>33600</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M45" s="3">
         <v>137000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>147800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>63400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>60600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>69000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>64700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>61900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>25300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>23800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>22400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>16200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>24600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>18500</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>18100</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>11800</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>20700</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>16600</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>18700</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>9200</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>12300</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>13400</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AH45" s="3">
         <v>13500</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AI45" s="3">
         <v>10700</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AJ45" s="3">
         <v>8100</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AK45" s="3">
         <v>8100</v>
       </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>758000</v>
+      </c>
+      <c r="E46" s="3">
+        <v>686000</v>
+      </c>
+      <c r="F46" s="3">
         <v>601400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>530800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>763700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>716400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>598600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>537000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>790100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>729600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>686200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>531700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>765400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>719200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>669700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>500800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>755700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>707000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>729100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>584900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>851200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>749200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>847800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>591400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>904000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>751200</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>867900</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>619400</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>954000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>778100</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>927500</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AI46" s="3">
         <v>602600</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AJ46" s="3">
         <v>880400</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AK46" s="3">
         <v>766000</v>
       </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4246,11 +4456,11 @@
       <c r="J47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
-      </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -4321,210 +4531,228 @@
       <c r="AI47" s="3">
         <v>0</v>
       </c>
+      <c r="AJ47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>222700</v>
+      </c>
+      <c r="E48" s="3">
+        <v>255200</v>
+      </c>
+      <c r="F48" s="3">
         <v>290100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>255400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>277500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>307900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>347500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>315100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>351700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>367200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>391800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>360200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>323000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>344500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>380200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>329600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>330300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>379200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>414400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>348600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>352800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>394900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>420300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>109800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>109400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>112000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>108100</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>111300</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>111000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>115300</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AH48" s="3">
         <v>112800</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AI48" s="3">
         <v>116600</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AJ48" s="3">
         <v>107300</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AK48" s="3">
         <v>108500</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>81600</v>
+      </c>
+      <c r="E49" s="3">
+        <v>85100</v>
+      </c>
+      <c r="F49" s="3">
         <v>87800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>94200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>97900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>104000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>107400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>110600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>119600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>125200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>128000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>131700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>138700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>146500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>150700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>155600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>160200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>170800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>175200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>179800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>184300</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>188900</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>193900</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>199700</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>262400</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>267900</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>263200</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>268400</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AF49" s="3">
         <v>273600</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AG49" s="3">
         <v>591900</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AH49" s="3">
         <v>535800</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AI49" s="3">
         <v>539400</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AJ49" s="3">
         <v>473000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AK49" s="3">
         <v>475900</v>
       </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4624,8 +4852,14 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4725,109 +4959,121 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>24200</v>
+      </c>
+      <c r="E52" s="3">
+        <v>12300</v>
+      </c>
+      <c r="F52" s="3">
         <v>11600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>11800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>12500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>16700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>17300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>16600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>19700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>42100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>44600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>52700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>39700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>42000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>43300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>45000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>42200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>40000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>42100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>43100</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>39800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>47300</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>40500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>45400</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>40200</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>41600</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>41700</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>40100</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>42000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>41900</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AH52" s="3">
         <v>42500</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AI52" s="3">
         <v>41200</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AJ52" s="3">
         <v>39200</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AK52" s="3">
         <v>38200</v>
       </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4927,109 +5173,121 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1087600</v>
+      </c>
+      <c r="E54" s="3">
+        <v>1052100</v>
+      </c>
+      <c r="F54" s="3">
         <v>1005200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>905100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>1151600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>1145000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>1070800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>980800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>1281100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>1238400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>1223600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>1071600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>1266700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>1252200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>1244000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>1031100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>1288500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>1297000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>1360800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>1156400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>1428100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>1380300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>1502400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>946200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>1316100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>1172700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>1280900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>1039200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>1380600</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>1527200</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>1618700</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AI54" s="3">
         <v>1299800</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AJ54" s="3">
         <v>1499900</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AK54" s="3">
         <v>1388600</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5065,8 +5323,10 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5102,614 +5362,652 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>303600</v>
+      </c>
+      <c r="E57" s="3">
+        <v>299000</v>
+      </c>
+      <c r="F57" s="3">
         <v>266300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>299200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>343100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>385900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>275400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>267900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>355300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>326000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>324400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>182600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>359700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>333100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>331100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>137600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>318800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>314000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>291500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>143700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>389100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>387700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>443100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>186800</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>464900</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>443300</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>463700</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>187900</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>489000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>458800</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>511500</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AI57" s="3">
         <v>192700</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AJ57" s="3">
         <v>480400</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AK57" s="3">
         <v>439700</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>101100</v>
+      </c>
+      <c r="E58" s="3">
+        <v>124900</v>
+      </c>
+      <c r="F58" s="3">
         <v>147800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>102200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>349600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>126400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>150900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>100000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>116100</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3">
         <v>40000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>40000</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
-      </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
       <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3">
         <v>50000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>50000</v>
       </c>
-      <c r="R58" s="3">
-        <v>0</v>
-      </c>
-      <c r="S58" s="3">
-        <v>0</v>
-      </c>
       <c r="T58" s="3">
         <v>0</v>
       </c>
       <c r="U58" s="3">
+        <v>0</v>
+      </c>
+      <c r="V58" s="3">
+        <v>0</v>
+      </c>
+      <c r="W58" s="3">
         <v>75000</v>
       </c>
-      <c r="V58" s="3">
-        <v>0</v>
-      </c>
-      <c r="W58" s="3">
-        <v>0</v>
-      </c>
       <c r="X58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z58" s="3">
         <v>100000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>100000</v>
       </c>
-      <c r="Z58" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA58" s="3">
-        <v>0</v>
-      </c>
       <c r="AB58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD58" s="3">
         <v>100000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>100000</v>
       </c>
-      <c r="AD58" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE58" s="3">
-        <v>0</v>
-      </c>
       <c r="AF58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH58" s="3">
         <v>100000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AI58" s="3">
         <v>100000</v>
       </c>
-      <c r="AH58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AI58" s="3" t="s">
+      <c r="AJ58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK58" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>49700</v>
+      </c>
+      <c r="E59" s="3">
+        <v>39500</v>
+      </c>
+      <c r="F59" s="3">
         <v>12000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>11300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>50000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>40400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>12800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>21400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>53700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>368400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>244100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>192800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>402300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>363900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>228000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>186100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>231400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>255700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>206600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>188000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>296000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>304900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>187000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>121700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>219700</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>170000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>93200</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>125600</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>252200</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>184300</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>89900</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AI59" s="3">
         <v>120500</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AJ59" s="3">
         <v>207700</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AK59" s="3">
         <v>140800</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>534700</v>
+      </c>
+      <c r="E60" s="3">
+        <v>523600</v>
+      </c>
+      <c r="F60" s="3">
         <v>489900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>478800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>849600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>624400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>516100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>462100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>609600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>575700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>608400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>415400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>611300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>574300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>609100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>373700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>550200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>569700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>498100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>406700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>685000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>692600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>730200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>408500</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>684600</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>613400</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>657000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>413500</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>741200</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>643100</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>701400</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AI60" s="3">
         <v>413200</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AJ60" s="3">
         <v>688100</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AK60" s="3">
         <v>580500</v>
       </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>263000</v>
+      </c>
+      <c r="E61" s="3">
+        <v>307300</v>
+      </c>
+      <c r="F61" s="3">
         <v>354100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>338500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>185400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>394100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>448800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>366900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>474100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>250400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>218600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>185700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>200400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>183300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>153700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>127600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>150800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>99500</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>234600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>99700</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>65900</v>
       </c>
-      <c r="W61" s="3">
-        <v>0</v>
-      </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z61" s="3">
         <v>74100</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>33500</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>70100</v>
       </c>
-      <c r="AA61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD61" s="3">
         <v>130200</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>96400</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AF61" s="3">
         <v>113000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AG61" s="3">
         <v>41800</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AH61" s="3">
         <v>120100</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AI61" s="3">
         <v>59600</v>
       </c>
-      <c r="AH61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK61" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E62" s="3">
+        <v>11100</v>
+      </c>
+      <c r="F62" s="3">
         <v>12200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>12300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>13700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>14800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>19000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>14900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>15100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>231500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>219800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>242100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>266300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>273600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>257300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>262100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>243300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>247300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>255900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>232300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>219800</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>230300</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>277400</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>53500</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>66600</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>67300</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>62000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>61400</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>77700</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>112500</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AH62" s="3">
         <v>116200</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AI62" s="3">
         <v>113300</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AJ62" s="3">
         <v>98900</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AK62" s="3">
         <v>101700</v>
       </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5809,8 +6107,14 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5910,8 +6214,14 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6011,109 +6321,121 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>804300</v>
+      </c>
+      <c r="E66" s="3">
+        <v>847200</v>
+      </c>
+      <c r="F66" s="3">
         <v>860800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>834500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>1054500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>1039000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>989800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>850000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>1104600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>1037900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>1046800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>843200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>1029300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>980000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>994700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>738100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>944300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>916600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>988500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>738700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>970700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>922900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>1081700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>495600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>821400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>680700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>849200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>571200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>931900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>797400</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>937800</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AI66" s="3">
         <v>586100</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AJ66" s="3">
         <v>787000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AK66" s="3">
         <v>682200</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6149,8 +6471,10 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6250,8 +6574,14 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6351,8 +6681,14 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6452,8 +6788,14 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6553,109 +6895,121 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-699200</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-706300</v>
+      </c>
+      <c r="F72" s="3">
         <v>-756000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-656600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-629200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-619600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-643700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-593400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-547100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-522100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-544200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-491500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-480500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-443700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-466300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-422600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-370300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-322000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-329500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-282800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-242500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-240800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>-276700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>-244600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>-198400</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>-199100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>-258800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>-220200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>-237300</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>46000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>-2400</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AI72" s="3">
         <v>32400</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AJ72" s="3">
         <v>32100</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AK72" s="3">
         <v>28400</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6755,8 +7109,14 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6856,8 +7216,14 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6957,109 +7323,121 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>283300</v>
+      </c>
+      <c r="E76" s="3">
+        <v>204800</v>
+      </c>
+      <c r="F76" s="3">
         <v>144400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>70600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>97100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>106000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>81100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>130800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>176500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>200500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>176800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>228400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>237500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>272200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>249300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>293000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>344200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>380400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>372300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>417800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>457400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>457300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>420800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>450600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>494700</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>492000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>431700</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>468000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>448700</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>729800</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>680900</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AI76" s="3">
         <v>713700</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AJ76" s="3">
         <v>712900</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AK76" s="3">
         <v>706400</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7159,215 +7537,233 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45682</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45591</v>
+      </c>
+      <c r="F80" s="2">
         <v>45500</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45409</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45318</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45227</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45136</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45045</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44954</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44863</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44772</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44681</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44590</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44499</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44408</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44317</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44226</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44135</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44044</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43953</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43855</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43764</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43673</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43582</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43491</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43400</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43309</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43218</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43127</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43036</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>42945</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>42854</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AJ80" s="2">
         <v>42763</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AK80" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E81" s="3">
+        <v>49700</v>
+      </c>
+      <c r="F81" s="3">
         <v>-99500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-27400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-9600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>24200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-50400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-46300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-25000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>22100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-52700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-10200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-36800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>-21100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>-43600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-52400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-48300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>7500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>-46700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-40300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-1700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>35900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-32100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>-46200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>59700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>-38600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>17100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>-283200</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>13600</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>-34800</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AI81" s="3">
         <v>200</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AJ81" s="3">
         <v>3800</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AK81" s="3">
         <v>29300</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7403,109 +7799,117 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>10100</v>
+      </c>
+      <c r="E83" s="3">
+        <v>10200</v>
+      </c>
+      <c r="F83" s="3">
         <v>10300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>10900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>10100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>10300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>10900</v>
       </c>
-      <c r="I83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L83" s="3">
         <v>13600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>12400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>14100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>14100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>13600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>27200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>13900</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>13700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>14600</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>14400</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>15200</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>16400</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>16200</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>16500</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>16800</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>17600</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>16200</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>16600</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AD83" s="3">
         <v>16500</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AE83" s="3">
         <v>16900</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AF83" s="3">
         <v>17000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AG83" s="3">
         <v>31700</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AH83" s="3">
         <v>15000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AI83" s="3">
         <v>14300</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AJ83" s="3">
         <v>13100</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AK83" s="3">
         <v>13000</v>
       </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7605,8 +8009,14 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7706,8 +8116,14 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7807,8 +8223,14 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7908,8 +8330,14 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8009,109 +8437,121 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-41900</v>
+      </c>
+      <c r="E89" s="3">
+        <v>47400</v>
+      </c>
+      <c r="F89" s="3">
         <v>-144000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>81700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-35800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>72000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-123100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>114300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-32000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>38400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-29000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-5800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-16400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>24300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>-17300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-8700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-49800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>144500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>-53100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>-100700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>-69400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>201700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>-40200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>-55000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>-60700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>263900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>-27400</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>-81400</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>-58200</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>199600</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>-56000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AI89" s="3">
         <v>-77000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AJ89" s="3">
         <v>-34300</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AK89" s="3">
         <v>204500</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8147,109 +8587,117 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="F91" s="3">
         <v>-3500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-2600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-3300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-4000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-4200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-3400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-4900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-7100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-9700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-12100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-9900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-11400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-11300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-9700</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-9100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-7100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-9400</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-7600</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-10900</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-8300</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-14700</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-8600</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-14900</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-8200</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-12700</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AF91" s="3">
         <v>-7700</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AG91" s="3">
         <v>-22400</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AH91" s="3">
         <v>-7900</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AI91" s="3">
         <v>-8200</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AJ91" s="3">
         <v>-9000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AK91" s="3">
         <v>-11300</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8349,8 +8797,14 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8450,109 +8904,121 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="F94" s="3">
         <v>-3200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-2600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-3300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-4000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>17300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-4700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-6000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-10600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-9700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-10000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-11900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-20800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-11000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-11300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-12600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-7500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-5500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-7900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-5600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-10000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-6100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-13000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-7400</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-25000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-9300</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-11300</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>-7500</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>-81300</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AH94" s="3">
         <v>-9100</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AI94" s="3">
         <v>-190800</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AJ94" s="3">
         <v>-10200</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AK94" s="3">
         <v>-10600</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8588,8 +9054,10 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8614,11 +9082,11 @@
       <c r="J96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -8689,8 +9157,14 @@
       <c r="AI96" s="3">
         <v>0</v>
       </c>
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8790,8 +9264,14 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8891,8 +9371,14 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8992,109 +9478,121 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>32500</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-37300</v>
+      </c>
+      <c r="F100" s="3">
         <v>139900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-65600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>18700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-52000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>93200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-106100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>32700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-9700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>33400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>25000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>17300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>3400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>24900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>25700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>62200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-135600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>59500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>108800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>65900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-175300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>40600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>60000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>70100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-232200</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>33800</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>83400</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>71200</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>-119400</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AH100" s="3">
         <v>60500</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AI100" s="3">
         <v>155100</v>
       </c>
-      <c r="AH100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK100" s="3">
         <v>-26300</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9119,11 +9617,11 @@
       <c r="J101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -9194,105 +9692,117 @@
       <c r="AI101" s="3">
         <v>0</v>
       </c>
+      <c r="AJ101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-12200</v>
+      </c>
+      <c r="E102" s="3">
+        <v>7700</v>
+      </c>
+      <c r="F102" s="3">
         <v>-7300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>13500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-20300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>16000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-12700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>3500</v>
-      </c>
-      <c r="J102" s="3">
-        <v>-5300</v>
-      </c>
-      <c r="K102" s="3">
-        <v>18100</v>
       </c>
       <c r="L102" s="3">
         <v>-5300</v>
       </c>
       <c r="M102" s="3">
+        <v>18100</v>
+      </c>
+      <c r="N102" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="O102" s="3">
         <v>9200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-10800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>6700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-3600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>6100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>2600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>-1600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-14800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>16400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>-5800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>-8000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>2000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>6800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>-2900</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>-8200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>4900</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>-1500</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>-4800</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AI102" s="3">
         <v>-112700</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AJ102" s="3">
         <v>-44500</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AK102" s="3">
         <v>167700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BNED_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BNED_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="92">
   <si>
     <t>BNED</t>
   </si>
@@ -656,16 +656,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AO102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
@@ -674,15 +674,15 @@
     <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="31" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
@@ -690,448 +690,499 @@
     <col min="34" max="34" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="35" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="37" max="37" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="38" max="38" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="40" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46053</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45962</v>
+      </c>
+      <c r="F7" s="2">
+        <v>45871</v>
+      </c>
+      <c r="G7" s="2">
+        <v>45780</v>
+      </c>
+      <c r="H7" s="2">
         <v>45682</v>
       </c>
-      <c r="E7" s="2">
+      <c r="I7" s="2">
         <v>45591</v>
       </c>
-      <c r="F7" s="2">
+      <c r="J7" s="2">
         <v>45500</v>
       </c>
-      <c r="G7" s="2">
+      <c r="K7" s="2">
         <v>45409</v>
       </c>
-      <c r="H7" s="2">
+      <c r="L7" s="2">
         <v>45318</v>
       </c>
-      <c r="I7" s="2">
+      <c r="M7" s="2">
         <v>45227</v>
       </c>
-      <c r="J7" s="2">
+      <c r="N7" s="2">
         <v>45136</v>
       </c>
-      <c r="K7" s="2">
+      <c r="O7" s="2">
         <v>45045</v>
       </c>
-      <c r="L7" s="2">
+      <c r="P7" s="2">
         <v>44954</v>
       </c>
-      <c r="M7" s="2">
+      <c r="Q7" s="2">
         <v>44863</v>
       </c>
-      <c r="N7" s="2">
+      <c r="R7" s="2">
         <v>44772</v>
       </c>
-      <c r="O7" s="2">
+      <c r="S7" s="2">
         <v>44681</v>
       </c>
-      <c r="P7" s="2">
+      <c r="T7" s="2">
         <v>44590</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="U7" s="2">
         <v>44499</v>
       </c>
-      <c r="R7" s="2">
+      <c r="V7" s="2">
         <v>44408</v>
       </c>
-      <c r="S7" s="2">
+      <c r="W7" s="2">
         <v>44317</v>
       </c>
-      <c r="T7" s="2">
+      <c r="X7" s="2">
         <v>44226</v>
       </c>
-      <c r="U7" s="2">
+      <c r="Y7" s="2">
         <v>44135</v>
       </c>
-      <c r="V7" s="2">
+      <c r="Z7" s="2">
         <v>44044</v>
       </c>
-      <c r="W7" s="2">
+      <c r="AA7" s="2">
         <v>43953</v>
       </c>
-      <c r="X7" s="2">
+      <c r="AB7" s="2">
         <v>43855</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AC7" s="2">
         <v>43764</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AD7" s="2">
         <v>43673</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AE7" s="2">
         <v>43582</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AF7" s="2">
         <v>43491</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AG7" s="2">
         <v>43400</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AH7" s="2">
         <v>43309</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AI7" s="2">
         <v>43218</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AJ7" s="2">
         <v>43127</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AK7" s="2">
         <v>43036</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AL7" s="2">
         <v>42945</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AM7" s="2">
         <v>42854</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AN7" s="2">
         <v>42763</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AO7" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>466300</v>
+        <v>515100</v>
       </c>
       <c r="E8" s="3">
+        <v>644400</v>
+      </c>
+      <c r="F8" s="3">
+        <v>288200</v>
+      </c>
+      <c r="G8" s="3">
+        <v>278300</v>
+      </c>
+      <c r="H8" s="3">
+        <v>462800</v>
+      </c>
+      <c r="I8" s="3">
         <v>602100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="J8" s="3">
         <v>263400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="K8" s="3">
         <v>235900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="L8" s="3">
         <v>456700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="M8" s="3">
         <v>610400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="N8" s="3">
         <v>264200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="O8" s="3">
         <v>241800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="P8" s="3">
         <v>438100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="Q8" s="3">
         <v>608600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="R8" s="3">
         <v>254700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="S8" s="3">
         <v>225200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="T8" s="3">
         <v>402800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="U8" s="3">
         <v>867800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="V8" s="3">
         <v>240800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="W8" s="3">
         <v>222800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="X8" s="3">
         <v>411600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="Y8" s="3">
         <v>595500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="Z8" s="3">
         <v>204000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="AA8" s="3">
         <v>256900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="AB8" s="3">
         <v>502300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AC8" s="3">
         <v>772200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AD8" s="3">
         <v>319700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AE8" s="3">
         <v>332100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AF8" s="3">
         <v>548000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AG8" s="3">
         <v>814800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AH8" s="3">
         <v>337500</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AI8" s="3">
         <v>357700</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AJ8" s="3">
         <v>603400</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AK8" s="3">
         <v>1242600</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AL8" s="3">
         <v>355700</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AM8" s="3">
         <v>342800</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AN8" s="3">
         <v>521600</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AO8" s="3">
         <v>770700</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>369900</v>
+        <v>419000</v>
       </c>
       <c r="E9" s="3">
-        <v>464500</v>
+        <v>514600</v>
       </c>
       <c r="F9" s="3">
-        <v>216200</v>
+        <v>232800</v>
       </c>
       <c r="G9" s="3">
+        <v>221700</v>
+      </c>
+      <c r="H9" s="3">
+        <v>369100</v>
+      </c>
+      <c r="I9" s="3">
+        <v>473600</v>
+      </c>
+      <c r="J9" s="3">
+        <v>218400</v>
+      </c>
+      <c r="K9" s="3">
         <v>166100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="L9" s="3">
         <v>356600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="M9" s="3">
         <v>474100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="N9" s="3">
         <v>213500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="O9" s="3">
         <v>183600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="P9" s="3">
         <v>341000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="Q9" s="3">
         <v>470500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="R9" s="3">
         <v>198700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="S9" s="3">
         <v>331900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="T9" s="3">
         <v>315800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="U9" s="3">
         <v>662200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="V9" s="3">
         <v>180800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="W9" s="3">
         <v>186900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="X9" s="3">
         <v>341000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="Y9" s="3">
         <v>480200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="Z9" s="3">
         <v>173200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="AA9" s="3">
         <v>191500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="AB9" s="3">
         <v>383800</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AC9" s="3">
         <v>585300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AD9" s="3">
         <v>248000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AE9" s="3">
         <v>214700</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AF9" s="3">
         <v>799300</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AG9" s="3">
         <v>1173000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AH9" s="3">
         <v>270900</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AI9" s="3">
         <v>228200</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AJ9" s="3">
         <v>456900</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AK9" s="3">
         <v>961300</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AL9" s="3">
         <v>291000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AM9" s="3">
         <v>218600</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AN9" s="3">
         <v>405700</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AO9" s="3">
         <v>599200</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>96400</v>
+        <v>96100</v>
       </c>
       <c r="E10" s="3">
-        <v>137600</v>
+        <v>129800</v>
       </c>
       <c r="F10" s="3">
-        <v>47200</v>
+        <v>55400</v>
       </c>
       <c r="G10" s="3">
+        <v>56600</v>
+      </c>
+      <c r="H10" s="3">
+        <v>93800</v>
+      </c>
+      <c r="I10" s="3">
+        <v>128500</v>
+      </c>
+      <c r="J10" s="3">
+        <v>45000</v>
+      </c>
+      <c r="K10" s="3">
         <v>69900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="L10" s="3">
         <v>100000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="M10" s="3">
         <v>136200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="N10" s="3">
         <v>50600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="O10" s="3">
         <v>58300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="P10" s="3">
         <v>97000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="Q10" s="3">
         <v>138100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="R10" s="3">
         <v>56000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="S10" s="3">
         <v>-106700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="T10" s="3">
         <v>87000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="U10" s="3">
         <v>205600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="V10" s="3">
         <v>60000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="W10" s="3">
         <v>35900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="X10" s="3">
         <v>70600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="Y10" s="3">
         <v>115300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="Z10" s="3">
         <v>30800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="AA10" s="3">
         <v>65400</v>
       </c>
-      <c r="X10" s="3">
+      <c r="AB10" s="3">
         <v>118500</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AC10" s="3">
         <v>186900</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AD10" s="3">
         <v>71700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AE10" s="3">
         <v>117400</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AF10" s="3">
         <v>-251300</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AG10" s="3">
         <v>-358200</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AH10" s="3">
         <v>66600</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AI10" s="3">
         <v>129500</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AJ10" s="3">
         <v>146500</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AK10" s="3">
         <v>281300</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AL10" s="3">
         <v>64700</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AM10" s="3">
         <v>124200</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AN10" s="3">
         <v>115900</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AO10" s="3">
         <v>171500</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1169,8 +1220,12 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
+      <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1276,8 +1331,20 @@
       <c r="AK12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AM12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AN12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AO12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1383,222 +1450,258 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>-5900</v>
-      </c>
-      <c r="E14" s="3">
-        <v>-200</v>
-      </c>
-      <c r="F14" s="3">
-        <v>58900</v>
+        <v>500</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G14" s="3">
+        <v>9200</v>
+      </c>
+      <c r="H14" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="I14" s="3">
+        <v>2700</v>
+      </c>
+      <c r="J14" s="3">
+        <v>58800</v>
+      </c>
+      <c r="K14" s="3">
         <v>9800</v>
       </c>
-      <c r="H14" s="3">
+      <c r="L14" s="3">
         <v>9200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="M14" s="3">
         <v>4300</v>
       </c>
-      <c r="J14" s="3">
+      <c r="N14" s="3">
         <v>4600</v>
       </c>
-      <c r="K14" s="3">
+      <c r="O14" s="3">
         <v>5300</v>
       </c>
-      <c r="L14" s="3">
+      <c r="P14" s="3">
         <v>10100</v>
       </c>
-      <c r="M14" s="3">
+      <c r="Q14" s="3">
         <v>300</v>
       </c>
-      <c r="N14" s="3">
+      <c r="R14" s="3">
         <v>400</v>
       </c>
-      <c r="O14" s="3">
+      <c r="S14" s="3">
         <v>-2800</v>
       </c>
-      <c r="P14" s="3">
+      <c r="T14" s="3">
         <v>6500</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="U14" s="3">
         <v>3000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="V14" s="3">
         <v>1900</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
-      <c r="T14" s="3">
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
         <v>29300</v>
       </c>
-      <c r="U14" s="3">
+      <c r="Y14" s="3">
         <v>3400</v>
       </c>
-      <c r="V14" s="3">
+      <c r="Z14" s="3">
         <v>5700</v>
       </c>
-      <c r="W14" s="3">
+      <c r="AA14" s="3">
         <v>15300</v>
       </c>
-      <c r="X14" s="3">
+      <c r="AB14" s="3">
         <v>200</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="AC14" s="3">
         <v>1600</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AD14" s="3">
         <v>1900</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AE14" s="3">
         <v>62500</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AF14" s="3">
         <v>2600</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AG14" s="3">
         <v>500</v>
       </c>
-      <c r="AD14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE14" s="3">
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI14" s="3">
         <v>200</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AJ14" s="3">
         <v>313200</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AK14" s="3">
         <v>7300</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AL14" s="3">
         <v>5800</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AM14" s="3">
         <v>7000</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AN14" s="3">
         <v>500</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AO14" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>7400</v>
+      </c>
+      <c r="E15" s="3">
+        <v>7600</v>
+      </c>
+      <c r="F15" s="3">
+        <v>9200</v>
+      </c>
+      <c r="G15" s="3">
+        <v>8500</v>
+      </c>
+      <c r="H15" s="3">
         <v>7800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="I15" s="3">
         <v>8500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="J15" s="3">
         <v>13100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="K15" s="3">
         <v>10000</v>
-      </c>
-      <c r="H15" s="3">
-        <v>10100</v>
-      </c>
-      <c r="I15" s="3">
-        <v>10200</v>
-      </c>
-      <c r="J15" s="3">
-        <v>10300</v>
-      </c>
-      <c r="K15" s="3">
-        <v>10900</v>
       </c>
       <c r="L15" s="3">
         <v>10100</v>
       </c>
       <c r="M15" s="3">
+        <v>10200</v>
+      </c>
+      <c r="N15" s="3">
         <v>10300</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>10900</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
+        <v>10100</v>
+      </c>
+      <c r="Q15" s="3">
+        <v>10300</v>
+      </c>
+      <c r="R15" s="3">
+        <v>10900</v>
+      </c>
+      <c r="S15" s="3">
         <v>5400</v>
       </c>
-      <c r="P15" s="3">
+      <c r="T15" s="3">
         <v>12200</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="U15" s="3">
         <v>24600</v>
       </c>
-      <c r="R15" s="3">
+      <c r="V15" s="3">
         <v>12600</v>
       </c>
-      <c r="S15" s="3">
+      <c r="W15" s="3">
         <v>12400</v>
       </c>
-      <c r="T15" s="3">
+      <c r="X15" s="3">
         <v>13300</v>
       </c>
-      <c r="U15" s="3">
+      <c r="Y15" s="3">
         <v>13200</v>
       </c>
-      <c r="V15" s="3">
+      <c r="Z15" s="3">
         <v>14100</v>
       </c>
-      <c r="W15" s="3">
+      <c r="AA15" s="3">
         <v>15300</v>
       </c>
-      <c r="X15" s="3">
+      <c r="AB15" s="3">
         <v>15100</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="AC15" s="3">
         <v>15500</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AD15" s="3">
         <v>15900</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AE15" s="3">
         <v>16500</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AF15" s="3">
         <v>16400</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AG15" s="3">
         <v>16400</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AH15" s="3">
         <v>16500</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AI15" s="3">
         <v>16900</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AJ15" s="3">
         <v>17000</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AK15" s="3">
         <v>31700</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AL15" s="3">
         <v>15000</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AM15" s="3">
         <v>14300</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AN15" s="3">
         <v>13100</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AO15" s="3">
         <v>13000</v>
       </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1633,222 +1736,250 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
+      <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>449300</v>
+        <v>500000</v>
       </c>
       <c r="E17" s="3">
-        <v>545900</v>
+        <v>603600</v>
       </c>
       <c r="F17" s="3">
-        <v>296300</v>
+        <v>311300</v>
       </c>
       <c r="G17" s="3">
+        <v>295800</v>
+      </c>
+      <c r="H17" s="3">
+        <v>448500</v>
+      </c>
+      <c r="I17" s="3">
+        <v>552300</v>
+      </c>
+      <c r="J17" s="3">
+        <v>298600</v>
+      </c>
+      <c r="K17" s="3">
         <v>243100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="L17" s="3">
         <v>446500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="M17" s="3">
         <v>570300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="N17" s="3">
         <v>301300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="O17" s="3">
         <v>270900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="P17" s="3">
         <v>443000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="Q17" s="3">
         <v>580000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="R17" s="3">
         <v>300300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="S17" s="3">
         <v>235800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="T17" s="3">
         <v>435900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="U17" s="3">
         <v>883900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="V17" s="3">
         <v>281500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="W17" s="3">
         <v>282800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="X17" s="3">
         <v>476300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="Y17" s="3">
         <v>588800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="Z17" s="3">
         <v>262900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="AA17" s="3">
         <v>309300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="AB17" s="3">
         <v>505300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AC17" s="3">
         <v>715800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AD17" s="3">
         <v>363500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AE17" s="3">
         <v>392100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AF17" s="3">
         <v>545000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AG17" s="3">
         <v>736300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AH17" s="3">
         <v>386600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AI17" s="3">
         <v>352400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AJ17" s="3">
         <v>899000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AK17" s="3">
         <v>1214900</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AL17" s="3">
         <v>411300</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AM17" s="3">
         <v>338500</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AN17" s="3">
         <v>516400</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AO17" s="3">
         <v>713900</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>17000</v>
+        <v>15100</v>
       </c>
       <c r="E18" s="3">
-        <v>56200</v>
+        <v>40800</v>
       </c>
       <c r="F18" s="3">
-        <v>-32900</v>
+        <v>-23200</v>
       </c>
       <c r="G18" s="3">
+        <v>-17500</v>
+      </c>
+      <c r="H18" s="3">
+        <v>14400</v>
+      </c>
+      <c r="I18" s="3">
+        <v>49800</v>
+      </c>
+      <c r="J18" s="3">
+        <v>-35100</v>
+      </c>
+      <c r="K18" s="3">
         <v>-7200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="L18" s="3">
         <v>10100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="M18" s="3">
         <v>40100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="N18" s="3">
         <v>-37100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="O18" s="3">
         <v>-29100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="P18" s="3">
         <v>-4900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="Q18" s="3">
         <v>28600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="R18" s="3">
         <v>-45600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="S18" s="3">
         <v>-10600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="T18" s="3">
         <v>-33100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="U18" s="3">
         <v>-16100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="V18" s="3">
         <v>-40700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="W18" s="3">
         <v>-60000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="X18" s="3">
         <v>-64700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="Y18" s="3">
         <v>6700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="Z18" s="3">
         <v>-58900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="AA18" s="3">
         <v>-52400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="AB18" s="3">
         <v>-3000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AC18" s="3">
         <v>56400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AD18" s="3">
         <v>-43800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AE18" s="3">
         <v>-60000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AF18" s="3">
         <v>3000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AG18" s="3">
         <v>78500</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AH18" s="3">
         <v>-49100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AI18" s="3">
         <v>5300</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AJ18" s="3">
         <v>-295600</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AK18" s="3">
         <v>27700</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AL18" s="3">
         <v>-55600</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AM18" s="3">
         <v>4300</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AN18" s="3">
         <v>5200</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AO18" s="3">
         <v>56800</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1886,8 +2017,12 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
+      <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1918,17 +2053,17 @@
       <c r="L20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
-      <c r="P20" s="3">
-        <v>0</v>
+      <c r="M20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q20" s="3">
         <v>0</v>
@@ -1993,436 +2128,496 @@
       <c r="AK20" s="3">
         <v>0</v>
       </c>
+      <c r="AL20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>24800</v>
+        <v>22500</v>
       </c>
       <c r="E21" s="3">
-        <v>64700</v>
+        <v>48400</v>
       </c>
       <c r="F21" s="3">
-        <v>-19800</v>
+        <v>-14000</v>
       </c>
       <c r="G21" s="3">
+        <v>-9000</v>
+      </c>
+      <c r="H21" s="3">
+        <v>22200</v>
+      </c>
+      <c r="I21" s="3">
+        <v>58400</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-22100</v>
+      </c>
+      <c r="K21" s="3">
         <v>2800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="L21" s="3">
         <v>20300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="M21" s="3">
         <v>50300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="N21" s="3">
         <v>-26800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="O21" s="3">
         <v>-18200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="P21" s="3">
         <v>5200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="Q21" s="3">
         <v>35700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="R21" s="3">
         <v>-31500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="S21" s="3">
         <v>-8800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="T21" s="3">
         <v>-19600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="U21" s="3">
         <v>11000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="V21" s="3">
         <v>-26800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="W21" s="3">
         <v>-46300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="X21" s="3">
         <v>-50100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="Y21" s="3">
         <v>21100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="Z21" s="3">
         <v>-43700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="AA21" s="3">
         <v>-36000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="AB21" s="3">
         <v>13200</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AC21" s="3">
         <v>73000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AD21" s="3">
         <v>-27000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AE21" s="3">
         <v>-42500</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AF21" s="3">
         <v>19200</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AG21" s="3">
         <v>95000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AH21" s="3">
         <v>-32500</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AI21" s="3">
         <v>22100</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AJ21" s="3">
         <v>-278600</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AK21" s="3">
         <v>59400</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AL21" s="3">
         <v>-40500</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AM21" s="3">
         <v>18600</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AN21" s="3">
         <v>18300</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AO21" s="3">
         <v>69700</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E22" s="3">
+        <v>3900</v>
+      </c>
+      <c r="F22" s="3">
+        <v>3800</v>
+      </c>
+      <c r="G22" s="3">
+        <v>4400</v>
+      </c>
+      <c r="H22" s="3">
         <v>5100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="I22" s="3">
         <v>5800</v>
       </c>
-      <c r="F22" s="3">
+      <c r="J22" s="3">
         <v>7700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="K22" s="3">
         <v>12000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="L22" s="3">
         <v>10600</v>
       </c>
-      <c r="I22" s="3">
+      <c r="M22" s="3">
         <v>10800</v>
       </c>
-      <c r="J22" s="3">
+      <c r="N22" s="3">
         <v>8300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="O22" s="3">
         <v>7500</v>
       </c>
-      <c r="L22" s="3">
+      <c r="P22" s="3">
         <v>6900</v>
       </c>
-      <c r="M22" s="3">
+      <c r="Q22" s="3">
         <v>4900</v>
       </c>
-      <c r="N22" s="3">
+      <c r="R22" s="3">
         <v>3900</v>
       </c>
-      <c r="O22" s="3">
+      <c r="S22" s="3">
         <v>2300</v>
       </c>
-      <c r="P22" s="3">
+      <c r="T22" s="3">
         <v>3100</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="U22" s="3">
         <v>4800</v>
       </c>
-      <c r="R22" s="3">
+      <c r="V22" s="3">
         <v>2500</v>
       </c>
-      <c r="S22" s="3">
+      <c r="W22" s="3">
         <v>2200</v>
       </c>
-      <c r="T22" s="3">
+      <c r="X22" s="3">
         <v>2300</v>
       </c>
-      <c r="U22" s="3">
+      <c r="Y22" s="3">
         <v>900</v>
       </c>
-      <c r="V22" s="3">
+      <c r="Z22" s="3">
         <v>2700</v>
       </c>
-      <c r="W22" s="3">
+      <c r="AA22" s="3">
         <v>1600</v>
       </c>
-      <c r="X22" s="3">
+      <c r="AB22" s="3">
         <v>1900</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="AC22" s="3">
         <v>1400</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AD22" s="3">
         <v>2500</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AE22" s="3">
         <v>1900</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AF22" s="3">
         <v>2500</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AG22" s="3">
         <v>1800</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AH22" s="3">
         <v>3500</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AI22" s="3">
         <v>2500</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AJ22" s="3">
         <v>3000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AK22" s="3">
         <v>4900</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AL22" s="3">
         <v>3000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AM22" s="3">
         <v>1500</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AN22" s="3">
         <v>700</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AO22" s="3">
         <v>600</v>
       </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>17800</v>
+        <v>9700</v>
       </c>
       <c r="E23" s="3">
-        <v>50900</v>
+        <v>36900</v>
       </c>
       <c r="F23" s="3">
-        <v>-99300</v>
+        <v>-26900</v>
       </c>
       <c r="G23" s="3">
+        <v>-30900</v>
+      </c>
+      <c r="H23" s="3">
+        <v>13800</v>
+      </c>
+      <c r="I23" s="3">
+        <v>41700</v>
+      </c>
+      <c r="J23" s="3">
+        <v>-101600</v>
+      </c>
+      <c r="K23" s="3">
         <v>-27800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="L23" s="3">
         <v>-9700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="M23" s="3">
         <v>25200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="N23" s="3">
         <v>-50000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="O23" s="3">
         <v>-41400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="P23" s="3">
         <v>-22000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="Q23" s="3">
         <v>23800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="R23" s="3">
         <v>-49500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="S23" s="3">
         <v>-12900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="T23" s="3">
         <v>-36200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="U23" s="3">
         <v>-20900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="V23" s="3">
         <v>-43200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="W23" s="3">
         <v>-62200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="X23" s="3">
         <v>-67000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="Y23" s="3">
         <v>5800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="Z23" s="3">
         <v>-61600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="AA23" s="3">
         <v>-54000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="AB23" s="3">
         <v>-4900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AC23" s="3">
         <v>55000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AD23" s="3">
         <v>-46300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AE23" s="3">
         <v>-62000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AF23" s="3">
         <v>500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AG23" s="3">
         <v>76600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AH23" s="3">
         <v>-52600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AI23" s="3">
         <v>2700</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AJ23" s="3">
         <v>-298600</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AK23" s="3">
         <v>22800</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AL23" s="3">
         <v>-58600</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AM23" s="3">
         <v>2900</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AN23" s="3">
         <v>4500</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AO23" s="3">
         <v>56100</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>10700</v>
+        <v>3100</v>
       </c>
       <c r="E24" s="3">
-        <v>1100</v>
+        <v>11900</v>
       </c>
       <c r="F24" s="3">
+        <v>-8600</v>
+      </c>
+      <c r="G24" s="3">
+        <v>-7700</v>
+      </c>
+      <c r="H24" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="I24" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="J24" s="3">
+        <v>2400</v>
+      </c>
+      <c r="K24" s="3">
+        <v>-300</v>
+      </c>
+      <c r="L24" s="3">
+        <v>200</v>
+      </c>
+      <c r="M24" s="3">
+        <v>300</v>
+      </c>
+      <c r="N24" s="3">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3">
+        <v>400</v>
+      </c>
+      <c r="P24" s="3">
         <v>100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="Q24" s="3">
+        <v>-400</v>
+      </c>
+      <c r="R24" s="3">
+        <v>800</v>
+      </c>
+      <c r="S24" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="T24" s="3">
+        <v>600</v>
+      </c>
+      <c r="U24" s="3">
+        <v>200</v>
+      </c>
+      <c r="V24" s="3">
+        <v>400</v>
+      </c>
+      <c r="W24" s="3">
+        <v>-9800</v>
+      </c>
+      <c r="X24" s="3">
+        <v>-18700</v>
+      </c>
+      <c r="Y24" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="Z24" s="3">
+        <v>-14900</v>
+      </c>
+      <c r="AA24" s="3">
+        <v>-13700</v>
+      </c>
+      <c r="AB24" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="AC24" s="3">
+        <v>19100</v>
+      </c>
+      <c r="AD24" s="3">
+        <v>-14200</v>
+      </c>
+      <c r="AE24" s="3">
+        <v>-15700</v>
+      </c>
+      <c r="AF24" s="3">
         <v>-300</v>
       </c>
-      <c r="H24" s="3">
-        <v>200</v>
-      </c>
-      <c r="I24" s="3">
-        <v>300</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
-      </c>
-      <c r="K24" s="3">
-        <v>400</v>
-      </c>
-      <c r="L24" s="3">
-        <v>100</v>
-      </c>
-      <c r="M24" s="3">
-        <v>-400</v>
-      </c>
-      <c r="N24" s="3">
+      <c r="AG24" s="3">
+        <v>16900</v>
+      </c>
+      <c r="AH24" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="AI24" s="3">
+        <v>-15000</v>
+      </c>
+      <c r="AJ24" s="3">
+        <v>5800</v>
+      </c>
+      <c r="AK24" s="3">
+        <v>9200</v>
+      </c>
+      <c r="AL24" s="3">
+        <v>-23800</v>
+      </c>
+      <c r="AM24" s="3">
+        <v>2600</v>
+      </c>
+      <c r="AN24" s="3">
         <v>800</v>
       </c>
-      <c r="O24" s="3">
-        <v>-10000</v>
-      </c>
-      <c r="P24" s="3">
-        <v>600</v>
-      </c>
-      <c r="Q24" s="3">
-        <v>200</v>
-      </c>
-      <c r="R24" s="3">
-        <v>400</v>
-      </c>
-      <c r="S24" s="3">
-        <v>-9800</v>
-      </c>
-      <c r="T24" s="3">
-        <v>-18700</v>
-      </c>
-      <c r="U24" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="V24" s="3">
-        <v>-14900</v>
-      </c>
-      <c r="W24" s="3">
-        <v>-13700</v>
-      </c>
-      <c r="X24" s="3">
-        <v>-3200</v>
-      </c>
-      <c r="Y24" s="3">
-        <v>19100</v>
-      </c>
-      <c r="Z24" s="3">
-        <v>-14200</v>
-      </c>
-      <c r="AA24" s="3">
-        <v>-15700</v>
-      </c>
-      <c r="AB24" s="3">
-        <v>-300</v>
-      </c>
-      <c r="AC24" s="3">
-        <v>16900</v>
-      </c>
-      <c r="AD24" s="3">
-        <v>-14000</v>
-      </c>
-      <c r="AE24" s="3">
-        <v>-15000</v>
-      </c>
-      <c r="AF24" s="3">
-        <v>5800</v>
-      </c>
-      <c r="AG24" s="3">
-        <v>9200</v>
-      </c>
-      <c r="AH24" s="3">
-        <v>-23800</v>
-      </c>
-      <c r="AI24" s="3">
-        <v>2600</v>
-      </c>
-      <c r="AJ24" s="3">
-        <v>800</v>
-      </c>
-      <c r="AK24" s="3">
+      <c r="AO24" s="3">
         <v>26800</v>
       </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2528,222 +2723,258 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>7100</v>
+        <v>6700</v>
       </c>
       <c r="E26" s="3">
-        <v>49700</v>
+        <v>25000</v>
       </c>
       <c r="F26" s="3">
-        <v>-99500</v>
+        <v>-18300</v>
       </c>
       <c r="G26" s="3">
+        <v>-23200</v>
+      </c>
+      <c r="H26" s="3">
+        <v>17900</v>
+      </c>
+      <c r="I26" s="3">
+        <v>43200</v>
+      </c>
+      <c r="J26" s="3">
+        <v>-103900</v>
+      </c>
+      <c r="K26" s="3">
         <v>-27400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="L26" s="3">
         <v>-9900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="M26" s="3">
         <v>24900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="N26" s="3">
         <v>-50000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="O26" s="3">
         <v>-41900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="P26" s="3">
         <v>-22100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="Q26" s="3">
         <v>24200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="R26" s="3">
         <v>-50300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="S26" s="3">
         <v>-2900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="T26" s="3">
         <v>-36800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="U26" s="3">
         <v>-21100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="V26" s="3">
         <v>-43600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="W26" s="3">
         <v>-52400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="X26" s="3">
         <v>-48300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="Y26" s="3">
         <v>7500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="Z26" s="3">
         <v>-46700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="AA26" s="3">
         <v>-40300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="AB26" s="3">
         <v>-1700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AC26" s="3">
         <v>35900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AD26" s="3">
         <v>-32200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AE26" s="3">
         <v>-46200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AF26" s="3">
         <v>800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AG26" s="3">
         <v>59700</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AH26" s="3">
         <v>-38600</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AI26" s="3">
         <v>17800</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AJ26" s="3">
         <v>-304400</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AK26" s="3">
         <v>13600</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AL26" s="3">
         <v>-34800</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AM26" s="3">
         <v>200</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AN26" s="3">
         <v>3800</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AO26" s="3">
         <v>29300</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>7100</v>
+        <v>6700</v>
       </c>
       <c r="E27" s="3">
-        <v>49700</v>
+        <v>25000</v>
       </c>
       <c r="F27" s="3">
-        <v>-99500</v>
+        <v>-18300</v>
       </c>
       <c r="G27" s="3">
+        <v>-23200</v>
+      </c>
+      <c r="H27" s="3">
+        <v>17900</v>
+      </c>
+      <c r="I27" s="3">
+        <v>43200</v>
+      </c>
+      <c r="J27" s="3">
+        <v>-103900</v>
+      </c>
+      <c r="K27" s="3">
         <v>-27400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="L27" s="3">
         <v>-9600</v>
-      </c>
-      <c r="I27" s="3">
-        <v>24200</v>
-      </c>
-      <c r="J27" s="3">
-        <v>-50400</v>
-      </c>
-      <c r="K27" s="3">
-        <v>-46300</v>
-      </c>
-      <c r="L27" s="3">
-        <v>-25000</v>
       </c>
       <c r="M27" s="3">
         <v>24200</v>
       </c>
       <c r="N27" s="3">
+        <v>-50400</v>
+      </c>
+      <c r="O27" s="3">
+        <v>-46300</v>
+      </c>
+      <c r="P27" s="3">
+        <v>-25000</v>
+      </c>
+      <c r="Q27" s="3">
+        <v>24200</v>
+      </c>
+      <c r="R27" s="3">
         <v>-50300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="S27" s="3">
         <v>-2900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="T27" s="3">
         <v>-36800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="U27" s="3">
         <v>-21100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="V27" s="3">
         <v>-43600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="W27" s="3">
         <v>-52400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="X27" s="3">
         <v>-48300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="Y27" s="3">
         <v>7500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="Z27" s="3">
         <v>-46700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="AA27" s="3">
         <v>-40300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="AB27" s="3">
         <v>-1700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AC27" s="3">
         <v>35900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AD27" s="3">
         <v>-32100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AE27" s="3">
         <v>-46200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AF27" s="3">
         <v>800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AG27" s="3">
         <v>59700</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AH27" s="3">
         <v>-38600</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AI27" s="3">
         <v>17800</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AJ27" s="3">
         <v>-304400</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AK27" s="3">
         <v>13600</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AL27" s="3">
         <v>-34800</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AM27" s="3">
         <v>200</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AN27" s="3">
         <v>3800</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AO27" s="3">
         <v>29300</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2849,8 +3080,20 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2864,49 +3107,49 @@
         <v>0</v>
       </c>
       <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3">
         <v>100</v>
       </c>
-      <c r="H29" s="3">
+      <c r="L29" s="3">
         <v>300</v>
       </c>
-      <c r="I29" s="3">
+      <c r="M29" s="3">
         <v>-700</v>
       </c>
-      <c r="J29" s="3">
+      <c r="N29" s="3">
         <v>-400</v>
       </c>
-      <c r="K29" s="3">
+      <c r="O29" s="3">
         <v>-4400</v>
       </c>
-      <c r="L29" s="3">
+      <c r="P29" s="3">
         <v>-2900</v>
       </c>
-      <c r="M29" s="3">
+      <c r="Q29" s="3">
         <v>-2000</v>
       </c>
-      <c r="N29" s="3">
+      <c r="R29" s="3">
         <v>-2400</v>
       </c>
-      <c r="O29" s="3">
+      <c r="S29" s="3">
         <v>-7300</v>
       </c>
-      <c r="P29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R29" s="3">
-        <v>0</v>
-      </c>
-      <c r="S29" s="3">
-        <v>0</v>
-      </c>
-      <c r="T29" s="3">
-        <v>0</v>
-      </c>
-      <c r="U29" s="3">
-        <v>0</v>
+      <c r="T29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="V29" s="3">
         <v>0</v>
@@ -2917,17 +3160,17 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-      <c r="Y29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB29" s="3" t="s">
-        <v>8</v>
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB29" s="3">
+        <v>0</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>8</v>
@@ -2935,29 +3178,41 @@
       <c r="AD29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AE29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI29" s="3">
         <v>-700</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AJ29" s="3">
         <v>21100</v>
       </c>
-      <c r="AG29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AI29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AJ29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AK29" s="3" t="s">
+      <c r="AK29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AM29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AN29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AO29" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3063,8 +3318,20 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3170,8 +3437,20 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3202,17 +3481,17 @@
       <c r="L32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
-      <c r="P32" s="3">
-        <v>0</v>
+      <c r="M32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q32" s="3">
         <v>0</v>
@@ -3277,115 +3556,139 @@
       <c r="AK32" s="3">
         <v>0</v>
       </c>
+      <c r="AL32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>7100</v>
+        <v>6700</v>
       </c>
       <c r="E33" s="3">
-        <v>49700</v>
+        <v>25000</v>
       </c>
       <c r="F33" s="3">
-        <v>-99500</v>
+        <v>-18300</v>
       </c>
       <c r="G33" s="3">
+        <v>-23200</v>
+      </c>
+      <c r="H33" s="3">
+        <v>17900</v>
+      </c>
+      <c r="I33" s="3">
+        <v>43200</v>
+      </c>
+      <c r="J33" s="3">
+        <v>-103900</v>
+      </c>
+      <c r="K33" s="3">
         <v>-27400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="L33" s="3">
         <v>-9600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="M33" s="3">
         <v>24200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="N33" s="3">
         <v>-50400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="O33" s="3">
         <v>-46300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="P33" s="3">
         <v>-25000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="Q33" s="3">
         <v>22100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="R33" s="3">
         <v>-52700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="S33" s="3">
         <v>-10200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="T33" s="3">
         <v>-36800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="U33" s="3">
         <v>-21100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="V33" s="3">
         <v>-43600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="W33" s="3">
         <v>-52400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="X33" s="3">
         <v>-48300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="Y33" s="3">
         <v>7500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="Z33" s="3">
         <v>-46700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="AA33" s="3">
         <v>-40300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="AB33" s="3">
         <v>-1700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AC33" s="3">
         <v>35900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AD33" s="3">
         <v>-32100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AE33" s="3">
         <v>-46200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AF33" s="3">
         <v>800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AG33" s="3">
         <v>59700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AH33" s="3">
         <v>-38600</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AI33" s="3">
         <v>17100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AJ33" s="3">
         <v>-283200</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AK33" s="3">
         <v>13600</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AL33" s="3">
         <v>-34800</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AM33" s="3">
         <v>200</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AN33" s="3">
         <v>3800</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AO33" s="3">
         <v>29300</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3491,227 +3794,263 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>7100</v>
+        <v>6700</v>
       </c>
       <c r="E35" s="3">
-        <v>49700</v>
+        <v>25000</v>
       </c>
       <c r="F35" s="3">
-        <v>-99500</v>
+        <v>-18300</v>
       </c>
       <c r="G35" s="3">
+        <v>-23200</v>
+      </c>
+      <c r="H35" s="3">
+        <v>17900</v>
+      </c>
+      <c r="I35" s="3">
+        <v>43200</v>
+      </c>
+      <c r="J35" s="3">
+        <v>-103900</v>
+      </c>
+      <c r="K35" s="3">
         <v>-27400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="L35" s="3">
         <v>-9600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="M35" s="3">
         <v>24200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="N35" s="3">
         <v>-50400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="O35" s="3">
         <v>-46300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="P35" s="3">
         <v>-25000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="Q35" s="3">
         <v>22100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="R35" s="3">
         <v>-52700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="S35" s="3">
         <v>-10200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="T35" s="3">
         <v>-36800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="U35" s="3">
         <v>-21100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="V35" s="3">
         <v>-43600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="W35" s="3">
         <v>-52400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="X35" s="3">
         <v>-48300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="Y35" s="3">
         <v>7500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="Z35" s="3">
         <v>-46700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="AA35" s="3">
         <v>-40300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="AB35" s="3">
         <v>-1700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AC35" s="3">
         <v>35900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AD35" s="3">
         <v>-32100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AE35" s="3">
         <v>-46200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AF35" s="3">
         <v>800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AG35" s="3">
         <v>59700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AH35" s="3">
         <v>-38600</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AI35" s="3">
         <v>17100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AJ35" s="3">
         <v>-283200</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AK35" s="3">
         <v>13600</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AL35" s="3">
         <v>-34800</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AM35" s="3">
         <v>200</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AN35" s="3">
         <v>3800</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AO35" s="3">
         <v>29300</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46053</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45962</v>
+      </c>
+      <c r="F38" s="2">
+        <v>45871</v>
+      </c>
+      <c r="G38" s="2">
+        <v>45780</v>
+      </c>
+      <c r="H38" s="2">
         <v>45682</v>
       </c>
-      <c r="E38" s="2">
+      <c r="I38" s="2">
         <v>45591</v>
       </c>
-      <c r="F38" s="2">
+      <c r="J38" s="2">
         <v>45500</v>
       </c>
-      <c r="G38" s="2">
+      <c r="K38" s="2">
         <v>45409</v>
       </c>
-      <c r="H38" s="2">
+      <c r="L38" s="2">
         <v>45318</v>
       </c>
-      <c r="I38" s="2">
+      <c r="M38" s="2">
         <v>45227</v>
       </c>
-      <c r="J38" s="2">
+      <c r="N38" s="2">
         <v>45136</v>
       </c>
-      <c r="K38" s="2">
+      <c r="O38" s="2">
         <v>45045</v>
       </c>
-      <c r="L38" s="2">
+      <c r="P38" s="2">
         <v>44954</v>
       </c>
-      <c r="M38" s="2">
+      <c r="Q38" s="2">
         <v>44863</v>
       </c>
-      <c r="N38" s="2">
+      <c r="R38" s="2">
         <v>44772</v>
       </c>
-      <c r="O38" s="2">
+      <c r="S38" s="2">
         <v>44681</v>
       </c>
-      <c r="P38" s="2">
+      <c r="T38" s="2">
         <v>44590</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="U38" s="2">
         <v>44499</v>
       </c>
-      <c r="R38" s="2">
+      <c r="V38" s="2">
         <v>44408</v>
       </c>
-      <c r="S38" s="2">
+      <c r="W38" s="2">
         <v>44317</v>
       </c>
-      <c r="T38" s="2">
+      <c r="X38" s="2">
         <v>44226</v>
       </c>
-      <c r="U38" s="2">
+      <c r="Y38" s="2">
         <v>44135</v>
       </c>
-      <c r="V38" s="2">
+      <c r="Z38" s="2">
         <v>44044</v>
       </c>
-      <c r="W38" s="2">
+      <c r="AA38" s="2">
         <v>43953</v>
       </c>
-      <c r="X38" s="2">
+      <c r="AB38" s="2">
         <v>43855</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AC38" s="2">
         <v>43764</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AD38" s="2">
         <v>43673</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AE38" s="2">
         <v>43582</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AF38" s="2">
         <v>43491</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AG38" s="2">
         <v>43400</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AH38" s="2">
         <v>43309</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AI38" s="2">
         <v>43218</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AJ38" s="2">
         <v>43127</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AK38" s="2">
         <v>43036</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AL38" s="2">
         <v>42945</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AM38" s="2">
         <v>42854</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AN38" s="2">
         <v>42763</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AO38" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3749,8 +4088,12 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
+      <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3788,115 +4131,131 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
+      <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>10100</v>
+      </c>
+      <c r="E41" s="3">
+        <v>11700</v>
+      </c>
+      <c r="F41" s="3">
+        <v>7300</v>
+      </c>
+      <c r="G41" s="3">
+        <v>9100</v>
+      </c>
+      <c r="H41" s="3">
         <v>9200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="I41" s="3">
         <v>11600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="J41" s="3">
         <v>8200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="K41" s="3">
         <v>10500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="L41" s="3">
         <v>8100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="M41" s="3">
         <v>15000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="N41" s="3">
         <v>7700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="O41" s="3">
         <v>14200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="P41" s="3">
         <v>11100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="Q41" s="3">
         <v>17300</v>
-      </c>
-      <c r="N41" s="3">
-        <v>7600</v>
-      </c>
-      <c r="O41" s="3">
-        <v>8800</v>
-      </c>
-      <c r="P41" s="3">
-        <v>10000</v>
-      </c>
-      <c r="Q41" s="3">
-        <v>11000</v>
       </c>
       <c r="R41" s="3">
         <v>7600</v>
       </c>
       <c r="S41" s="3">
+        <v>8800</v>
+      </c>
+      <c r="T41" s="3">
+        <v>10000</v>
+      </c>
+      <c r="U41" s="3">
+        <v>11000</v>
+      </c>
+      <c r="V41" s="3">
+        <v>7600</v>
+      </c>
+      <c r="W41" s="3">
         <v>8000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="X41" s="3">
         <v>9900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="Y41" s="3">
         <v>7400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="Z41" s="3">
         <v>7500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="AA41" s="3">
         <v>8200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="AB41" s="3">
         <v>9800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AC41" s="3">
         <v>24600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AD41" s="3">
         <v>8200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AE41" s="3">
         <v>14000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AF41" s="3">
         <v>22000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AG41" s="3">
         <v>20000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AH41" s="3">
         <v>13300</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AI41" s="3">
         <v>16100</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AJ41" s="3">
         <v>22400</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AK41" s="3">
         <v>17500</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AL41" s="3">
         <v>14200</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AM41" s="3">
         <v>19000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AN41" s="3">
         <v>132100</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AO41" s="3">
         <v>176600</v>
       </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4002,222 +4361,258 @@
       <c r="AK42" s="3">
         <v>0</v>
       </c>
+      <c r="AL42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>416400</v>
+      </c>
+      <c r="E43" s="3">
+        <v>315000</v>
+      </c>
+      <c r="F43" s="3">
+        <v>162000</v>
+      </c>
+      <c r="G43" s="3">
+        <v>97100</v>
+      </c>
+      <c r="H43" s="3">
         <v>354200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="I43" s="3">
         <v>278500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="J43" s="3">
         <v>162900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="K43" s="3">
         <v>118600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="L43" s="3">
         <v>315100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="M43" s="3">
         <v>221800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="N43" s="3">
         <v>150900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="O43" s="3">
         <v>98700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="P43" s="3">
         <v>277500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="Q43" s="3">
         <v>209300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="R43" s="3">
         <v>119000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="S43" s="3">
         <v>136000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="T43" s="3">
         <v>250200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="U43" s="3">
         <v>218100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="V43" s="3">
         <v>118300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="W43" s="3">
         <v>121100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="X43" s="3">
         <v>227200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="Y43" s="3">
         <v>167500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="Z43" s="3">
         <v>107500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="AA43" s="3">
         <v>90900</v>
       </c>
-      <c r="X43" s="3">
+      <c r="AB43" s="3">
         <v>238000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AC43" s="3">
         <v>162500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AD43" s="3">
         <v>98500</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AE43" s="3">
         <v>98200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AF43" s="3">
         <v>231100</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AG43" s="3">
         <v>138000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AH43" s="3">
         <v>99800</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AI43" s="3">
         <v>100100</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AJ43" s="3">
         <v>243400</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AK43" s="3">
         <v>153600</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AL43" s="3">
         <v>112500</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AM43" s="3">
         <v>86000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AN43" s="3">
         <v>178800</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AO43" s="3">
         <v>93300</v>
       </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>373100</v>
+      </c>
+      <c r="E44" s="3">
+        <v>377600</v>
+      </c>
+      <c r="F44" s="3">
+        <v>409500</v>
+      </c>
+      <c r="G44" s="3">
+        <v>326000</v>
+      </c>
+      <c r="H44" s="3">
         <v>367900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="I44" s="3">
         <v>365100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="J44" s="3">
         <v>405600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="K44" s="3">
         <v>377000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="L44" s="3">
         <v>386100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="M44" s="3">
         <v>416100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="N44" s="3">
         <v>391000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="O44" s="3">
         <v>353300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="P44" s="3">
         <v>444400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="Q44" s="3">
         <v>420900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="R44" s="3">
         <v>472100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="S44" s="3">
         <v>323500</v>
       </c>
-      <c r="P44" s="3">
+      <c r="T44" s="3">
         <v>444600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="U44" s="3">
         <v>421200</v>
       </c>
-      <c r="R44" s="3">
+      <c r="V44" s="3">
         <v>479100</v>
       </c>
-      <c r="S44" s="3">
+      <c r="W44" s="3">
         <v>309800</v>
       </c>
-      <c r="T44" s="3">
+      <c r="X44" s="3">
         <v>493300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="Y44" s="3">
         <v>508400</v>
       </c>
-      <c r="V44" s="3">
+      <c r="Z44" s="3">
         <v>591700</v>
       </c>
-      <c r="W44" s="3">
+      <c r="AA44" s="3">
         <v>469600</v>
       </c>
-      <c r="X44" s="3">
+      <c r="AB44" s="3">
         <v>578700</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AC44" s="3">
         <v>543600</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AD44" s="3">
         <v>723000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AE44" s="3">
         <v>467300</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AF44" s="3">
         <v>630200</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AG44" s="3">
         <v>576500</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AH44" s="3">
         <v>736100</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AI44" s="3">
         <v>493900</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AJ44" s="3">
         <v>675900</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AK44" s="3">
         <v>593600</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AL44" s="3">
         <v>787300</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AM44" s="3">
         <v>486900</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AN44" s="3">
         <v>561400</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AO44" s="3">
         <v>488000</v>
       </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4231,207 +4626,231 @@
         <v>8</v>
       </c>
       <c r="G45" s="3">
+        <v>1000</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K45" s="3">
         <v>1300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="L45" s="3">
         <v>14600</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O45" s="3">
         <v>33600</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M45" s="3">
+      <c r="P45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q45" s="3">
         <v>137000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="R45" s="3">
         <v>147800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="S45" s="3">
         <v>63400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="T45" s="3">
         <v>60600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="U45" s="3">
         <v>69000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="V45" s="3">
         <v>64700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="W45" s="3">
         <v>61900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="X45" s="3">
         <v>25300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="Y45" s="3">
         <v>23800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="Z45" s="3">
         <v>22400</v>
       </c>
-      <c r="W45" s="3">
+      <c r="AA45" s="3">
         <v>16200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="AB45" s="3">
         <v>24600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AC45" s="3">
         <v>18500</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AD45" s="3">
         <v>18100</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AE45" s="3">
         <v>11800</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AF45" s="3">
         <v>20700</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AG45" s="3">
         <v>16600</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AH45" s="3">
         <v>18700</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AI45" s="3">
         <v>9200</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AJ45" s="3">
         <v>12300</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AK45" s="3">
         <v>13400</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AL45" s="3">
         <v>13500</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AM45" s="3">
         <v>10700</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AN45" s="3">
         <v>8100</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AO45" s="3">
         <v>8100</v>
       </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>825700</v>
+      </c>
+      <c r="E46" s="3">
+        <v>743200</v>
+      </c>
+      <c r="F46" s="3">
+        <v>621400</v>
+      </c>
+      <c r="G46" s="3">
+        <v>465400</v>
+      </c>
+      <c r="H46" s="3">
         <v>758000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="I46" s="3">
         <v>686000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="J46" s="3">
         <v>601400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="K46" s="3">
         <v>530800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="L46" s="3">
         <v>763700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="M46" s="3">
         <v>716400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="N46" s="3">
         <v>598600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="O46" s="3">
         <v>537000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="P46" s="3">
         <v>790100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="Q46" s="3">
         <v>729600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="R46" s="3">
         <v>686200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="S46" s="3">
         <v>531700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="T46" s="3">
         <v>765400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="U46" s="3">
         <v>719200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="V46" s="3">
         <v>669700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="W46" s="3">
         <v>500800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="X46" s="3">
         <v>755700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="Y46" s="3">
         <v>707000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="Z46" s="3">
         <v>729100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="AA46" s="3">
         <v>584900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="AB46" s="3">
         <v>851200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AC46" s="3">
         <v>749200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AD46" s="3">
         <v>847800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AE46" s="3">
         <v>591400</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AF46" s="3">
         <v>904000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AG46" s="3">
         <v>751200</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AH46" s="3">
         <v>867900</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AI46" s="3">
         <v>619400</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AJ46" s="3">
         <v>954000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AK46" s="3">
         <v>778100</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AL46" s="3">
         <v>927500</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AM46" s="3">
         <v>602600</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AN46" s="3">
         <v>880400</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AO46" s="3">
         <v>766000</v>
       </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4462,17 +4881,17 @@
       <c r="L47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
-      </c>
-      <c r="N47" s="3">
-        <v>0</v>
-      </c>
-      <c r="O47" s="3">
-        <v>0</v>
-      </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -4537,222 +4956,258 @@
       <c r="AK47" s="3">
         <v>0</v>
       </c>
+      <c r="AL47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>217700</v>
+      </c>
+      <c r="E48" s="3">
+        <v>229200</v>
+      </c>
+      <c r="F48" s="3">
+        <v>234200</v>
+      </c>
+      <c r="G48" s="3">
+        <v>223900</v>
+      </c>
+      <c r="H48" s="3">
         <v>222700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="I48" s="3">
         <v>255200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="J48" s="3">
         <v>290100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="K48" s="3">
         <v>255400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="L48" s="3">
         <v>277500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="M48" s="3">
         <v>307900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="N48" s="3">
         <v>347500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="O48" s="3">
         <v>315100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="P48" s="3">
         <v>351700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="Q48" s="3">
         <v>367200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="R48" s="3">
         <v>391800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="S48" s="3">
         <v>360200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="T48" s="3">
         <v>323000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="U48" s="3">
         <v>344500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="V48" s="3">
         <v>380200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="W48" s="3">
         <v>329600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="X48" s="3">
         <v>330300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="Y48" s="3">
         <v>379200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="Z48" s="3">
         <v>414400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="AA48" s="3">
         <v>348600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="AB48" s="3">
         <v>352800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AC48" s="3">
         <v>394900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AD48" s="3">
         <v>420300</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AE48" s="3">
         <v>109800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AF48" s="3">
         <v>109400</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AG48" s="3">
         <v>112000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AH48" s="3">
         <v>108100</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AI48" s="3">
         <v>111300</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AJ48" s="3">
         <v>111000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AK48" s="3">
         <v>115300</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AL48" s="3">
         <v>112800</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AM48" s="3">
         <v>116600</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AN48" s="3">
         <v>107300</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AO48" s="3">
         <v>108500</v>
       </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>67900</v>
+      </c>
+      <c r="E49" s="3">
+        <v>70900</v>
+      </c>
+      <c r="F49" s="3">
+        <v>73900</v>
+      </c>
+      <c r="G49" s="3">
+        <v>78200</v>
+      </c>
+      <c r="H49" s="3">
         <v>81600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="I49" s="3">
         <v>85100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="J49" s="3">
         <v>87800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="K49" s="3">
         <v>94200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="L49" s="3">
         <v>97900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="M49" s="3">
         <v>104000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="N49" s="3">
         <v>107400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="O49" s="3">
         <v>110600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="P49" s="3">
         <v>119600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="Q49" s="3">
         <v>125200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="R49" s="3">
         <v>128000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="S49" s="3">
         <v>131700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="T49" s="3">
         <v>138700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="U49" s="3">
         <v>146500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="V49" s="3">
         <v>150700</v>
       </c>
-      <c r="S49" s="3">
+      <c r="W49" s="3">
         <v>155600</v>
       </c>
-      <c r="T49" s="3">
+      <c r="X49" s="3">
         <v>160200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="Y49" s="3">
         <v>170800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="Z49" s="3">
         <v>175200</v>
       </c>
-      <c r="W49" s="3">
+      <c r="AA49" s="3">
         <v>179800</v>
       </c>
-      <c r="X49" s="3">
+      <c r="AB49" s="3">
         <v>184300</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AC49" s="3">
         <v>188900</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AD49" s="3">
         <v>193900</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AE49" s="3">
         <v>199700</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AF49" s="3">
         <v>262400</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AG49" s="3">
         <v>267900</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AH49" s="3">
         <v>263200</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AI49" s="3">
         <v>268400</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AJ49" s="3">
         <v>273600</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AK49" s="3">
         <v>591900</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AL49" s="3">
         <v>535800</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AM49" s="3">
         <v>539400</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AN49" s="3">
         <v>473000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AO49" s="3">
         <v>475900</v>
       </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4858,8 +5313,20 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4965,115 +5432,139 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>10100</v>
+      </c>
+      <c r="E52" s="3">
+        <v>10400</v>
+      </c>
+      <c r="F52" s="3">
+        <v>10700</v>
+      </c>
+      <c r="G52" s="3">
+        <v>11100</v>
+      </c>
+      <c r="H52" s="3">
         <v>24200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="I52" s="3">
         <v>12300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="J52" s="3">
         <v>11600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="K52" s="3">
         <v>11800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="L52" s="3">
         <v>12500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="M52" s="3">
         <v>16700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="N52" s="3">
         <v>17300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="O52" s="3">
         <v>16600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="P52" s="3">
         <v>19700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="Q52" s="3">
         <v>42100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="R52" s="3">
         <v>44600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="S52" s="3">
         <v>52700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="T52" s="3">
         <v>39700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="U52" s="3">
         <v>42000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="V52" s="3">
         <v>43300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="W52" s="3">
         <v>45000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="X52" s="3">
         <v>42200</v>
       </c>
-      <c r="U52" s="3">
+      <c r="Y52" s="3">
         <v>40000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="Z52" s="3">
         <v>42100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="AA52" s="3">
         <v>43100</v>
       </c>
-      <c r="X52" s="3">
+      <c r="AB52" s="3">
         <v>39800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AC52" s="3">
         <v>47300</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AD52" s="3">
         <v>40500</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AE52" s="3">
         <v>45400</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AF52" s="3">
         <v>40200</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AG52" s="3">
         <v>41600</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AH52" s="3">
         <v>41700</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AI52" s="3">
         <v>40100</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AJ52" s="3">
         <v>42000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AK52" s="3">
         <v>41900</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AL52" s="3">
         <v>42500</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AM52" s="3">
         <v>41200</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AN52" s="3">
         <v>39200</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AO52" s="3">
         <v>38200</v>
       </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5179,115 +5670,139 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1130300</v>
+      </c>
+      <c r="E54" s="3">
+        <v>1063400</v>
+      </c>
+      <c r="F54" s="3">
+        <v>950800</v>
+      </c>
+      <c r="G54" s="3">
+        <v>790300</v>
+      </c>
+      <c r="H54" s="3">
         <v>1087600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="I54" s="3">
         <v>1052100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="J54" s="3">
         <v>1005200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="K54" s="3">
         <v>905100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="L54" s="3">
         <v>1151600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="M54" s="3">
         <v>1145000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="N54" s="3">
         <v>1070800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="O54" s="3">
         <v>980800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="P54" s="3">
         <v>1281100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="Q54" s="3">
         <v>1238400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="R54" s="3">
         <v>1223600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="S54" s="3">
         <v>1071600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="T54" s="3">
         <v>1266700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="U54" s="3">
         <v>1252200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="V54" s="3">
         <v>1244000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="W54" s="3">
         <v>1031100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="X54" s="3">
         <v>1288500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="Y54" s="3">
         <v>1297000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="Z54" s="3">
         <v>1360800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="AA54" s="3">
         <v>1156400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="AB54" s="3">
         <v>1428100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AC54" s="3">
         <v>1380300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AD54" s="3">
         <v>1502400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AE54" s="3">
         <v>946200</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AF54" s="3">
         <v>1316100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AG54" s="3">
         <v>1172700</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AH54" s="3">
         <v>1280900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AI54" s="3">
         <v>1039200</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AJ54" s="3">
         <v>1380600</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AK54" s="3">
         <v>1527200</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AL54" s="3">
         <v>1618700</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AM54" s="3">
         <v>1299800</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AN54" s="3">
         <v>1499900</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AO54" s="3">
         <v>1388600</v>
       </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5325,8 +5840,12 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
+      <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5364,189 +5883,205 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
+      <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>319200</v>
+      </c>
+      <c r="E57" s="3">
+        <v>345400</v>
+      </c>
+      <c r="F57" s="3">
+        <v>236500</v>
+      </c>
+      <c r="G57" s="3">
+        <v>148800</v>
+      </c>
+      <c r="H57" s="3">
         <v>303600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="I57" s="3">
         <v>299000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="J57" s="3">
         <v>266300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="K57" s="3">
         <v>299200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="L57" s="3">
         <v>343100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="M57" s="3">
         <v>385900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="N57" s="3">
         <v>275400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="O57" s="3">
         <v>267900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="P57" s="3">
         <v>355300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="Q57" s="3">
         <v>326000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="R57" s="3">
         <v>324400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="S57" s="3">
         <v>182600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="T57" s="3">
         <v>359700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="U57" s="3">
         <v>333100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="V57" s="3">
         <v>331100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="W57" s="3">
         <v>137600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="X57" s="3">
         <v>318800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="Y57" s="3">
         <v>314000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="Z57" s="3">
         <v>291500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="AA57" s="3">
         <v>143700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="AB57" s="3">
         <v>389100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AC57" s="3">
         <v>387700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AD57" s="3">
         <v>443100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AE57" s="3">
         <v>186800</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AF57" s="3">
         <v>464900</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AG57" s="3">
         <v>443300</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AH57" s="3">
         <v>463700</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AI57" s="3">
         <v>187900</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AJ57" s="3">
         <v>489000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AK57" s="3">
         <v>458800</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AL57" s="3">
         <v>511500</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AM57" s="3">
         <v>192700</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AN57" s="3">
         <v>480400</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AO57" s="3">
         <v>439700</v>
       </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>73700</v>
+      </c>
+      <c r="E58" s="3">
+        <v>76100</v>
+      </c>
+      <c r="F58" s="3">
+        <v>79400</v>
+      </c>
+      <c r="G58" s="3">
+        <v>64500</v>
+      </c>
+      <c r="H58" s="3">
         <v>101100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="I58" s="3">
         <v>124900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="J58" s="3">
         <v>147800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="K58" s="3">
         <v>102200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="L58" s="3">
         <v>349600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="M58" s="3">
         <v>126400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="N58" s="3">
         <v>150900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="O58" s="3">
         <v>100000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="P58" s="3">
         <v>116100</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
-      <c r="N58" s="3">
+      <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3">
         <v>40000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="S58" s="3">
         <v>40000</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
+        <v>0</v>
+      </c>
+      <c r="U58" s="3">
+        <v>0</v>
+      </c>
+      <c r="V58" s="3">
         <v>50000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="W58" s="3">
         <v>50000</v>
       </c>
-      <c r="T58" s="3">
-        <v>0</v>
-      </c>
-      <c r="U58" s="3">
-        <v>0</v>
-      </c>
-      <c r="V58" s="3">
-        <v>0</v>
-      </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA58" s="3">
         <v>75000</v>
-      </c>
-      <c r="X58" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y58" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z58" s="3">
-        <v>100000</v>
-      </c>
-      <c r="AA58" s="3">
-        <v>100000</v>
       </c>
       <c r="AB58" s="3">
         <v>0</v>
@@ -5572,442 +6107,502 @@
       <c r="AI58" s="3">
         <v>100000</v>
       </c>
-      <c r="AJ58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AK58" s="3" t="s">
+      <c r="AJ58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL58" s="3">
+        <v>100000</v>
+      </c>
+      <c r="AM58" s="3">
+        <v>100000</v>
+      </c>
+      <c r="AN58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AO58" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>52900</v>
+      </c>
+      <c r="E59" s="3">
+        <v>31900</v>
+      </c>
+      <c r="F59" s="3">
+        <v>12400</v>
+      </c>
+      <c r="G59" s="3">
+        <v>10400</v>
+      </c>
+      <c r="H59" s="3">
         <v>49700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="I59" s="3">
         <v>39500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="J59" s="3">
         <v>12000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="K59" s="3">
         <v>11300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="L59" s="3">
         <v>50000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="M59" s="3">
         <v>40400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="N59" s="3">
         <v>12800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="O59" s="3">
         <v>21400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="P59" s="3">
         <v>53700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="Q59" s="3">
         <v>368400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="R59" s="3">
         <v>244100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="S59" s="3">
         <v>192800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="T59" s="3">
         <v>402300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="U59" s="3">
         <v>363900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="V59" s="3">
         <v>228000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="W59" s="3">
         <v>186100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="X59" s="3">
         <v>231400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="Y59" s="3">
         <v>255700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="Z59" s="3">
         <v>206600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="AA59" s="3">
         <v>188000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="AB59" s="3">
         <v>296000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AC59" s="3">
         <v>304900</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AD59" s="3">
         <v>187000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AE59" s="3">
         <v>121700</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AF59" s="3">
         <v>219700</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AG59" s="3">
         <v>170000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AH59" s="3">
         <v>93200</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AI59" s="3">
         <v>125600</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AJ59" s="3">
         <v>252200</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AK59" s="3">
         <v>184300</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AL59" s="3">
         <v>89900</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AM59" s="3">
         <v>120500</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AN59" s="3">
         <v>207700</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AO59" s="3">
         <v>140800</v>
       </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>579800</v>
+      </c>
+      <c r="E60" s="3">
+        <v>525400</v>
+      </c>
+      <c r="F60" s="3">
+        <v>385700</v>
+      </c>
+      <c r="G60" s="3">
+        <v>279200</v>
+      </c>
+      <c r="H60" s="3">
         <v>534700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="I60" s="3">
         <v>523600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="J60" s="3">
         <v>489900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="K60" s="3">
         <v>478800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="L60" s="3">
         <v>849600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="M60" s="3">
         <v>624400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="N60" s="3">
         <v>516100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="O60" s="3">
         <v>462100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="P60" s="3">
         <v>609600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="Q60" s="3">
         <v>575700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="R60" s="3">
         <v>608400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="S60" s="3">
         <v>415400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="T60" s="3">
         <v>611300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="U60" s="3">
         <v>574300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="V60" s="3">
         <v>609100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="W60" s="3">
         <v>373700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="X60" s="3">
         <v>550200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="Y60" s="3">
         <v>569700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="Z60" s="3">
         <v>498100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="AA60" s="3">
         <v>406700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="AB60" s="3">
         <v>685000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AC60" s="3">
         <v>692600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AD60" s="3">
         <v>730200</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AE60" s="3">
         <v>408500</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AF60" s="3">
         <v>684600</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AG60" s="3">
         <v>613400</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AH60" s="3">
         <v>657000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AI60" s="3">
         <v>413500</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AJ60" s="3">
         <v>741200</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AK60" s="3">
         <v>643100</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AL60" s="3">
         <v>701400</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AM60" s="3">
         <v>413200</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AN60" s="3">
         <v>688100</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AO60" s="3">
         <v>580500</v>
       </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>242400</v>
+      </c>
+      <c r="E61" s="3">
+        <v>235800</v>
+      </c>
+      <c r="F61" s="3">
+        <v>287200</v>
+      </c>
+      <c r="G61" s="3">
+        <v>218600</v>
+      </c>
+      <c r="H61" s="3">
         <v>263000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="I61" s="3">
         <v>307300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="J61" s="3">
         <v>354100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="K61" s="3">
         <v>338500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="L61" s="3">
         <v>185400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="M61" s="3">
         <v>394100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="N61" s="3">
         <v>448800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="O61" s="3">
         <v>366900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="P61" s="3">
         <v>474100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="Q61" s="3">
         <v>250400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="R61" s="3">
         <v>218600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="S61" s="3">
         <v>185700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="T61" s="3">
         <v>200400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="U61" s="3">
         <v>183300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="V61" s="3">
         <v>153700</v>
       </c>
-      <c r="S61" s="3">
+      <c r="W61" s="3">
         <v>127600</v>
       </c>
-      <c r="T61" s="3">
+      <c r="X61" s="3">
         <v>150800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="Y61" s="3">
         <v>99500</v>
       </c>
-      <c r="V61" s="3">
+      <c r="Z61" s="3">
         <v>234600</v>
       </c>
-      <c r="W61" s="3">
+      <c r="AA61" s="3">
         <v>99700</v>
       </c>
-      <c r="X61" s="3">
+      <c r="AB61" s="3">
         <v>65900</v>
       </c>
-      <c r="Y61" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z61" s="3">
+      <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD61" s="3">
         <v>74100</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AE61" s="3">
         <v>33500</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AF61" s="3">
         <v>70100</v>
       </c>
-      <c r="AC61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD61" s="3">
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH61" s="3">
         <v>130200</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AI61" s="3">
         <v>96400</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AJ61" s="3">
         <v>113000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AK61" s="3">
         <v>41800</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AL61" s="3">
         <v>120100</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AM61" s="3">
         <v>59600</v>
       </c>
-      <c r="AJ61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK61" s="3">
+      <c r="AN61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO61" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>15200</v>
+      </c>
+      <c r="E62" s="3">
+        <v>15400</v>
+      </c>
+      <c r="F62" s="3">
+        <v>15900</v>
+      </c>
+      <c r="G62" s="3">
+        <v>16000</v>
+      </c>
+      <c r="H62" s="3">
         <v>3300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="I62" s="3">
         <v>11100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="J62" s="3">
         <v>12200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="K62" s="3">
         <v>12300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="L62" s="3">
         <v>13700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="M62" s="3">
         <v>14800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="N62" s="3">
         <v>19000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="O62" s="3">
         <v>14900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="P62" s="3">
         <v>15100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="Q62" s="3">
         <v>231500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="R62" s="3">
         <v>219800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="S62" s="3">
         <v>242100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="T62" s="3">
         <v>266300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="U62" s="3">
         <v>273600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="V62" s="3">
         <v>257300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="W62" s="3">
         <v>262100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="X62" s="3">
         <v>243300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="Y62" s="3">
         <v>247300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="Z62" s="3">
         <v>255900</v>
       </c>
-      <c r="W62" s="3">
+      <c r="AA62" s="3">
         <v>232300</v>
       </c>
-      <c r="X62" s="3">
+      <c r="AB62" s="3">
         <v>219800</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AC62" s="3">
         <v>230300</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AD62" s="3">
         <v>277400</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AE62" s="3">
         <v>53500</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AF62" s="3">
         <v>66600</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AG62" s="3">
         <v>67300</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AH62" s="3">
         <v>62000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AI62" s="3">
         <v>61400</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AJ62" s="3">
         <v>77700</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AK62" s="3">
         <v>112500</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AL62" s="3">
         <v>116200</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AM62" s="3">
         <v>113300</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AN62" s="3">
         <v>98900</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AO62" s="3">
         <v>101700</v>
       </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6113,8 +6708,20 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6220,8 +6827,20 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6327,115 +6946,139 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>840300</v>
+      </c>
+      <c r="E66" s="3">
+        <v>780100</v>
+      </c>
+      <c r="F66" s="3">
+        <v>694400</v>
+      </c>
+      <c r="G66" s="3">
+        <v>518100</v>
+      </c>
+      <c r="H66" s="3">
         <v>804300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="I66" s="3">
         <v>847200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="J66" s="3">
         <v>860800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="K66" s="3">
         <v>834500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="L66" s="3">
         <v>1054500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="M66" s="3">
         <v>1039000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="N66" s="3">
         <v>989800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="O66" s="3">
         <v>850000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="P66" s="3">
         <v>1104600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="Q66" s="3">
         <v>1037900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="R66" s="3">
         <v>1046800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="S66" s="3">
         <v>843200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="T66" s="3">
         <v>1029300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="U66" s="3">
         <v>980000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="V66" s="3">
         <v>994700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="W66" s="3">
         <v>738100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="X66" s="3">
         <v>944300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="Y66" s="3">
         <v>916600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="Z66" s="3">
         <v>988500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="AA66" s="3">
         <v>738700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="AB66" s="3">
         <v>970700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AC66" s="3">
         <v>922900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AD66" s="3">
         <v>1081700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AE66" s="3">
         <v>495600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AF66" s="3">
         <v>821400</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AG66" s="3">
         <v>680700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AH66" s="3">
         <v>849200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AI66" s="3">
         <v>571200</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AJ66" s="3">
         <v>931900</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AK66" s="3">
         <v>797400</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AL66" s="3">
         <v>937800</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AM66" s="3">
         <v>586100</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AN66" s="3">
         <v>787000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AO66" s="3">
         <v>682200</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6473,8 +7116,12 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
+      <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6580,8 +7227,20 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6687,8 +7346,20 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6794,8 +7465,20 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6901,8 +7584,20 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -6910,106 +7605,118 @@
         <v>-699200</v>
       </c>
       <c r="E72" s="3">
+        <v>-705800</v>
+      </c>
+      <c r="F72" s="3">
+        <v>-730800</v>
+      </c>
+      <c r="G72" s="3">
+        <v>-712600</v>
+      </c>
+      <c r="H72" s="3">
+        <v>-699200</v>
+      </c>
+      <c r="I72" s="3">
         <v>-706300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="J72" s="3">
         <v>-756000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="K72" s="3">
         <v>-656600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="L72" s="3">
         <v>-629200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="M72" s="3">
         <v>-619600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="N72" s="3">
         <v>-643700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="O72" s="3">
         <v>-593400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="P72" s="3">
         <v>-547100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="Q72" s="3">
         <v>-522100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="R72" s="3">
         <v>-544200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="S72" s="3">
         <v>-491500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="T72" s="3">
         <v>-480500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="U72" s="3">
         <v>-443700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="V72" s="3">
         <v>-466300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="W72" s="3">
         <v>-422600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="X72" s="3">
         <v>-370300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="Y72" s="3">
         <v>-322000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="Z72" s="3">
         <v>-329500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="AA72" s="3">
         <v>-282800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="AB72" s="3">
         <v>-242500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AC72" s="3">
         <v>-240800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AD72" s="3">
         <v>-276700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AE72" s="3">
         <v>-244600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AF72" s="3">
         <v>-198400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AG72" s="3">
         <v>-199100</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AH72" s="3">
         <v>-258800</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AI72" s="3">
         <v>-220200</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AJ72" s="3">
         <v>-237300</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AK72" s="3">
         <v>46000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AL72" s="3">
         <v>-2400</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AM72" s="3">
         <v>32400</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AN72" s="3">
         <v>32100</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AO72" s="3">
         <v>28400</v>
       </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7115,8 +7822,20 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7222,8 +7941,20 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7329,115 +8060,139 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>290000</v>
+      </c>
+      <c r="E76" s="3">
+        <v>283200</v>
+      </c>
+      <c r="F76" s="3">
+        <v>256500</v>
+      </c>
+      <c r="G76" s="3">
+        <v>272200</v>
+      </c>
+      <c r="H76" s="3">
         <v>283300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="I76" s="3">
         <v>204800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="J76" s="3">
         <v>144400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="K76" s="3">
         <v>70600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="L76" s="3">
         <v>97100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="M76" s="3">
         <v>106000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="N76" s="3">
         <v>81100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="O76" s="3">
         <v>130800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="P76" s="3">
         <v>176500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="Q76" s="3">
         <v>200500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="R76" s="3">
         <v>176800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="S76" s="3">
         <v>228400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="T76" s="3">
         <v>237500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="U76" s="3">
         <v>272200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="V76" s="3">
         <v>249300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="W76" s="3">
         <v>293000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="X76" s="3">
         <v>344200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="Y76" s="3">
         <v>380400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="Z76" s="3">
         <v>372300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="AA76" s="3">
         <v>417800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="AB76" s="3">
         <v>457400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AC76" s="3">
         <v>457300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AD76" s="3">
         <v>420800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AE76" s="3">
         <v>450600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AF76" s="3">
         <v>494700</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AG76" s="3">
         <v>492000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AH76" s="3">
         <v>431700</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AI76" s="3">
         <v>468000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AJ76" s="3">
         <v>448700</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AK76" s="3">
         <v>729800</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AL76" s="3">
         <v>680900</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AM76" s="3">
         <v>713700</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AN76" s="3">
         <v>712900</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AO76" s="3">
         <v>706400</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7543,227 +8298,263 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46053</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45962</v>
+      </c>
+      <c r="F80" s="2">
+        <v>45871</v>
+      </c>
+      <c r="G80" s="2">
+        <v>45780</v>
+      </c>
+      <c r="H80" s="2">
         <v>45682</v>
       </c>
-      <c r="E80" s="2">
+      <c r="I80" s="2">
         <v>45591</v>
       </c>
-      <c r="F80" s="2">
+      <c r="J80" s="2">
         <v>45500</v>
       </c>
-      <c r="G80" s="2">
+      <c r="K80" s="2">
         <v>45409</v>
       </c>
-      <c r="H80" s="2">
+      <c r="L80" s="2">
         <v>45318</v>
       </c>
-      <c r="I80" s="2">
+      <c r="M80" s="2">
         <v>45227</v>
       </c>
-      <c r="J80" s="2">
+      <c r="N80" s="2">
         <v>45136</v>
       </c>
-      <c r="K80" s="2">
+      <c r="O80" s="2">
         <v>45045</v>
       </c>
-      <c r="L80" s="2">
+      <c r="P80" s="2">
         <v>44954</v>
       </c>
-      <c r="M80" s="2">
+      <c r="Q80" s="2">
         <v>44863</v>
       </c>
-      <c r="N80" s="2">
+      <c r="R80" s="2">
         <v>44772</v>
       </c>
-      <c r="O80" s="2">
+      <c r="S80" s="2">
         <v>44681</v>
       </c>
-      <c r="P80" s="2">
+      <c r="T80" s="2">
         <v>44590</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="U80" s="2">
         <v>44499</v>
       </c>
-      <c r="R80" s="2">
+      <c r="V80" s="2">
         <v>44408</v>
       </c>
-      <c r="S80" s="2">
+      <c r="W80" s="2">
         <v>44317</v>
       </c>
-      <c r="T80" s="2">
+      <c r="X80" s="2">
         <v>44226</v>
       </c>
-      <c r="U80" s="2">
+      <c r="Y80" s="2">
         <v>44135</v>
       </c>
-      <c r="V80" s="2">
+      <c r="Z80" s="2">
         <v>44044</v>
       </c>
-      <c r="W80" s="2">
+      <c r="AA80" s="2">
         <v>43953</v>
       </c>
-      <c r="X80" s="2">
+      <c r="AB80" s="2">
         <v>43855</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AC80" s="2">
         <v>43764</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AD80" s="2">
         <v>43673</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AE80" s="2">
         <v>43582</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AF80" s="2">
         <v>43491</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AG80" s="2">
         <v>43400</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AH80" s="2">
         <v>43309</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AI80" s="2">
         <v>43218</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AJ80" s="2">
         <v>43127</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AK80" s="2">
         <v>43036</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AL80" s="2">
         <v>42945</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AM80" s="2">
         <v>42854</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AN80" s="2">
         <v>42763</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AO80" s="2">
         <v>42672</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>7100</v>
+        <v>6700</v>
       </c>
       <c r="E81" s="3">
-        <v>49700</v>
+        <v>25000</v>
       </c>
       <c r="F81" s="3">
-        <v>-99500</v>
+        <v>-18300</v>
       </c>
       <c r="G81" s="3">
+        <v>-23200</v>
+      </c>
+      <c r="H81" s="3">
+        <v>17900</v>
+      </c>
+      <c r="I81" s="3">
+        <v>43200</v>
+      </c>
+      <c r="J81" s="3">
+        <v>-103900</v>
+      </c>
+      <c r="K81" s="3">
         <v>-27400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="L81" s="3">
         <v>-9600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="M81" s="3">
         <v>24200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="N81" s="3">
         <v>-50400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="O81" s="3">
         <v>-46300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="P81" s="3">
         <v>-25000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="Q81" s="3">
         <v>22100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="R81" s="3">
         <v>-52700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="S81" s="3">
         <v>-10200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="T81" s="3">
         <v>-36800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="U81" s="3">
         <v>-21100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="V81" s="3">
         <v>-43600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="W81" s="3">
         <v>-52400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="X81" s="3">
         <v>-48300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="Y81" s="3">
         <v>7500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="Z81" s="3">
         <v>-46700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="AA81" s="3">
         <v>-40300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="AB81" s="3">
         <v>-1700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AC81" s="3">
         <v>35900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AD81" s="3">
         <v>-32100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AE81" s="3">
         <v>-46200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AF81" s="3">
         <v>800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AG81" s="3">
         <v>59700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AH81" s="3">
         <v>-38600</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AI81" s="3">
         <v>17100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AJ81" s="3">
         <v>-283200</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AK81" s="3">
         <v>13600</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AL81" s="3">
         <v>-34800</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AM81" s="3">
         <v>200</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AN81" s="3">
         <v>3800</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AO81" s="3">
         <v>29300</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7801,115 +8592,131 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
+      <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>10100</v>
+        <v>7800</v>
       </c>
       <c r="E83" s="3">
-        <v>10200</v>
+        <v>8500</v>
       </c>
       <c r="F83" s="3">
-        <v>10300</v>
+        <v>13100</v>
       </c>
       <c r="G83" s="3">
-        <v>10900</v>
+        <v>10000</v>
       </c>
       <c r="H83" s="3">
         <v>10100</v>
       </c>
       <c r="I83" s="3">
+        <v>10200</v>
+      </c>
+      <c r="J83" s="3">
         <v>10300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>10900</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L83" s="3">
-        <v>13600</v>
+        <v>10100</v>
       </c>
       <c r="M83" s="3">
-        <v>12400</v>
+        <v>10300</v>
       </c>
       <c r="N83" s="3">
-        <v>14100</v>
-      </c>
-      <c r="O83" s="3">
-        <v>14100</v>
+        <v>10900</v>
+      </c>
+      <c r="O83" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P83" s="3">
         <v>13600</v>
       </c>
       <c r="Q83" s="3">
+        <v>12400</v>
+      </c>
+      <c r="R83" s="3">
+        <v>14100</v>
+      </c>
+      <c r="S83" s="3">
+        <v>14100</v>
+      </c>
+      <c r="T83" s="3">
+        <v>13600</v>
+      </c>
+      <c r="U83" s="3">
         <v>27200</v>
       </c>
-      <c r="R83" s="3">
+      <c r="V83" s="3">
         <v>13900</v>
       </c>
-      <c r="S83" s="3">
+      <c r="W83" s="3">
         <v>13700</v>
       </c>
-      <c r="T83" s="3">
+      <c r="X83" s="3">
         <v>14600</v>
       </c>
-      <c r="U83" s="3">
+      <c r="Y83" s="3">
         <v>14400</v>
       </c>
-      <c r="V83" s="3">
+      <c r="Z83" s="3">
         <v>15200</v>
       </c>
-      <c r="W83" s="3">
+      <c r="AA83" s="3">
         <v>16400</v>
-      </c>
-      <c r="X83" s="3">
-        <v>16200</v>
-      </c>
-      <c r="Y83" s="3">
-        <v>16500</v>
-      </c>
-      <c r="Z83" s="3">
-        <v>16800</v>
-      </c>
-      <c r="AA83" s="3">
-        <v>17600</v>
       </c>
       <c r="AB83" s="3">
         <v>16200</v>
       </c>
       <c r="AC83" s="3">
+        <v>16500</v>
+      </c>
+      <c r="AD83" s="3">
+        <v>16800</v>
+      </c>
+      <c r="AE83" s="3">
+        <v>17600</v>
+      </c>
+      <c r="AF83" s="3">
+        <v>16200</v>
+      </c>
+      <c r="AG83" s="3">
         <v>16600</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AH83" s="3">
         <v>16500</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AI83" s="3">
         <v>16900</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AJ83" s="3">
         <v>17000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AK83" s="3">
         <v>31700</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AL83" s="3">
         <v>15000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AM83" s="3">
         <v>14300</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AN83" s="3">
         <v>13100</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AO83" s="3">
         <v>13000</v>
       </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8015,8 +8822,20 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8122,8 +8941,20 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8229,8 +9060,20 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8336,8 +9179,20 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8443,115 +9298,139 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-29400</v>
+      </c>
+      <c r="E89" s="3">
+        <v>66200</v>
+      </c>
+      <c r="F89" s="3">
+        <v>-67600</v>
+      </c>
+      <c r="G89" s="3">
+        <v>53100</v>
+      </c>
+      <c r="H89" s="3">
         <v>-41900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="I89" s="3">
         <v>47400</v>
       </c>
-      <c r="F89" s="3">
-        <v>-144000</v>
-      </c>
-      <c r="G89" s="3">
+      <c r="J89" s="3">
+        <v>-143500</v>
+      </c>
+      <c r="K89" s="3">
         <v>81700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="L89" s="3">
         <v>-35800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="M89" s="3">
         <v>72000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="N89" s="3">
         <v>-123100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="O89" s="3">
         <v>114300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="P89" s="3">
         <v>-32000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="Q89" s="3">
         <v>38400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="R89" s="3">
         <v>-29000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="S89" s="3">
         <v>-5800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="T89" s="3">
         <v>-16400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="U89" s="3">
         <v>24300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="V89" s="3">
         <v>-17300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="W89" s="3">
         <v>-8700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="X89" s="3">
         <v>-49800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="Y89" s="3">
         <v>144500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="Z89" s="3">
         <v>-53100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="AA89" s="3">
         <v>-100700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="AB89" s="3">
         <v>-69400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AC89" s="3">
         <v>201700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AD89" s="3">
         <v>-40200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AE89" s="3">
         <v>-55000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AF89" s="3">
         <v>-60700</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AG89" s="3">
         <v>263900</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AH89" s="3">
         <v>-27400</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AI89" s="3">
         <v>-81400</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AJ89" s="3">
         <v>-58200</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AK89" s="3">
         <v>199600</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AL89" s="3">
         <v>-56000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AM89" s="3">
         <v>-77000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AN89" s="3">
         <v>-34300</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AO89" s="3">
         <v>204500</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8589,115 +9468,131 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
+      <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="F91" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="G91" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="H91" s="3">
         <v>-2800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="I91" s="3">
         <v>-3100</v>
       </c>
-      <c r="F91" s="3">
-        <v>-3500</v>
-      </c>
-      <c r="G91" s="3">
+      <c r="J91" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="K91" s="3">
         <v>-2600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="L91" s="3">
         <v>-3300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="M91" s="3">
         <v>-4000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="N91" s="3">
         <v>-4200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="O91" s="3">
         <v>-3400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="P91" s="3">
         <v>-4900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="Q91" s="3">
         <v>-7100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="R91" s="3">
         <v>-9700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="S91" s="3">
         <v>-200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="T91" s="3">
         <v>-12100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="U91" s="3">
         <v>-9900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="V91" s="3">
         <v>-11400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="W91" s="3">
         <v>-11300</v>
       </c>
-      <c r="T91" s="3">
+      <c r="X91" s="3">
         <v>-9700</v>
       </c>
-      <c r="U91" s="3">
+      <c r="Y91" s="3">
         <v>-9100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="Z91" s="3">
         <v>-7100</v>
       </c>
-      <c r="W91" s="3">
+      <c r="AA91" s="3">
         <v>-9400</v>
       </c>
-      <c r="X91" s="3">
+      <c r="AB91" s="3">
         <v>-7600</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AC91" s="3">
         <v>-10900</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AD91" s="3">
         <v>-8300</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AE91" s="3">
         <v>-14700</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AF91" s="3">
         <v>-8600</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AG91" s="3">
         <v>-14900</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AH91" s="3">
         <v>-8200</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AI91" s="3">
         <v>-12700</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AJ91" s="3">
         <v>-7700</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AK91" s="3">
         <v>-22400</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AL91" s="3">
         <v>-7900</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AM91" s="3">
         <v>-8200</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AN91" s="3">
         <v>-9000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AO91" s="3">
         <v>-11300</v>
       </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8803,8 +9698,20 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8910,115 +9817,139 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="F94" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="G94" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="H94" s="3">
         <v>-2800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="I94" s="3">
         <v>-2500</v>
       </c>
-      <c r="F94" s="3">
-        <v>-3200</v>
-      </c>
-      <c r="G94" s="3">
+      <c r="J94" s="3">
+        <v>-3700</v>
+      </c>
+      <c r="K94" s="3">
         <v>-2600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="L94" s="3">
         <v>-3300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="M94" s="3">
         <v>-4000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="N94" s="3">
         <v>17300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="O94" s="3">
         <v>-4700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="P94" s="3">
         <v>-6000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="Q94" s="3">
         <v>-10600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="R94" s="3">
         <v>-9700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="S94" s="3">
         <v>-10000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="T94" s="3">
         <v>-11900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="U94" s="3">
         <v>-20800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="V94" s="3">
         <v>-11000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="W94" s="3">
         <v>-11300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="X94" s="3">
         <v>-12600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="Y94" s="3">
         <v>-7500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="Z94" s="3">
         <v>-5500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="AA94" s="3">
         <v>-7900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="AB94" s="3">
         <v>-5600</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AC94" s="3">
         <v>-10000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AD94" s="3">
         <v>-6100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AE94" s="3">
         <v>-13000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AF94" s="3">
         <v>-7400</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AG94" s="3">
         <v>-25000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AH94" s="3">
         <v>-9300</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AI94" s="3">
         <v>-11300</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AJ94" s="3">
         <v>-7500</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AK94" s="3">
         <v>-81300</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AL94" s="3">
         <v>-9100</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AM94" s="3">
         <v>-190800</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AN94" s="3">
         <v>-10200</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AO94" s="3">
         <v>-10600</v>
       </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9056,8 +9987,12 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
+      <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9088,17 +10023,17 @@
       <c r="L96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -9163,8 +10098,20 @@
       <c r="AK96" s="3">
         <v>0</v>
       </c>
+      <c r="AL96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9270,8 +10217,20 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9377,8 +10336,20 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9484,115 +10455,139 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>15100</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-47900</v>
+      </c>
+      <c r="F100" s="3">
+        <v>65000</v>
+      </c>
+      <c r="G100" s="3">
+        <v>-37500</v>
+      </c>
+      <c r="H100" s="3">
         <v>32500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="I100" s="3">
         <v>-37300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="J100" s="3">
         <v>139900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="K100" s="3">
         <v>-65600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="L100" s="3">
         <v>18700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="M100" s="3">
         <v>-52000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="N100" s="3">
         <v>93200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="O100" s="3">
         <v>-106100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="P100" s="3">
         <v>32700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="Q100" s="3">
         <v>-9700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="R100" s="3">
         <v>33400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="S100" s="3">
         <v>25000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="T100" s="3">
         <v>17300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="U100" s="3">
         <v>3400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="V100" s="3">
         <v>24900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="W100" s="3">
         <v>25700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="X100" s="3">
         <v>62200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="Y100" s="3">
         <v>-135600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="Z100" s="3">
         <v>59500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="AA100" s="3">
         <v>108800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="AB100" s="3">
         <v>65900</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AC100" s="3">
         <v>-175300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AD100" s="3">
         <v>40600</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AE100" s="3">
         <v>60000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AF100" s="3">
         <v>70100</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AG100" s="3">
         <v>-232200</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AH100" s="3">
         <v>33800</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AI100" s="3">
         <v>83400</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AJ100" s="3">
         <v>71200</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AK100" s="3">
         <v>-119400</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AL100" s="3">
         <v>60500</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AM100" s="3">
         <v>155100</v>
       </c>
-      <c r="AJ100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK100" s="3">
+      <c r="AN100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO100" s="3">
         <v>-26300</v>
       </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9623,17 +10618,17 @@
       <c r="L101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
-      </c>
-      <c r="N101" s="3">
-        <v>0</v>
-      </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -9698,111 +10693,135 @@
       <c r="AK101" s="3">
         <v>0</v>
       </c>
+      <c r="AL101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-18000</v>
+      </c>
+      <c r="E102" s="3">
+        <v>14000</v>
+      </c>
+      <c r="F102" s="3">
+        <v>-6300</v>
+      </c>
+      <c r="G102" s="3">
+        <v>12000</v>
+      </c>
+      <c r="H102" s="3">
         <v>-12200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="I102" s="3">
         <v>7700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="J102" s="3">
         <v>-7300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="K102" s="3">
         <v>13500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="L102" s="3">
         <v>-20300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="M102" s="3">
         <v>16000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="N102" s="3">
         <v>-12700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="O102" s="3">
         <v>3500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="P102" s="3">
         <v>-5300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="Q102" s="3">
         <v>18100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="R102" s="3">
         <v>-5300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="S102" s="3">
         <v>9200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="T102" s="3">
         <v>-10800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="U102" s="3">
         <v>6700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="V102" s="3">
         <v>-3600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="W102" s="3">
         <v>6100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="X102" s="3">
         <v>2600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="Y102" s="3">
         <v>-100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="Z102" s="3">
         <v>-800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="AA102" s="3">
         <v>-1600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="AB102" s="3">
         <v>-14800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AC102" s="3">
         <v>16400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AD102" s="3">
         <v>-5800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AE102" s="3">
         <v>-8000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AF102" s="3">
         <v>2000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AG102" s="3">
         <v>6800</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AH102" s="3">
         <v>-2900</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AI102" s="3">
         <v>-8200</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AJ102" s="3">
         <v>4900</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AK102" s="3">
         <v>-1500</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AL102" s="3">
         <v>-4800</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AM102" s="3">
         <v>-112700</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AN102" s="3">
         <v>-44500</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AO102" s="3">
         <v>167700</v>
       </c>
     </row>
